--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -567,7 +567,7 @@
         <v>44460.70982638889</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44606</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45810.50783564815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45616</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45189</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>44490</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44370</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>44112</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45735.34555555556</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45352.45320601852</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44867</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>44347</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>44145</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44266</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>45174.32886574074</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45428.42564814815</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>44937</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45652.74018518518</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45447</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45075</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>44120</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45730.63277777778</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45695.93653935185</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45358.44835648148</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>44785.43395833333</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45093.3646875</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>45093.3703587963</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>45853</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45832</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45222</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44175</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44375</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>44602</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45695.93015046296</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45615.62699074074</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>45215</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>44980</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>45316</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>45721.65631944445</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>45496.6761574074</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45096</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45541.51222222222</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>45042</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44909</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44504.50979166666</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45594</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44120</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>45701.45335648148</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45103</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>45449.38423611111</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45110</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>44448.31037037037</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>44648</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>45581.56951388889</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>44656</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>45621.64417824074</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>45840.8834375</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45621.63548611111</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45846.4975</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>45621.64115740741</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45850.60619212963</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>45754.48619212963</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>45307</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>44365</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>45863.39380787037</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44917</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>45596.52869212963</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>45604.50471064815</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>44966.64579861111</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44917</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44073</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44057</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44060</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44059</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44064</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44074</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44053.41489583333</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>44261</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>44347</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44179</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44073.7496875</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>44130</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>44378</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44110.43048611111</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44120</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44224</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44183</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>44230</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44300.3625</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44385.40346064815</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>44123</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>44208</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44491</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>44120</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44278</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44407.34103009259</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>44363.76037037037</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>44267.32773148148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>44201</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>44462</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44407.35815972222</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>44379</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>44630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>44089</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>44418.56681712963</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>44320</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44236</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44225</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44342.65030092592</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44297</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>44194</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44365</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44071</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44363.75403935185</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44889.52459490741</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>44302</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>44691</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>44138</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>44474</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>44137.79510416667</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>44412</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>44859</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>44102</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44164</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44861</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44475</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44246</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44365</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44473.51576388889</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>44245</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44362</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44581</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>44449.57666666667</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44656</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>44587</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>44844</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>44816</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44571.48392361111</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>44612</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>44152</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44645.61962962963</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44187</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44088</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>44201</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>44565</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>44130</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>44256</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>44365</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44312.52064814815</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44088</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>44593.58975694444</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44131</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>44831.51668981482</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>44840</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44783</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44179</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>44365</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>44375.42613425926</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>44369</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44084</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44566</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>44060</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44328</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44684</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44347</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44365</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>44306</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>44806.30436342592</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>44315.67481481482</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>44364.69368055555</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>44493.7688425926</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>44488.93328703703</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>44362</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>44833.85800925926</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>44217.63880787037</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44083</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>44078</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44386.50282407407</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>44468.38931712963</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>44587</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>44624.4716087963</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>44593</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>44294.69576388889</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>44449.61309027778</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44449</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>44169</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>44172</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>44419</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>44321.32876157408</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44295.56511574074</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44851</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>44340.37452546296</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>44136</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>44284</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>44363.75775462963</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44259</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>44776.4441087963</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>44073</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>44384</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44870.4825462963</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>44378.27100694444</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>44650</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>44351</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
         <v>44449.61662037037</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>44211</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>44137</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>44223</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>44839.34592592593</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>44594.37494212963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>44629</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44494</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>44748.39954861111</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>44771.403125</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44183</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44593</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44378.26744212963</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44365</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>44881.46946759259</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44634</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44634</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>44418</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>44218</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44727</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>44796</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44075</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>44370.25283564815</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44657</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44805.72581018518</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44243.24046296296</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>44551.60501157407</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>44104.58186342593</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>44112</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44375</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>44250</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>44161</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44270.62047453703</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>44183</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>44299.65049768519</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>44612.64552083334</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>44407.33940972222</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>44300.5134375</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44160</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>44449</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>44593</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44092</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>44617.57709490741</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>44593</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44813.46402777778</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44363.75042824074</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44526.31395833333</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44225</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>44169</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>44089</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44054</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44207.56376157407</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44275.89116898148</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44376.47229166667</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>44376</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>44551</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44375.39068287037</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>44551</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>44508</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44246</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>44870.4822337963</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44578.49199074074</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>44445</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44407.35585648148</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>44407.35945601852</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>44587</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44785.35797453704</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45733.60050925926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45078</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44991.4569212963</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44222</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45554</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45488.44295138889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45050</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>45702.52855324074</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>45091.44322916667</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44816</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45762.40821759259</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45401.70074074074</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45149.52997685185</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45075</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45190</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45679</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>44951.40828703704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>44880.27605324074</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>44853</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>44881</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>44844</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>45744.33675925926</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>45758.65511574074</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45216</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45341.43773148148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45773</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45509.84324074074</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>45737.66959490741</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>45189</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45606.57449074074</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44376</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44348</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45043</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>45729.53114583333</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45054</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44418</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>45728.58208333333</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44586.39371527778</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45093.41260416667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45572.49996527778</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>44700.52403935185</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45072.49364583333</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>44419</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45510.39084490741</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45761.60565972222</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45713</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>45517.5049074074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45162</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>44865</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>44909.50149305556</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>44839</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>44889</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44866.62503472222</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>44866.6291550926</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>44755</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45085.55108796297</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45135</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>44867</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45308.45605324074</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45649.57708333333</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45649.58368055556</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>45649.63318287037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>45240.48289351852</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45055.32497685185</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>44785.36618055555</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45075</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45253</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45111.56173611111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>44270</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45342.93903935186</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>44827</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45761.7169212963</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45762.37043981482</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45775</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>45363.79693287037</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>45567</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>44295</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45426.64987268519</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45011</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45210</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45110</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45568</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45336</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45649.56231481482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45649.56582175926</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>45591.31592592593</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45434.42591435185</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>45635.46313657407</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45670.48837962963</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45028.64141203704</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>44869.44665509259</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45763</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>44811.50899305556</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45616.69401620371</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45078</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>44867</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45702.63752314815</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45429.49690972222</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>44307.41146990741</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45093</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>44236</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>44431</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>44431</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>44594</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45331.60153935185</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45188</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45757.40310185185</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>44890.45898148148</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45103.4578125</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45103.4828125</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45762.38353009259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>44874.3702662037</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45077</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>45376.57670138889</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45013.53428240741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45090.57193287037</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45440</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44868.38045138889</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45022</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44609.62754629629</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45149.53783564815</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45177</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>44882</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>44778.47969907407</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>45754.58804398148</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45056</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45149</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>44407.33692129629</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45561</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45469.49331018519</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>45205.32967592592</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>45478.55826388889</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>45210</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>45296</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45754.57903935185</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>44882</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45596.74167824074</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45721</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45392.56559027778</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45107</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45103.42912037037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>45359.64686342593</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>44825</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>45342.58582175926</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>45096</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>45103</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>45098</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44839</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45240.54020833333</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44910</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45575.40405092593</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44183</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45156.74657407407</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44903.63063657407</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>45279</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45313</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>45561</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45477.45034722222</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45761.36119212963</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>44368.48951388889</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>45407.58145833333</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>44973.51290509259</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>44973</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45770.36494212963</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>44056</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>45412</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27851,7 +27851,7 @@
         <v>44882</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>44368.47782407407</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>45069.42486111111</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45163.48395833333</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45373.4965625</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45369.51451388889</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>45394.64731481481</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>45356.37466435185</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>45446.57478009259</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>45368.71136574074</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>45369.51261574074</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45166.81506944444</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45321.30368055555</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45233</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28664,7 +28664,7 @@
         <v>44957</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>44957.56633101852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>45579</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44505</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45118.44516203704</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>44266.66663194444</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45121</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45280.75414351852</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45123.42461805556</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45756.64157407408</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45013.59971064814</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45560.65891203703</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45653.6771875</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>45603</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>45117.52946759259</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45644.49726851852</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>45096</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45342.58545138889</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45622.7463425926</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>44528.68445601852</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45084.52010416667</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45762.6184375</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45679</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>45551.45940972222</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45561.42905092592</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>44489</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45713</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45714.28113425926</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>45079.47167824074</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>44596.39430555556</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30374,7 +30374,7 @@
         <v>45649.55618055556</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>45649.59947916667</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45649.63702546297</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>44453</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45107.72561342592</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>44465.45304398148</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>45217.64325231482</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>45762.62880787037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>44953</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45341</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>44999</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>45666.41087962963</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45156.75122685185</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45475.72082175926</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45475.76681712963</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45181</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45104.47891203704</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45070</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>44277</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>44606.73197916667</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45601.6175</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>45449.73532407408</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45545.46103009259</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>45729.53497685185</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45476.37739583333</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>44915.64974537037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45489.67844907408</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>45545</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>44972</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>44908</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32089,7 +32089,7 @@
         <v>45155</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>45429.32715277778</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>45089.45716435185</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>45551.45708333333</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>44488</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44938.4812962963</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45587.39587962963</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44973.68172453704</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>45786.36038194445</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>45665.30042824074</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45785.85196759259</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45706.64979166666</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>45698.47010416666</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45547.5259375</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45572.50128472222</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>44914.5846875</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45547.44084490741</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44867.83456018518</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>45544.7580787037</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>44300.37375</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44315.61856481482</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>45230.60619212963</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45370</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44904</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45246.69150462963</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>45253</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45357.56929398148</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>45744.56760416667</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45442.44923611111</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>45260</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44959</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45517.57674768518</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45367.30908564815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45744.58425925926</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>44982.82561342593</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>45785.57039351852</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>45616.68453703704</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45616.69777777778</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>45664</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>45096</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>45673.35722222222</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45785.5658912037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>44928</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>45579</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>45301</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>45625</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>45474.54547453704</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45489</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45785.33315972222</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45169.62481481482</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>44580.39465277778</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>44544.63826388889</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>44333.68109953704</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>44959.60054398148</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>45079</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45758.47427083334</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>45750.40331018518</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45320.32636574074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44495</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44692</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>45561</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>45561</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>45786.35825231481</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>45113</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44917.52387731482</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45408.42273148148</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>45616.66118055556</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44992.53199074074</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45401.55627314815</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>45577.88273148148</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45785.87679398148</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>45786.3628125</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>45098</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45118</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>45534.67787037037</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>45131</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45763</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44873.78972222222</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45534.39119212963</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45773</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>45315</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45016.44748842593</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45791.46207175926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>45561.61627314815</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45145</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>45145.57739583333</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>45653</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44566</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>44593</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>45790.8237962963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45092.3945949074</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45792.46319444444</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45668.61670138889</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45792.46534722222</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45335</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>45791.45240740741</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>45222.46246527778</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37663,7 +37663,7 @@
         <v>45792.4578587963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>45792.46865740741</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>44973.87971064815</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>45197</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>45385</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>45603</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>44910</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>45035</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38129,7 +38129,7 @@
         <v>44973.28375</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38186,7 +38186,7 @@
         <v>44832.45126157408</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>45796.54754629629</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>45701.1425</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>45572.55528935185</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45372.34578703704</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>45218.41752314815</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>45169.63607638889</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45338.3546412037</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>44939.46715277778</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>45223</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>45230.60807870371</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>45367.31642361111</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45560.66090277778</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>45837.43159722222</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45837.45643518519</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>44645.61398148148</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>45761.54658564815</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>45478.47974537037</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>45727.54988425926</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>44867.83100694444</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>45727</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>45713.67922453704</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>44970.82792824074</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>45714.24815972222</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>45602</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>44966.65418981481</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44966.65623842592</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45702.6415625</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         <v>45191.43909722222</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>45664.89855324074</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45840.8866087963</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>44677</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>45373.43667824074</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45798.38493055556</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>45327</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45063</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>45596.73567129629</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>45764</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45764</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>45082</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>45095</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40672,7 +40672,7 @@
         <v>45737.66273148148</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         <v>45695.44407407408</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45191.39680555555</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>45733.27633101852</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40905,7 +40905,7 @@
         <v>44713.63434027778</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>44351</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>44657</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45415.32408564815</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45071</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>44594</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45586</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45439.56545138889</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45840.36429398148</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45049</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>44120</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41537,7 +41537,7 @@
         <v>45740.58935185185</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>44622</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>44825.37355324074</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>45070</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41765,7 +41765,7 @@
         <v>45367.29472222222</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>45224.64084490741</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45411.56006944444</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45177</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45637.55811342593</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45072.49809027778</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45842.47361111111</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>44713.6349537037</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45798.87049768519</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45121.62556712963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42340,7 +42340,7 @@
         <v>45121</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>44746.56648148148</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>44697</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>45841.34291666667</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>45664.88829861111</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>45762.3843287037</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45762.47326388889</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>45754.57761574074</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>45118</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>44209</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>44798.56335648148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>45307</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>45628</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45359.64494212963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43153,7 +43153,7 @@
         <v>45392.56177083333</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>45089</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>45196.41028935185</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>45629.52961805555</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43386,7 +43386,7 @@
         <v>44931.48902777778</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>44231.57006944445</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45106.66513888889</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>45561</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43624,7 +43624,7 @@
         <v>45561</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>44833.86636574074</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>45846.47327546297</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45846.46805555555</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45525.37091435185</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43909,7 +43909,7 @@
         <v>44690.55664351852</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>45754.58637731482</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45762.38605324074</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>45685.44299768518</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>44684.43402777778</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45615</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45805</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45182</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45720.48189814815</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45175</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45093</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44551,7 +44551,7 @@
         <v>45057</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>45057</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>44819</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44722,7 +44722,7 @@
         <v>45244</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>45849.47482638889</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
         <v>45849.46460648148</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44893,7 +44893,7 @@
         <v>45741.39699074074</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44950,7 +44950,7 @@
         <v>45022.47684027778</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>45681</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>45756.4618287037</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45126,7 +45126,7 @@
         <v>45211</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>44223</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45240,7 +45240,7 @@
         <v>44223</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>45187.45348379629</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45354,7 +45354,7 @@
         <v>45702.63559027778</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>45852.64087962963</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>44351.66695601852</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>44368.48412037037</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45587,7 +45587,7 @@
         <v>45253</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>45754.4484375</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>45210.43765046296</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45763,7 +45763,7 @@
         <v>45407.33482638889</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45820,7 +45820,7 @@
         <v>45475.70619212963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45877,7 +45877,7 @@
         <v>45239</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>44742</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45991,7 +45991,7 @@
         <v>44999.51451388889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46048,7 +46048,7 @@
         <v>45852.67128472222</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>45177</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46167,7 +46167,7 @@
         <v>44909</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>45175</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45177</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46343,7 +46343,7 @@
         <v>45198.49947916667</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46400,7 +46400,7 @@
         <v>44298.33628472222</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>45758.44347222222</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46514,7 +46514,7 @@
         <v>45810.50623842593</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>45211.43076388889</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         <v>45705.37840277778</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46690,7 +46690,7 @@
         <v>44333.63303240741</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>45757.42518518519</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>45225</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>44224</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>44340.37858796296</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>44749</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>45812.58846064815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>45812.59289351852</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>45832</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>44721</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>44743</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>45812.31928240741</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>45727.55368055555</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>45750.40939814815</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>45706.59305555555</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>45175.79483796296</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47607,7 +47607,7 @@
         <v>45119.35530092593</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47664,7 +47664,7 @@
         <v>44075</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>45813.61592592593</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>45813.61734953704</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>45734.48820601852</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45856.42729166667</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45856.43209490741</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>45414.88950231481</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45754.5805787037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45756.46728009259</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45744.34409722222</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48259,7 +48259,7 @@
         <v>44909.51041666666</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>45484.50256944444</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>45856.4249537037</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>45244</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48492,7 +48492,7 @@
         <v>45813.61375</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>44841</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48611,7 +48611,7 @@
         <v>45817.49847222222</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48668,7 +48668,7 @@
         <v>45818.33222222222</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>45775.61712962963</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48782,7 +48782,7 @@
         <v>44803</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48839,7 +48839,7 @@
         <v>44693.40193287037</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48901,7 +48901,7 @@
         <v>45448.40923611111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48958,7 +48958,7 @@
         <v>45859.46207175926</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>44739</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>45409.28716435185</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>44746.52041666667</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49186,7 +49186,7 @@
         <v>45817.4940625</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>45694.35719907407</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49300,7 +49300,7 @@
         <v>44308</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>44302.60905092592</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49414,7 +49414,7 @@
         <v>45254.55388888889</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49471,7 +49471,7 @@
         <v>45330</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49528,7 +49528,7 @@
         <v>45820.4099537037</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>45820.40359953704</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>45819</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>44497</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49766,7 +49766,7 @@
         <v>45818</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>45818</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>44974.39552083334</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49937,7 +49937,7 @@
         <v>45022</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49994,7 +49994,7 @@
         <v>45820.40600694445</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50056,7 +50056,7 @@
         <v>45820.43005787037</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>45379</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50170,7 +50170,7 @@
         <v>45862.62265046296</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>45366.36186342593</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>45189</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45862.61716435185</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45820</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>44335</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>45653.66523148148</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50574,7 +50574,7 @@
         <v>45154.46340277778</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45863.79833333333</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45824.57248842593</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50755,7 +50755,7 @@
         <v>45217.49613425926</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50812,7 +50812,7 @@
         <v>44390.44760416666</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50874,7 +50874,7 @@
         <v>44917</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50936,7 +50936,7 @@
         <v>44368</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45821.48188657407</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45824.47503472222</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45863.78525462963</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45863.79356481481</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45730.29663194445</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45824.63803240741</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45478</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>44959</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>45111.3095949074</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45273.43420138889</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>44819</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>45601</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51682,7 +51682,7 @@
         <v>45301.31474537037</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>45301.32008101852</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>44390</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>45763.38137731481</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51915,7 +51915,7 @@
         <v>45763</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>45824.56317129629</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>45327.3969212963</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52091,7 +52091,7 @@
         <v>45825.38628472222</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52148,7 +52148,7 @@
         <v>45231</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52205,7 +52205,7 @@
         <v>44056</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>44369</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>44386.57552083334</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52376,7 +52376,7 @@
         <v>45687.58510416667</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52433,7 +52433,7 @@
         <v>44818</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52490,7 +52490,7 @@
         <v>45744.35152777778</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52547,7 +52547,7 @@
         <v>45369.55871527778</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52604,7 +52604,7 @@
         <v>45092.3869675926</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52666,7 +52666,7 @@
         <v>45762.406875</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>45762.41121527777</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52790,7 +52790,7 @@
         <v>45346.58555555555</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52847,7 +52847,7 @@
         <v>45628</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52904,7 +52904,7 @@
         <v>44945.47278935185</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52961,7 +52961,7 @@
         <v>44494.39315972223</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>45728.57760416667</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>45775.59509259259</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>45728.71716435185</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>45831.28561342593</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53251,7 +53251,7 @@
         <v>45616.70280092592</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53308,7 +53308,7 @@
         <v>45831</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53365,7 +53365,7 @@
         <v>45278</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53422,7 +53422,7 @@
         <v>45090.53722222222</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53479,7 +53479,7 @@
         <v>45610.49638888889</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53536,7 +53536,7 @@
         <v>44756</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53598,7 +53598,7 @@
         <v>45091.44966435185</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53655,7 +53655,7 @@
         <v>44868</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53712,7 +53712,7 @@
         <v>45728.71802083333</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>45832</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53826,7 +53826,7 @@
         <v>44621</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53883,7 +53883,7 @@
         <v>45873.50734953704</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53945,7 +53945,7 @@
         <v>44936.7375925926</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54002,7 +54002,7 @@
         <v>45636.68237268519</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>45833.62319444444</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>45484.50075231482</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>45834.48055555556</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>44865.32546296297</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>45772.56983796296</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>45834.42243055555</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>45834.48547453704</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54458,7 +54458,7 @@
         <v>44985.4822337963</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54515,7 +54515,7 @@
         <v>45833.63016203704</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>45834.49290509259</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>44084.64604166667</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45463</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45834.42037037037</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54800,7 +54800,7 @@
         <v>45534.65803240741</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54857,7 +54857,7 @@
         <v>45394.66318287037</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45090.50210648148</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45342.93295138889</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55033,7 +55033,7 @@
         <v>45400.70824074074</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55090,7 +55090,7 @@
         <v>45552.43833333333</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55147,7 +55147,7 @@
         <v>44382</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55204,7 +55204,7 @@
         <v>44909</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55261,7 +55261,7 @@
         <v>44973.8353125</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>44364</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55375,7 +55375,7 @@
         <v>44243</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>44904</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55489,7 +55489,7 @@
         <v>45174.32129629629</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>45335</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55608,7 +55608,7 @@
         <v>44992.52833333334</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55665,7 +55665,7 @@
         <v>44462</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55722,7 +55722,7 @@
         <v>44463.49251157408</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>44579.36934027778</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55836,7 +55836,7 @@
         <v>44928.58678240741</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55893,7 +55893,7 @@
         <v>44594.37378472222</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>44933.42714120371</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>44977</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56064,7 +56064,7 @@
         <v>44977.54047453704</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>44881.47697916667</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56178,7 +56178,7 @@
         <v>45188</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56235,7 +56235,7 @@
         <v>45244</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56292,7 +56292,7 @@
         <v>45072</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56349,7 +56349,7 @@
         <v>45371.47248842593</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>44914.47359953704</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56463,7 +56463,7 @@
         <v>44083</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56525,7 +56525,7 @@
         <v>44497.23909722222</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56582,7 +56582,7 @@
         <v>44949.39141203704</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56639,7 +56639,7 @@
         <v>45512.32738425926</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>45260</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>45188.35988425926</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>44909.49190972222</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56867,7 +56867,7 @@
         <v>44798</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45385.47306712963</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56981,7 +56981,7 @@
         <v>45056.72038194445</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57038,7 +57038,7 @@
         <v>45606.57791666667</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>45710.35591435185</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57152,7 +57152,7 @@
         <v>45075</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57209,7 +57209,7 @@
         <v>45603</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57266,7 +57266,7 @@
         <v>44900.47381944444</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57323,7 +57323,7 @@
         <v>45213.83515046296</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>44904</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>44984</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45082.42459490741</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57551,7 +57551,7 @@
         <v>44909.51342592593</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57608,7 +57608,7 @@
         <v>45091.44643518519</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57665,7 +57665,7 @@
         <v>45648</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57722,7 +57722,7 @@
         <v>44494.38530092593</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57779,7 +57779,7 @@
         <v>44463.49472222223</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57836,7 +57836,7 @@
         <v>45392.59135416667</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57893,7 +57893,7 @@
         <v>45063.42767361111</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>44798</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>45611.48372685185</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58069,7 +58069,7 @@
         <v>45069.67789351852</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58126,7 +58126,7 @@
         <v>44853.58972222222</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58183,7 +58183,7 @@
         <v>45470.66217592593</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>45021</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>45079</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58354,7 +58354,7 @@
         <v>45111</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>45668.48770833333</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58468,7 +58468,7 @@
         <v>45668.49403935186</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58525,7 +58525,7 @@
         <v>44713.63319444445</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58582,7 +58582,7 @@
         <v>44908</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58639,7 +58639,7 @@
         <v>44974.3628125</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58696,7 +58696,7 @@
         <v>45079.49798611111</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58753,7 +58753,7 @@
         <v>45208</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58810,7 +58810,7 @@
         <v>45078</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58867,7 +58867,7 @@
         <v>45525.33855324074</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58924,7 +58924,7 @@
         <v>45590.48756944444</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58981,7 +58981,7 @@
         <v>45175.80216435185</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59038,7 +59038,7 @@
         <v>44973.68408564815</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -567,7 +567,7 @@
         <v>44460.70982638889</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44606</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45810.50783564815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45616</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45189</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>44490</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44370</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>44112</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45735.34555555556</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45352.45320601852</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44867</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>44347</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>44145</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44266</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>45174.32886574074</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45428.42564814815</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>44937</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45652.74018518518</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45447</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45075</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>44120</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45730.63277777778</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45695.93653935185</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45358.44835648148</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>44785.43395833333</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45093.3646875</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>45093.3703587963</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>45853</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45832</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45222</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44175</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44375</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>44602</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45695.93015046296</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45615.62699074074</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>45215</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>44980</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>45316</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>45721.65631944445</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>45496.6761574074</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45096</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45541.51222222222</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>45042</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44909</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44504.50979166666</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45594</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44120</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>45701.45335648148</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45103</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>45449.38423611111</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45110</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>44448.31037037037</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>44648</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>45581.56951388889</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>44656</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>45621.64417824074</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>45840.8834375</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45621.63548611111</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45846.4975</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>45621.64115740741</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45850.60619212963</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>45754.48619212963</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>45307</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>44365</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>45863.39380787037</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44917</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>45596.52869212963</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>45604.50471064815</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>44966.64579861111</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44917</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44073</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44057</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44060</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44059</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44064</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44074</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44053.41489583333</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>44261</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>44347</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44179</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44073.7496875</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>44130</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>44378</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44110.43048611111</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44120</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44224</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44183</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>44230</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44300.3625</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44385.40346064815</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>44123</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>44208</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44491</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>44120</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44278</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44407.34103009259</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>44363.76037037037</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>44267.32773148148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>44201</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>44462</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44407.35815972222</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>44379</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>44630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>44089</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>44418.56681712963</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>44320</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44236</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44225</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44342.65030092592</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44297</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>44194</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44365</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44071</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>44363.75403935185</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44889.52459490741</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>44302</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>44691</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>44138</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>44474</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>44137.79510416667</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>44412</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>44859</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>44102</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44164</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44861</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44475</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44246</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44365</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44473.51576388889</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>44245</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44362</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44581</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>44449.57666666667</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44656</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>44587</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>44844</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>44816</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44571.48392361111</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>44612</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>44152</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44645.61962962963</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44187</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44088</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>44201</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>44565</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>44130</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>44256</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>44365</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44312.52064814815</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44088</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>44593.58975694444</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44131</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>44831.51668981482</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>44840</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44783</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44179</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>44365</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>44375.42613425926</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>44369</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44084</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44566</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>44060</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44328</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44684</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44347</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44365</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>44306</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>44806.30436342592</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>44315.67481481482</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>44364.69368055555</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>44493.7688425926</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>44488.93328703703</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>44362</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>44833.85800925926</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>44217.63880787037</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44083</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>44078</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44386.50282407407</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>44468.38931712963</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>44587</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>44624.4716087963</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>44593</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>44294.69576388889</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>44449.61309027778</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44449</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>44169</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>44172</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>44419</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>44321.32876157408</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44295.56511574074</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44851</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>44340.37452546296</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>44136</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>44284</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>44363.75775462963</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44259</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>44776.4441087963</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>44073</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>44384</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44870.4825462963</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>44378.27100694444</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>44650</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>44351</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
         <v>44449.61662037037</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>44211</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>44137</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>44223</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>44839.34592592593</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>44594.37494212963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>44629</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44494</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>44748.39954861111</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>44771.403125</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44183</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44593</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44378.26744212963</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44365</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>44881.46946759259</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44634</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44634</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>44418</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>44218</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44727</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>44796</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44075</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>44370.25283564815</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44657</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44805.72581018518</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44243.24046296296</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>44551.60501157407</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>44104.58186342593</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>44112</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44375</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>44250</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>44161</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44270.62047453703</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>44183</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>44299.65049768519</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>44612.64552083334</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>44407.33940972222</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>44300.5134375</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44160</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>44449</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>44593</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44092</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>44617.57709490741</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>44593</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44813.46402777778</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44363.75042824074</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44526.31395833333</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44225</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>44169</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>44089</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44054</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44207.56376157407</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44275.89116898148</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44376.47229166667</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>44376</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>44551</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44375.39068287037</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>44551</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>44508</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44246</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>44870.4822337963</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44578.49199074074</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>44445</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44407.35585648148</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>44407.35945601852</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>44587</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44785.35797453704</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45733.60050925926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45078</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44991.4569212963</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>44222</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45554</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45488.44295138889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45050</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>45702.52855324074</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>45091.44322916667</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44816</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45762.40821759259</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45401.70074074074</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45149.52997685185</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45075</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45190</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45679</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>44951.40828703704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>44880.27605324074</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>44853</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>44881</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>44844</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>45744.33675925926</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>45758.65511574074</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45216</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45341.43773148148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45773</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45509.84324074074</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>45737.66959490741</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>45189</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45606.57449074074</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44376</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44348</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45043</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>45729.53114583333</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45054</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44418</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>45728.58208333333</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44586.39371527778</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45093.41260416667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45572.49996527778</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>44700.52403935185</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45072.49364583333</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>44419</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45510.39084490741</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45761.60565972222</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45713</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>45517.5049074074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45162</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>44865</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>44909.50149305556</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>44839</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>44889</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44866.62503472222</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>44866.6291550926</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>44755</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45085.55108796297</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45135</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>44867</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45308.45605324074</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45649.57708333333</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45649.58368055556</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>45649.63318287037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>45240.48289351852</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45055.32497685185</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>44785.36618055555</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45075</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45253</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45111.56173611111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>44270</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45342.93903935186</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>44827</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45761.7169212963</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45762.37043981482</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45775</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>45363.79693287037</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>45567</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>44295</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45426.64987268519</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45011</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45210</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45110</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45568</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45336</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45649.56231481482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45649.56582175926</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>45591.31592592593</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45434.42591435185</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>45635.46313657407</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45670.48837962963</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45028.64141203704</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>44869.44665509259</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45763</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>44811.50899305556</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45616.69401620371</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45078</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>44867</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45702.63752314815</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45429.49690972222</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>44307.41146990741</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45093</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>44236</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>44431</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>44431</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>44594</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45331.60153935185</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45188</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45757.40310185185</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>44890.45898148148</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45103.4578125</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45103.4828125</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45762.38353009259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>44874.3702662037</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45077</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>45376.57670138889</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45013.53428240741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45090.57193287037</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45440</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44868.38045138889</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45022</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44609.62754629629</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45149.53783564815</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45177</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>44882</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>44778.47969907407</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>45754.58804398148</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45056</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45149</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>44407.33692129629</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45561</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45469.49331018519</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>45205.32967592592</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>45478.55826388889</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>45210</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>45296</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45754.57903935185</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>44882</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45596.74167824074</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45721</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45392.56559027778</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45107</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45103.42912037037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>45359.64686342593</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>44825</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>45342.58582175926</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>45096</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>45103</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>45098</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44839</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45240.54020833333</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44910</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45575.40405092593</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44183</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45156.74657407407</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44903.63063657407</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>45279</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45313</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>45561</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45477.45034722222</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45761.36119212963</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>44368.48951388889</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>45407.58145833333</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>44973.51290509259</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>44973</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45770.36494212963</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>44056</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>45412</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27851,7 +27851,7 @@
         <v>44882</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>44368.47782407407</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>45069.42486111111</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45163.48395833333</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45373.4965625</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45369.51451388889</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>45394.64731481481</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>45356.37466435185</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>45446.57478009259</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>45368.71136574074</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>45369.51261574074</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45166.81506944444</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45321.30368055555</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45233</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28664,7 +28664,7 @@
         <v>44957</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>44957.56633101852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>45579</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44505</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45118.44516203704</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>44266.66663194444</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45121</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45280.75414351852</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45123.42461805556</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45756.64157407408</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45013.59971064814</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45560.65891203703</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45653.6771875</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>45603</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>45117.52946759259</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45644.49726851852</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>45096</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45342.58545138889</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45622.7463425926</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>44528.68445601852</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45084.52010416667</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45762.6184375</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45679</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>45551.45940972222</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45561.42905092592</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>44489</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45713</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45714.28113425926</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>45079.47167824074</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>44596.39430555556</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30374,7 +30374,7 @@
         <v>45649.55618055556</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>45649.59947916667</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45649.63702546297</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>44453</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45107.72561342592</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>44465.45304398148</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>45217.64325231482</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>45762.62880787037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>44953</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45341</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>44999</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>45666.41087962963</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45156.75122685185</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45475.72082175926</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45475.76681712963</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45181</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45104.47891203704</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45070</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>44277</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>44606.73197916667</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45601.6175</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>45449.73532407408</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45545.46103009259</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>45729.53497685185</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45476.37739583333</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>44915.64974537037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45489.67844907408</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>45545</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>44972</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>44908</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32089,7 +32089,7 @@
         <v>45155</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>45429.32715277778</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>45089.45716435185</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>45551.45708333333</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>44488</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44938.4812962963</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45587.39587962963</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44973.68172453704</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>45786.36038194445</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>45665.30042824074</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45785.85196759259</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45706.64979166666</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>45698.47010416666</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45547.5259375</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45572.50128472222</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>44914.5846875</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45547.44084490741</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44867.83456018518</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>45544.7580787037</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>44300.37375</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44315.61856481482</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>45230.60619212963</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45370</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44904</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45246.69150462963</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>45253</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45357.56929398148</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>45744.56760416667</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45442.44923611111</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>45260</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44959</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45517.57674768518</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45367.30908564815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45744.58425925926</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>44982.82561342593</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>45785.57039351852</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>45616.68453703704</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45616.69777777778</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>45664</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>45096</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>45673.35722222222</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45785.5658912037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>44928</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>45579</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>45301</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>45625</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>45474.54547453704</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45489</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45785.33315972222</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45169.62481481482</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>44580.39465277778</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>44544.63826388889</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>44333.68109953704</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>44959.60054398148</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>45079</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45758.47427083334</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>45750.40331018518</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45320.32636574074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44495</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44692</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>45561</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>45561</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>45786.35825231481</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>45113</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44917.52387731482</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45408.42273148148</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>45616.66118055556</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44992.53199074074</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45401.55627314815</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>45577.88273148148</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45785.87679398148</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>45786.3628125</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>45098</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45118</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>45534.67787037037</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>45131</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45763</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44873.78972222222</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45534.39119212963</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45773</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>45315</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45016.44748842593</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45791.46207175926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>45561.61627314815</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45145</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>45145.57739583333</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>45653</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44566</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>44593</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>45790.8237962963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45092.3945949074</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45792.46319444444</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45668.61670138889</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45792.46534722222</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45335</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>45791.45240740741</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>45222.46246527778</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37663,7 +37663,7 @@
         <v>45792.4578587963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>45792.46865740741</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>44973.87971064815</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>45197</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>45385</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>45603</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>44910</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>45035</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38129,7 +38129,7 @@
         <v>44973.28375</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38186,7 +38186,7 @@
         <v>44832.45126157408</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>45796.54754629629</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>45701.1425</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>45572.55528935185</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45372.34578703704</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>45218.41752314815</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>45037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>45169.63607638889</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45338.3546412037</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>44939.46715277778</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>45223</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>45230.60807870371</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>45367.31642361111</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45560.66090277778</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>45837.43159722222</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45837.45643518519</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>44645.61398148148</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>45761.54658564815</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>45478.47974537037</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>45727.54988425926</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>44867.83100694444</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>45727</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>45713.67922453704</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>44970.82792824074</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>45714.24815972222</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>45602</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>44966.65418981481</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44966.65623842592</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45702.6415625</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         <v>45191.43909722222</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>45664.89855324074</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45840.8866087963</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>44677</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>45373.43667824074</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45798.38493055556</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>45327</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45063</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>45596.73567129629</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>45764</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45764</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>45082</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>45095</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40672,7 +40672,7 @@
         <v>45737.66273148148</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         <v>45695.44407407408</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45191.39680555555</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>45733.27633101852</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40905,7 +40905,7 @@
         <v>44713.63434027778</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>44351</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>44657</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45415.32408564815</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45071</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>44594</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45586</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45439.56545138889</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45840.36429398148</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45049</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>44120</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41537,7 +41537,7 @@
         <v>45740.58935185185</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>44622</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>44825.37355324074</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>45070</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41765,7 +41765,7 @@
         <v>45367.29472222222</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>45224.64084490741</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45411.56006944444</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45177</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45637.55811342593</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45072.49809027778</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45842.47361111111</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>44713.6349537037</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45798.87049768519</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45121.62556712963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42340,7 +42340,7 @@
         <v>45121</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>44746.56648148148</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>44697</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>45841.34291666667</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>45664.88829861111</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>45762.3843287037</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45762.47326388889</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>45754.57761574074</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>45118</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>44209</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>44798.56335648148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>45307</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>45628</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45359.64494212963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43153,7 +43153,7 @@
         <v>45392.56177083333</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>45089</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>45196.41028935185</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>45629.52961805555</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43386,7 +43386,7 @@
         <v>44931.48902777778</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>44231.57006944445</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45106.66513888889</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>45561</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43624,7 +43624,7 @@
         <v>45561</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>44833.86636574074</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>45846.47327546297</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45846.46805555555</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>45525.37091435185</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43909,7 +43909,7 @@
         <v>44690.55664351852</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>45754.58637731482</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45762.38605324074</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>45685.44299768518</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>44684.43402777778</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45615</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45805</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45182</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45720.48189814815</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>45175</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45093</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44551,7 +44551,7 @@
         <v>45057</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>45057</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>44819</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44722,7 +44722,7 @@
         <v>45244</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>45849.47482638889</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
         <v>45849.46460648148</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44893,7 +44893,7 @@
         <v>45741.39699074074</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44950,7 +44950,7 @@
         <v>45022.47684027778</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>45681</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>45756.4618287037</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45126,7 +45126,7 @@
         <v>45211</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>44223</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45240,7 +45240,7 @@
         <v>44223</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>45187.45348379629</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45354,7 +45354,7 @@
         <v>45702.63559027778</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>45852.64087962963</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>44351.66695601852</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>44368.48412037037</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45587,7 +45587,7 @@
         <v>45253</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>45754.4484375</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>45210.43765046296</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45763,7 +45763,7 @@
         <v>45407.33482638889</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45820,7 +45820,7 @@
         <v>45475.70619212963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45877,7 +45877,7 @@
         <v>45239</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>44742</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45991,7 +45991,7 @@
         <v>44999.51451388889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46048,7 +46048,7 @@
         <v>45852.67128472222</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>45177</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46167,7 +46167,7 @@
         <v>44909</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>45175</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45177</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46343,7 +46343,7 @@
         <v>45198.49947916667</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46400,7 +46400,7 @@
         <v>44298.33628472222</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>45758.44347222222</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46514,7 +46514,7 @@
         <v>45810.50623842593</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>45211.43076388889</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         <v>45705.37840277778</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46690,7 +46690,7 @@
         <v>44333.63303240741</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>45757.42518518519</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>45225</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>44224</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>44340.37858796296</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>44749</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>45812.58846064815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>45812.59289351852</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>45832</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>44721</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>44743</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>45812.31928240741</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>45727.55368055555</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>45750.40939814815</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>45706.59305555555</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>45175.79483796296</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47607,7 +47607,7 @@
         <v>45119.35530092593</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47664,7 +47664,7 @@
         <v>44075</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>45813.61592592593</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>45813.61734953704</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>45734.48820601852</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45856.42729166667</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45856.43209490741</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>45414.88950231481</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45754.5805787037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45756.46728009259</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45744.34409722222</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48259,7 +48259,7 @@
         <v>44909.51041666666</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>45484.50256944444</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>45856.4249537037</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>45244</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48492,7 +48492,7 @@
         <v>45813.61375</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>44841</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48611,7 +48611,7 @@
         <v>45817.49847222222</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48668,7 +48668,7 @@
         <v>45818.33222222222</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>45775.61712962963</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48782,7 +48782,7 @@
         <v>44803</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48839,7 +48839,7 @@
         <v>44693.40193287037</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48901,7 +48901,7 @@
         <v>45448.40923611111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48958,7 +48958,7 @@
         <v>45859.46207175926</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>44739</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>45409.28716435185</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>44746.52041666667</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49186,7 +49186,7 @@
         <v>45817.4940625</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>45694.35719907407</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49300,7 +49300,7 @@
         <v>44308</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>44302.60905092592</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49414,7 +49414,7 @@
         <v>45254.55388888889</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49471,7 +49471,7 @@
         <v>45330</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49528,7 +49528,7 @@
         <v>45820.4099537037</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>45820.40359953704</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>45819</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>44497</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49766,7 +49766,7 @@
         <v>45818</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>45818</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>44974.39552083334</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49937,7 +49937,7 @@
         <v>45022</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49994,7 +49994,7 @@
         <v>45820.40600694445</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50056,7 +50056,7 @@
         <v>45820.43005787037</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>45379</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50170,7 +50170,7 @@
         <v>45862.62265046296</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>45366.36186342593</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>45189</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45862.61716435185</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45820</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>44335</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>45653.66523148148</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50574,7 +50574,7 @@
         <v>45154.46340277778</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45863.79833333333</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45824.57248842593</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50755,7 +50755,7 @@
         <v>45217.49613425926</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50812,7 +50812,7 @@
         <v>44390.44760416666</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50874,7 +50874,7 @@
         <v>44917</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50936,7 +50936,7 @@
         <v>44368</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45821.48188657407</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45824.47503472222</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45863.78525462963</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45863.79356481481</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45730.29663194445</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45824.63803240741</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45478</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>44959</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>45111.3095949074</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45273.43420138889</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>44819</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>45601</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51682,7 +51682,7 @@
         <v>45301.31474537037</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>45301.32008101852</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>44390</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>45763.38137731481</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51915,7 +51915,7 @@
         <v>45763</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>45824.56317129629</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>45327.3969212963</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52091,7 +52091,7 @@
         <v>45825.38628472222</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52148,7 +52148,7 @@
         <v>45231</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52205,7 +52205,7 @@
         <v>44056</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>44369</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>44386.57552083334</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52376,7 +52376,7 @@
         <v>45687.58510416667</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52433,7 +52433,7 @@
         <v>44818</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52490,7 +52490,7 @@
         <v>45744.35152777778</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52547,7 +52547,7 @@
         <v>45369.55871527778</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52604,7 +52604,7 @@
         <v>45092.3869675926</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52666,7 +52666,7 @@
         <v>45762.406875</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>45762.41121527777</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52790,7 +52790,7 @@
         <v>45346.58555555555</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52847,7 +52847,7 @@
         <v>45628</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52904,7 +52904,7 @@
         <v>44945.47278935185</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52961,7 +52961,7 @@
         <v>44494.39315972223</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>45728.57760416667</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>45775.59509259259</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>45728.71716435185</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>45831.28561342593</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53251,7 +53251,7 @@
         <v>45616.70280092592</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53308,7 +53308,7 @@
         <v>45831</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53365,7 +53365,7 @@
         <v>45278</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53422,7 +53422,7 @@
         <v>45090.53722222222</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53479,7 +53479,7 @@
         <v>45610.49638888889</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53536,7 +53536,7 @@
         <v>44756</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53598,7 +53598,7 @@
         <v>45091.44966435185</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53655,7 +53655,7 @@
         <v>44868</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53712,7 +53712,7 @@
         <v>45728.71802083333</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>45832</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53826,7 +53826,7 @@
         <v>44621</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53883,7 +53883,7 @@
         <v>45873.50734953704</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53945,7 +53945,7 @@
         <v>44936.7375925926</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54002,7 +54002,7 @@
         <v>45636.68237268519</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>45833.62319444444</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>45484.50075231482</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>45834.48055555556</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>44865.32546296297</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>45772.56983796296</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>45834.42243055555</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>45834.48547453704</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54458,7 +54458,7 @@
         <v>44985.4822337963</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54515,7 +54515,7 @@
         <v>45833.63016203704</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>45834.49290509259</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>44084.64604166667</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45463</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45834.42037037037</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54800,7 +54800,7 @@
         <v>45534.65803240741</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54857,7 +54857,7 @@
         <v>45394.66318287037</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45090.50210648148</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45342.93295138889</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55033,7 +55033,7 @@
         <v>45400.70824074074</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55090,7 +55090,7 @@
         <v>45552.43833333333</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55147,7 +55147,7 @@
         <v>44382</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55204,7 +55204,7 @@
         <v>44909</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55261,7 +55261,7 @@
         <v>44973.8353125</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>44364</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55375,7 +55375,7 @@
         <v>44243</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>44904</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55489,7 +55489,7 @@
         <v>45174.32129629629</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>45335</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55608,7 +55608,7 @@
         <v>44992.52833333334</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55665,7 +55665,7 @@
         <v>44462</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55722,7 +55722,7 @@
         <v>44463.49251157408</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>44579.36934027778</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55836,7 +55836,7 @@
         <v>44928.58678240741</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55893,7 +55893,7 @@
         <v>44594.37378472222</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>44933.42714120371</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>44977</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56064,7 +56064,7 @@
         <v>44977.54047453704</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>44881.47697916667</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56178,7 +56178,7 @@
         <v>45188</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56235,7 +56235,7 @@
         <v>45244</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56292,7 +56292,7 @@
         <v>45072</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56349,7 +56349,7 @@
         <v>45371.47248842593</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>44914.47359953704</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56463,7 +56463,7 @@
         <v>44083</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56525,7 +56525,7 @@
         <v>44497.23909722222</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56582,7 +56582,7 @@
         <v>44949.39141203704</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56639,7 +56639,7 @@
         <v>45512.32738425926</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>45260</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>45188.35988425926</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>44909.49190972222</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56867,7 +56867,7 @@
         <v>44798</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45385.47306712963</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56981,7 +56981,7 @@
         <v>45056.72038194445</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57038,7 +57038,7 @@
         <v>45606.57791666667</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>45710.35591435185</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57152,7 +57152,7 @@
         <v>45075</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57209,7 +57209,7 @@
         <v>45603</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57266,7 +57266,7 @@
         <v>44900.47381944444</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57323,7 +57323,7 @@
         <v>45213.83515046296</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>44904</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>44984</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45082.42459490741</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57551,7 +57551,7 @@
         <v>44909.51342592593</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57608,7 +57608,7 @@
         <v>45091.44643518519</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57665,7 +57665,7 @@
         <v>45648</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57722,7 +57722,7 @@
         <v>44494.38530092593</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57779,7 +57779,7 @@
         <v>44463.49472222223</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57836,7 +57836,7 @@
         <v>45392.59135416667</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57893,7 +57893,7 @@
         <v>45063.42767361111</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>44798</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>45611.48372685185</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58069,7 +58069,7 @@
         <v>45069.67789351852</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58126,7 +58126,7 @@
         <v>44853.58972222222</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58183,7 +58183,7 @@
         <v>45470.66217592593</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>45021</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>45079</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58354,7 +58354,7 @@
         <v>45111</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>45668.48770833333</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58468,7 +58468,7 @@
         <v>45668.49403935186</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58525,7 +58525,7 @@
         <v>44713.63319444445</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58582,7 +58582,7 @@
         <v>44908</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58639,7 +58639,7 @@
         <v>44974.3628125</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58696,7 +58696,7 @@
         <v>45079.49798611111</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58753,7 +58753,7 @@
         <v>45208</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58810,7 +58810,7 @@
         <v>45078</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58867,7 +58867,7 @@
         <v>45525.33855324074</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58924,7 +58924,7 @@
         <v>45590.48756944444</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58981,7 +58981,7 @@
         <v>45175.80216435185</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59038,7 +59038,7 @@
         <v>44973.68408564815</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -567,7 +567,7 @@
         <v>44460.70982638889</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44606</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45810.50783564815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45616</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45189</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>44490</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44370</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>45735.34555555556</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>44112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45352.45320601852</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44867</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>44347</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>44145</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44266</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>45652.74018518518</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45174.32886574074</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>45428.42564814815</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>45447</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>45730.63277777778</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>45695.93653935185</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45358.44835648148</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45853</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>45832</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>45075</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44120</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>44785.43395833333</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45093.3646875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>45093.3703587963</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45222</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>44937</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44175</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44375</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>44602</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45721.65631944445</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45215</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>45541.51222222222</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45096</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>44909</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>44504.50979166666</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>45594</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>45701.45335648148</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>44648</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>45846.4975</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>45621.64417824074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>45316</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>45621.64115740741</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>45850.60619212963</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45042</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45754.48619212963</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45863.39380787037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>44120</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45103</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45307</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>45449.38423611111</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>45110</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45873</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44448.31037037037</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>45840.8834375</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44917</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>45581.56951388889</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44656</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45621.63548611111</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>45596.52869212963</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45604.50471064815</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44966.64579861111</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>44917</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44365</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>45695.93015046296</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>45615.62699074074</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>44980</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44073</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44059</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44060</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44064</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44074</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44261</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44347</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44073.7496875</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>44378</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44179</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44130</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44110.43048611111</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44120</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>44183</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>44224</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>44230</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44272</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44300.3625</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44385.40346064815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>44123</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>44208</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>44491</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>44120</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>44278</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>44363.76037037037</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>44267.32773148148</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44407.34103009259</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>44462</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44201</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44379</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44407.35815972222</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44630</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>44418.56681712963</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44089</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44320</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44236</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44225</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44342.65030092592</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44297</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44365</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44194</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>44071</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44363.75403935185</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44889.52459490741</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44302</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>44691</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>44138</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44474</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44137.79510416667</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44412</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44859</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44102</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44164</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44861</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44475</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44246</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>44365</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44473.51576388889</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44362</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44245</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>44581</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>44587</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44656</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>44449.57666666667</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44844</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>44816</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>44571.48392361111</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>44612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44152</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>44645.61962962963</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>44187</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>44088</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44088</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>44201</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>44130</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>44565</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44256</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>44365</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>44312.52064814815</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44593.58975694444</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>44131</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>44831.51668981482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44840</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>44783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44179</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44365</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>44375.42613425926</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>44369</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44566</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>44084</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44060</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>44684</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>44328</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>44347</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44365</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>44306</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>44315.67481481482</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>44806.30436342592</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>44364.69368055555</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>44493.7688425926</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>44488.93328703703</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44362</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>44833.85800925926</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>44217.63880787037</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>44083</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>44078</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>44386.50282407407</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>44468.38931712963</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44587</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>44624.4716087963</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>44593</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>44294.69576388889</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>44449.61309027778</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44449</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>44169</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>44172</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>44419</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>44321.32876157408</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>44295.56511574074</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>44340.37452546296</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>44284</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>44363.75775462963</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>44259</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>44776.4441087963</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>44870.4825462963</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>44351</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>44594.37494212963</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>44629</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>44494</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44211</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>44137</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44223</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>44839.34592592593</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44748.39954861111</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44771.403125</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>44593</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>44378.26744212963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>44881.46946759259</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>44183</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>44365</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>44418</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44634</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>44634</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>44796</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>44075</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44370.25283564815</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44727</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44218</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>44657</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>44551.60501157407</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>44104.58186342593</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44805.72581018518</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>44112</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>44243.24046296296</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>44375</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>44161</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>44250</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>44270.62047453703</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44183</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44612.64552083334</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>44299.65049768519</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>44407.33940972222</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>44300.5134375</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44593</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>44449</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>44160</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44092</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>44617.57709490741</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>44813.46402777778</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44593</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>44363.75042824074</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>44526.31395833333</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>44169</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>44225</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>44207.56376157407</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44089</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>44376.47229166667</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>44551</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44508</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>44246</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>44375.39068287037</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>44376</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>44551</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44578.49199074074</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44445</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44407.35585648148</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44407.35945601852</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44785.35797453704</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>44870.4822337963</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>44587</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44136</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>44073</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>44853</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44378.27100694444</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>44384</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44851</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44650</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44222</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44839</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45702.52855324074</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44866.62503472222</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44866.6291550926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45091.44322916667</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>44755</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>44867</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45190</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>45075</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45253</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>44270</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45579</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45342.93903935186</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>44827</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45216</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45341.43773148148</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>45363.79693287037</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>44505</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45773</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45118.44516203704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>44266.66663194444</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>44295</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>44449.61662037037</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>45121</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>45280.75414351852</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45123.42461805556</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45336</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45434.42591435185</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>44376</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>45762.6184375</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>44348</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45043</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45054</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45679</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45117.52946759259</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>45078</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45702.63752314815</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>44307.41146990741</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>45622.7463425926</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>45093</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45084.52010416667</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45572.49996527778</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45713</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20584,7 +20584,7 @@
         <v>45714.28113425926</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>45649.55618055556</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45551.45940972222</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45649.59947916667</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>45649.63702546297</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44419</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45561.42905092592</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44489</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45510.39084490741</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>44890.45898148148</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>45217.64325231482</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>45762.62880787037</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44999</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45103.4578125</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45103.4828125</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45713</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>45666.41087962963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45181</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45376.57670138889</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45440</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45079.47167824074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>44868.38045138889</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>45070</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>44453</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>44277</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45107.72561342592</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>44606.73197916667</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>44465.45304398148</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>44953</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45601.6175</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45449.73532407408</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45545.46103009259</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45476.37739583333</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45156.75122685185</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45489.67844907408</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45104.47891203704</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>45149.53783564815</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45155</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45429.32715277778</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45587.39587962963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45754.58804398148</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>44407.33692129629</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>44938.4812962963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>45786.36038194445</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>45665.30042824074</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>45785.85196759259</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45706.64979166666</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>45698.47010416666</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45547.5259375</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>45572.50128472222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>44973.68172453704</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>44867.83456018518</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>44300.37375</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>44315.61856481482</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45230.60619212963</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45370</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45246.69150462963</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45253</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45357.56929398148</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45367.30908564815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45744.56760416667</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45260</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45785.57039351852</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45673.35722222222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45785.5658912037</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45301</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>44982.82561342593</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>45625</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>45489</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45785.33315972222</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45616.68453703704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45616.69777777778</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45096</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>45579</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>45474.54547453704</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45169.62481481482</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>44580.39465277778</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44333.68109953704</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45786.35825231481</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>45079</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45320.32636574074</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45401.55627314815</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>45785.87679398148</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45786.3628125</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>44495</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45534.67787037037</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45791.46207175926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45113</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45790.8237962963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45616.66118055556</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>45469.49331018519</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45792.46319444444</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45792.46534722222</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45791.45240740741</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45792.4578587963</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45792.46865740741</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>45478.55826388889</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>45118</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45131</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45763</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45534.39119212963</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45773</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45315</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45016.44748842593</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>45561.61627314815</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45392.56559027778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45796.54754629629</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>45701.1425</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44566</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45092.3945949074</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>45668.61670138889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45761.54658564815</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45197</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45603</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45035</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>45798.38493055556</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45359.64686342593</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>44832.45126157408</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>45218.41752314815</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45169.63607638889</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45338.3546412037</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>45560.66090277778</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>44645.61398148148</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>45798.87049768519</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>45478.47974537037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>44697</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>45727.54988425926</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45727</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45713.67922453704</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>45714.24815972222</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45602</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45664.89855324074</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44677</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45373.43667824074</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45846.47327546297</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>45846.46805555555</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45525.37091435185</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45327</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>45063</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45082</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>45805</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>45191.39680555555</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>44839</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>44910</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>44351</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>44657</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>44594</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45049</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>44120</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>44622</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>44973.51290509259</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>44973</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>45770.36494212963</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29375,7 +29375,7 @@
         <v>45849.47482638889</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45224.64084490741</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45849.46460648148</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>45177</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45637.55811342593</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45072.49809027778</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>45852.64087962963</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45664.88829861111</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>45762.47326388889</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>45754.57761574074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45118</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>44209</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45233</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44957</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>44957.56633101852</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45392.56177083333</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45196.41028935185</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44833.86636574074</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>45852.67128472222</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44690.55664351852</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45754.58637731482</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45762.38605324074</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>45685.44299768518</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>45342.58545138889</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>44684.43402777778</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45615</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>44528.68445601852</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>45810.50623842593</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>45182</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45720.48189814815</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>45175</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>45093</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45812.58846064815</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>45812.59289351852</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>45832</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44596.39430555556</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45244</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>45341</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45741.39699074074</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45812.31928240741</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>45756.4618287037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>45475.72082175926</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>45475.76681712963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>45813.61592592593</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45813.61734953704</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45211</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44223</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>44223</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>45856.42729166667</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45856.43209490741</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>45187.45348379629</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45856.4249537037</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>45813.61375</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>45729.53497685185</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>45702.63559027778</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>45817.49847222222</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>44915.64974537037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>44368.48412037037</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32756,7 +32756,7 @@
         <v>45545</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>45407.33482638889</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>44972</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45818.33222222222</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44908</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>45859.46207175926</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>45089.45716435185</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45817.4940625</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>45551.45708333333</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>44488</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45239</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>44742</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45177</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>44909</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45175</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>45198.49947916667</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>44914.5846875</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45547.44084490741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>45544.7580787037</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>45211.43076388889</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45757.42518518519</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>45225</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>44224</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>45820.4099537037</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>44749</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>45820.40359953704</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45819</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45818</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>45818</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>44721</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45820.40600694445</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>45820.43005787037</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>45862.62265046296</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45862.61716435185</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>45820</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>44743</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>45750.40939814815</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34890,7 +34890,7 @@
         <v>45863.79833333333</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>45824.57248842593</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45175.79483796296</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>45821.48188657407</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>45824.47503472222</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>45863.78525462963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>45863.79356481481</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45824.63803240741</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>45478</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>44904</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45601</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>45824.56317129629</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>45734.48820601852</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>45414.88950231481</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>45442.44923611111</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>45825.38628472222</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>44959</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>45517.57674768518</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         <v>45744.58425925926</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>45754.5805787037</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45756.46728009259</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36102,7 +36102,7 @@
         <v>45744.34409722222</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>44909.51041666666</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>45664</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45244</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>44928</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>44841</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>44544.63826388889</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45775.61712962963</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>44803</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>44693.40193287037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>44959.60054398148</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>45448.40923611111</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>44739</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>44746.52041666667</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36905,7 +36905,7 @@
         <v>45758.47427083334</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45750.40331018518</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>44692</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45254.55388888889</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45561</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>45561</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>45330</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>44917.52387731482</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45408.42273148148</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45831.28561342593</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45831</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>44497</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>44992.53199074074</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>44974.39552083334</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45577.88273148148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45379</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45366.36186342593</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45189</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45098</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38018,7 +38018,7 @@
         <v>44335</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>45832</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>45873.50734953704</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>45217.49613425926</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45833.62319444444</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>44917</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38370,7 +38370,7 @@
         <v>44368</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>45834.48055555556</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>44873.78972222222</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45834.42243055555</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>45730.29663194445</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>44959</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45834.48547453704</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>45273.43420138889</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>44819</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>45301.31474537037</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45301.32008101852</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45763.38137731481</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>45833.63016203704</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45763</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>45327.3969212963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>45834.49290509259</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>45834.42037037037</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45145</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>45744.35152777778</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>45145.57739583333</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>45653</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45092.3869675926</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>44275.89116898148</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>44593</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45346.58555555555</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45628</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45728.57760416667</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45873</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>45616.70280092592</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45278</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45880.32877314815</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45090.53722222222</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>45610.49638888889</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>44756</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>45091.44966435185</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>45880.33408564814</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45837.43159722222</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45837.45643518519</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45335</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>45728.71802083333</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45222.46246527778</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>44973.87971064815</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45385</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>45882.68247685185</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>44621</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45881.43982638889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>44936.7375925926</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>45882.68072916667</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>44910</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45636.68237268519</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45484.50075231482</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>44865.32546296297</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45772.56983796296</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45840.36429398148</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>44973.28375</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>44985.4822337963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45883.58712962963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45883.60289351852</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45572.55528935185</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>45840.8866087963</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45372.34578703704</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45037</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>44939.46715277778</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45463</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45223</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>45230.60807870371</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45367.31642361111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42281,7 +42281,7 @@
         <v>45534.65803240741</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>45841.34291666667</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>45394.66318287037</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45090.50210648148</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45342.93295138889</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>44867.83100694444</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>44970.82792824074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45400.70824074074</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>44966.65418981481</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>44966.65623842592</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>45842.47361111111</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45552.43833333333</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45702.6415625</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44382</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45191.43909722222</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>44909</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>44973.8353125</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>44364</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43379,7 +43379,7 @@
         <v>45596.73567129629</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43436,7 +43436,7 @@
         <v>45764</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45764</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45095</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45737.66273148148</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>44243</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45695.44407407408</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45733.27633101852</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>44713.63434027778</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>44904</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45174.32129629629</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45415.32408564815</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45071</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44120,7 +44120,7 @@
         <v>45335</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45586</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45439.56545138889</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>44992.52833333334</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45740.58935185185</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>44825.37355324074</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45070</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45367.29472222222</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>44462</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>44463.49251157408</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45411.56006944444</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>44579.36934027778</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44809,7 +44809,7 @@
         <v>44713.6349537037</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
         <v>45121.62556712963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44923,7 +44923,7 @@
         <v>45121</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44980,7 +44980,7 @@
         <v>44928.58678240741</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>44594.37378472222</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>44933.42714120371</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>44977</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>44977.54047453704</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>44746.56648148148</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45322,7 +45322,7 @@
         <v>45762.3843287037</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45384,7 +45384,7 @@
         <v>44881.47697916667</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45441,7 +45441,7 @@
         <v>45188</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>44798.56335648148</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>45307</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45628</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45669,7 +45669,7 @@
         <v>45244</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>45359.64494212963</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>45089</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>45629.52961805555</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>44931.48902777778</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>45072</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46021,7 +46021,7 @@
         <v>44231.57006944445</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>45371.47248842593</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45106.66513888889</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>45561</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>45561</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>44914.47359953704</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>44083</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>44497.23909722222</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>44949.39141203704</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>45512.32738425926</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>45260</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>45057</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>45057</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>45188.35988425926</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>44909.49190972222</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>44798</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46943,7 +46943,7 @@
         <v>44819</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>45385.47306712963</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47057,7 +47057,7 @@
         <v>45056.72038194445</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47114,7 +47114,7 @@
         <v>45022.47684027778</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>45606.57791666667</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>45710.35591435185</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47285,7 +47285,7 @@
         <v>45681</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47347,7 +47347,7 @@
         <v>45075</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>45603</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47461,7 +47461,7 @@
         <v>44351.66695601852</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47518,7 +47518,7 @@
         <v>45253</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
         <v>44900.47381944444</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45754.4484375</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>45210.43765046296</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>45213.83515046296</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>45475.70619212963</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>44904</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47922,7 +47922,7 @@
         <v>44999.51451388889</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47979,7 +47979,7 @@
         <v>44984</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48036,7 +48036,7 @@
         <v>45082.42459490741</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>45177</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>44909.51342592593</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>44298.33628472222</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>45758.44347222222</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48326,7 +48326,7 @@
         <v>45091.44643518519</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45648</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48440,7 +48440,7 @@
         <v>45705.37840277778</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48497,7 +48497,7 @@
         <v>44333.63303240741</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>44494.38530092593</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48611,7 +48611,7 @@
         <v>44463.49472222223</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48668,7 +48668,7 @@
         <v>44340.37858796296</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>45392.59135416667</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48782,7 +48782,7 @@
         <v>45063.42767361111</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48839,7 +48839,7 @@
         <v>44798</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>45069.67789351852</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48953,7 +48953,7 @@
         <v>44853.58972222222</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49010,7 +49010,7 @@
         <v>45470.66217592593</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>45021</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>45079</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49181,7 +49181,7 @@
         <v>45727.55368055555</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49238,7 +49238,7 @@
         <v>45111</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49295,7 +49295,7 @@
         <v>45706.59305555555</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>45119.35530092593</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49409,7 +49409,7 @@
         <v>45668.48770833333</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49466,7 +49466,7 @@
         <v>45668.49403935186</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>44075</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49580,7 +49580,7 @@
         <v>45484.50256944444</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49637,7 +49637,7 @@
         <v>45409.28716435185</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>45694.35719907407</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49751,7 +49751,7 @@
         <v>44308</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>44713.63319444445</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44302.60905092592</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>44908</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>44974.3628125</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>45079.49798611111</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45208</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>45078</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>45525.33855324074</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>45022</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50321,7 +50321,7 @@
         <v>45590.48756944444</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>45653.66523148148</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45154.46340277778</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50497,7 +50497,7 @@
         <v>44390.44760416666</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>45175.80216435185</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45111.3095949074</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>44973.68408564815</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50730,7 +50730,7 @@
         <v>44390</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50787,7 +50787,7 @@
         <v>45078</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45231</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50901,7 +50901,7 @@
         <v>45488.44295138889</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>45050</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>45401.70074074074</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51072,7 +51072,7 @@
         <v>45149.52997685185</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>45075</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51186,7 +51186,7 @@
         <v>45679</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>44369</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>44951.40828703704</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>44880.27605324074</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>45758.65511574074</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>44386.57552083334</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51528,7 +51528,7 @@
         <v>45737.66959490741</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51585,7 +51585,7 @@
         <v>45687.58510416667</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51642,7 +51642,7 @@
         <v>45606.57449074074</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51699,7 +51699,7 @@
         <v>44818</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51756,7 +51756,7 @@
         <v>45369.55871527778</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>45762.406875</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>45762.41121527777</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>44945.47278935185</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51994,7 +51994,7 @@
         <v>44494.39315972223</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>44586.39371527778</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52108,7 +52108,7 @@
         <v>45093.41260416667</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52165,7 +52165,7 @@
         <v>45775.59509259259</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>45728.71716435185</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52279,7 +52279,7 @@
         <v>45733.60050925926</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52336,7 +52336,7 @@
         <v>45761.60565972222</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>45517.5049074074</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52450,7 +52450,7 @@
         <v>44991.4569212963</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52507,7 +52507,7 @@
         <v>45162</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52564,7 +52564,7 @@
         <v>45554</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52626,7 +52626,7 @@
         <v>44865</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52683,7 +52683,7 @@
         <v>44909.50149305556</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52740,7 +52740,7 @@
         <v>44816</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52797,7 +52797,7 @@
         <v>45762.40821759259</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52859,7 +52859,7 @@
         <v>45085.55108796297</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52916,7 +52916,7 @@
         <v>45308.45605324074</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>45649.57708333333</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45649.58368055556</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         <v>45649.63318287037</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53144,7 +53144,7 @@
         <v>45240.48289351852</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>44785.36618055555</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53258,7 +53258,7 @@
         <v>44881</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>44844</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53372,7 +53372,7 @@
         <v>45744.33675925926</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>45509.84324074074</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53486,7 +53486,7 @@
         <v>45189</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>45011</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53605,7 +53605,7 @@
         <v>45210</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53662,7 +53662,7 @@
         <v>45729.53114583333</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53719,7 +53719,7 @@
         <v>45110</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53781,7 +53781,7 @@
         <v>45568</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         <v>44418</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45728.58208333333</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45649.56231481482</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45649.56582175926</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>45591.31592592593</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>45635.46313657407</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>45670.48837962963</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54252,7 +54252,7 @@
         <v>45028.64141203704</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>44700.52403935185</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54366,7 +54366,7 @@
         <v>45072.49364583333</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         <v>44811.50899305556</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>45616.69401620371</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>44867</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45429.49690972222</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>44889</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45135</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>44594</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>45055.32497685185</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>45331.60153935185</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>45111.56173611111</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45762.38353009259</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55055,7 +55055,7 @@
         <v>45761.7169212963</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55117,7 +55117,7 @@
         <v>45762.37043981482</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55174,7 +55174,7 @@
         <v>45775</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55236,7 +55236,7 @@
         <v>45567</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55298,7 +55298,7 @@
         <v>45426.64987268519</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55355,7 +55355,7 @@
         <v>45022</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55412,7 +55412,7 @@
         <v>45177</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>44778.47969907407</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55531,7 +55531,7 @@
         <v>45056</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55588,7 +55588,7 @@
         <v>45149</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45561</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45205.32967592592</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>44869.44665509259</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>45763</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>44882</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55935,7 +55935,7 @@
         <v>45721</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>44236</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56049,7 +56049,7 @@
         <v>45103.42912037037</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56106,7 +56106,7 @@
         <v>44431</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56163,7 +56163,7 @@
         <v>44431</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56220,7 +56220,7 @@
         <v>45188</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56277,7 +56277,7 @@
         <v>45757.40310185185</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56334,7 +56334,7 @@
         <v>44874.3702662037</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56391,7 +56391,7 @@
         <v>45240.54020833333</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56448,7 +56448,7 @@
         <v>45077</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56505,7 +56505,7 @@
         <v>45013.53428240741</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56562,7 +56562,7 @@
         <v>45090.57193287037</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56619,7 +56619,7 @@
         <v>44903.63063657407</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56676,7 +56676,7 @@
         <v>45279</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56733,7 +56733,7 @@
         <v>44609.62754629629</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45477.45034722222</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>44368.48951388889</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56904,7 +56904,7 @@
         <v>45407.58145833333</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56961,7 +56961,7 @@
         <v>44882</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57018,7 +57018,7 @@
         <v>45412</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>44882</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57132,7 +57132,7 @@
         <v>45210</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57189,7 +57189,7 @@
         <v>45296</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57246,7 +57246,7 @@
         <v>45754.57903935185</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57308,7 +57308,7 @@
         <v>45596.74167824074</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57365,7 +57365,7 @@
         <v>44368.47782407407</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57422,7 +57422,7 @@
         <v>45069.42486111111</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57479,7 +57479,7 @@
         <v>45163.48395833333</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57536,7 +57536,7 @@
         <v>45107</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57593,7 +57593,7 @@
         <v>45373.4965625</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57650,7 +57650,7 @@
         <v>45369.51451388889</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57707,7 +57707,7 @@
         <v>44825</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57764,7 +57764,7 @@
         <v>45342.58582175926</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57821,7 +57821,7 @@
         <v>45096</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57878,7 +57878,7 @@
         <v>45356.37466435185</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57935,7 +57935,7 @@
         <v>45103</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57992,7 +57992,7 @@
         <v>45098</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58049,7 +58049,7 @@
         <v>45166.81506944444</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58106,7 +58106,7 @@
         <v>45321.30368055555</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58163,7 +58163,7 @@
         <v>45575.40405092593</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58220,7 +58220,7 @@
         <v>44183</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58277,7 +58277,7 @@
         <v>45156.74657407407</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>45313</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58391,7 +58391,7 @@
         <v>45561</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58453,7 +58453,7 @@
         <v>45761.36119212963</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58510,7 +58510,7 @@
         <v>45756.64157407408</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58567,7 +58567,7 @@
         <v>45394.64731481481</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58629,7 +58629,7 @@
         <v>45013.59971064814</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58686,7 +58686,7 @@
         <v>45560.65891203703</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58743,7 +58743,7 @@
         <v>45653.6771875</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58800,7 +58800,7 @@
         <v>45603</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58857,7 +58857,7 @@
         <v>45446.57478009259</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58919,7 +58919,7 @@
         <v>45368.71136574074</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58976,7 +58976,7 @@
         <v>45369.51261574074</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59033,7 +59033,7 @@
         <v>45644.49726851852</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59090,7 +59090,7 @@
         <v>45096</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -567,7 +567,7 @@
         <v>44460.70982638889</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44606</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45810.50783564815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45616</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45189</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>44490</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44370</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>45735.34555555556</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>44112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45352.45320601852</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44867</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>44347</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>44145</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44266</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>45652.74018518518</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45174.32886574074</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>45428.42564814815</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>45447</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>45730.63277777778</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>45695.93653935185</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45358.44835648148</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45853</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>45832</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>45075</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44120</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>44785.43395833333</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45093.3646875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>45093.3703587963</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45222</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>44937</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44175</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44375</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>44602</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45721.65631944445</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45215</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>45541.51222222222</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45096</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>44909</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>44504.50979166666</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>45594</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>45701.45335648148</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>44648</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>45846.4975</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>45621.64417824074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>45316</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>45621.64115740741</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>45850.60619212963</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45042</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45754.48619212963</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45863.39380787037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>44120</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45103</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45307</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>45449.38423611111</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>45110</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45873</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44448.31037037037</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>45840.8834375</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44917</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>45581.56951388889</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44656</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45621.63548611111</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>45596.52869212963</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45604.50471064815</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44966.64579861111</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>44917</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44365</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>45695.93015046296</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>45615.62699074074</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>44980</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44073</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44059</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44060</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44064</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44074</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44261</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44347</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44073.7496875</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>44378</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44179</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44130</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44110.43048611111</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44120</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>44183</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>44224</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>44230</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44272</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44300.3625</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44385.40346064815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>44123</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>44208</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>44491</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>44120</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>44278</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>44363.76037037037</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>44267.32773148148</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44407.34103009259</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>44462</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44201</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44379</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44407.35815972222</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44630</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>44418.56681712963</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44089</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44320</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44236</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44225</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44342.65030092592</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44297</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44365</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44194</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>44071</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44363.75403935185</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44889.52459490741</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44302</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>44691</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>44138</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44474</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44137.79510416667</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44412</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44859</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44102</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44164</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44861</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44475</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44246</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>44365</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44473.51576388889</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44362</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44245</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>44581</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>44587</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44656</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>44449.57666666667</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44844</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>44816</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>44571.48392361111</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>44612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44152</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>44645.61962962963</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>44187</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>44088</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44088</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>44201</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>44130</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>44565</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44256</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>44365</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>44312.52064814815</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44593.58975694444</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>44131</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>44831.51668981482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44840</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>44783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44179</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44365</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>44375.42613425926</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>44369</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44566</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>44084</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44060</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>44684</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>44328</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>44347</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44365</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>44306</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>44315.67481481482</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>44806.30436342592</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>44364.69368055555</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>44493.7688425926</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>44488.93328703703</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44362</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>44833.85800925926</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>44217.63880787037</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>44083</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>44078</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>44386.50282407407</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>44468.38931712963</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44587</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>44624.4716087963</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>44593</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>44294.69576388889</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>44449.61309027778</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44449</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>44169</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>44172</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>44419</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>44321.32876157408</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>44295.56511574074</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>44340.37452546296</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>44284</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>44363.75775462963</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>44259</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>44776.4441087963</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>44870.4825462963</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>44351</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>44594.37494212963</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>44629</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>44494</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44211</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>44137</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44223</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>44839.34592592593</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44748.39954861111</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44771.403125</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>44593</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>44378.26744212963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>44881.46946759259</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>44183</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>44365</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>44418</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44634</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>44634</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>44796</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>44075</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44370.25283564815</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44727</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44218</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>44657</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>44551.60501157407</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>44104.58186342593</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44805.72581018518</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>44112</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>44243.24046296296</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>44375</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>44161</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>44250</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>44270.62047453703</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44183</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44612.64552083334</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>44299.65049768519</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>44407.33940972222</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>44300.5134375</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44593</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>44449</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>44160</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44092</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>44617.57709490741</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>44813.46402777778</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44593</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>44363.75042824074</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>44526.31395833333</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>44169</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>44225</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>44207.56376157407</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44089</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>44376.47229166667</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>44551</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44508</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>44246</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>44375.39068287037</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>44376</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>44551</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44578.49199074074</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44445</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44407.35585648148</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44407.35945601852</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44785.35797453704</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>44870.4822337963</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>44587</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44136</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>44073</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>44853</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44378.27100694444</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>44384</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44851</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44650</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44222</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44839</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45702.52855324074</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44866.62503472222</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44866.6291550926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45091.44322916667</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>44755</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>44867</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45190</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>45075</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45253</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>44270</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45579</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45342.93903935186</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>44827</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45216</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45341.43773148148</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>45363.79693287037</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>44505</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45773</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45118.44516203704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>44266.66663194444</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>44295</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>44449.61662037037</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>45121</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>45280.75414351852</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45123.42461805556</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45336</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45434.42591435185</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>44376</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>45762.6184375</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>44348</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45043</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45054</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45679</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45117.52946759259</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>45078</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45702.63752314815</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>44307.41146990741</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>45622.7463425926</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>45093</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45084.52010416667</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45572.49996527778</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45713</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20584,7 +20584,7 @@
         <v>45714.28113425926</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>45649.55618055556</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45551.45940972222</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45649.59947916667</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>45649.63702546297</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44419</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45561.42905092592</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44489</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45510.39084490741</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>44890.45898148148</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>45217.64325231482</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>45762.62880787037</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44999</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45103.4578125</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45103.4828125</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45713</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>45666.41087962963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45181</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45376.57670138889</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45440</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45079.47167824074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>44868.38045138889</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>45070</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>44453</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>44277</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45107.72561342592</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>44606.73197916667</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>44465.45304398148</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>44953</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45601.6175</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45449.73532407408</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45545.46103009259</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45476.37739583333</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45156.75122685185</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45489.67844907408</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45104.47891203704</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>45149.53783564815</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45155</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45429.32715277778</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45587.39587962963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45754.58804398148</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>44407.33692129629</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>44938.4812962963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>45786.36038194445</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>45665.30042824074</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>45785.85196759259</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45706.64979166666</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>45698.47010416666</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45547.5259375</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>45572.50128472222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>44973.68172453704</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>44867.83456018518</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>44300.37375</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>44315.61856481482</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45230.60619212963</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45370</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45246.69150462963</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45253</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45357.56929398148</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45367.30908564815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45744.56760416667</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45260</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45785.57039351852</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45673.35722222222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45785.5658912037</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45301</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>44982.82561342593</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>45625</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>45489</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45785.33315972222</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45616.68453703704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45616.69777777778</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45096</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>45579</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>45474.54547453704</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45169.62481481482</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>44580.39465277778</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44333.68109953704</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45786.35825231481</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>45079</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45320.32636574074</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45401.55627314815</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>45785.87679398148</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45786.3628125</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>44495</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45534.67787037037</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45791.46207175926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45113</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45790.8237962963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45616.66118055556</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>45469.49331018519</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45792.46319444444</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45792.46534722222</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45791.45240740741</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45792.4578587963</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45792.46865740741</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>45478.55826388889</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>45118</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45131</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45763</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45534.39119212963</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45773</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45315</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45016.44748842593</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>45561.61627314815</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45392.56559027778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45796.54754629629</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>45701.1425</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44566</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45092.3945949074</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>45668.61670138889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45761.54658564815</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45197</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45603</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45035</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>45798.38493055556</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45359.64686342593</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>44832.45126157408</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>45218.41752314815</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45169.63607638889</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45338.3546412037</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>45560.66090277778</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>44645.61398148148</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>45798.87049768519</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>45478.47974537037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>44697</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>45727.54988425926</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45727</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45713.67922453704</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>45714.24815972222</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45602</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45664.89855324074</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44677</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45373.43667824074</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45846.47327546297</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>45846.46805555555</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45525.37091435185</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45327</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>45063</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45082</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>45805</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>45191.39680555555</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>44839</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>44910</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>44351</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>44657</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>44594</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45049</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>44120</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>44622</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>44973.51290509259</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>44973</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>45770.36494212963</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29375,7 +29375,7 @@
         <v>45849.47482638889</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45224.64084490741</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45849.46460648148</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>45177</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45637.55811342593</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45072.49809027778</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>45852.64087962963</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45664.88829861111</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>45762.47326388889</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>45754.57761574074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45118</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>44209</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45233</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44957</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>44957.56633101852</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45392.56177083333</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45196.41028935185</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44833.86636574074</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>45852.67128472222</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44690.55664351852</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45754.58637731482</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45762.38605324074</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>45685.44299768518</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>45342.58545138889</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>44684.43402777778</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45615</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>44528.68445601852</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>45810.50623842593</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>45182</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45720.48189814815</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>45175</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>45093</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45812.58846064815</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>45812.59289351852</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>45832</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44596.39430555556</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45244</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>45341</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45741.39699074074</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45812.31928240741</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>45756.4618287037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>45475.72082175926</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>45475.76681712963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>45813.61592592593</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45813.61734953704</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45211</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44223</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>44223</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>45856.42729166667</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45856.43209490741</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>45187.45348379629</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45856.4249537037</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>45813.61375</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>45729.53497685185</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>45702.63559027778</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>45817.49847222222</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>44915.64974537037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>44368.48412037037</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32756,7 +32756,7 @@
         <v>45545</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>45407.33482638889</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>44972</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45818.33222222222</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44908</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>45859.46207175926</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>45089.45716435185</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45817.4940625</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>45551.45708333333</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>44488</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45239</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>44742</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45177</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>44909</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45175</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>45198.49947916667</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>44914.5846875</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45547.44084490741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>45544.7580787037</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>45211.43076388889</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45757.42518518519</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>45225</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>44224</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>45820.4099537037</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>44749</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>45820.40359953704</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45819</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45818</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>45818</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>44721</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45820.40600694445</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>45820.43005787037</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>45862.62265046296</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45862.61716435185</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>45820</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>44743</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>45750.40939814815</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34890,7 +34890,7 @@
         <v>45863.79833333333</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>45824.57248842593</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45175.79483796296</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>45821.48188657407</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>45824.47503472222</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>45863.78525462963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>45863.79356481481</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45824.63803240741</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>45478</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>44904</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45601</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>45824.56317129629</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>45734.48820601852</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>45414.88950231481</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>45442.44923611111</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>45825.38628472222</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>44959</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>45517.57674768518</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         <v>45744.58425925926</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>45754.5805787037</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45756.46728009259</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36102,7 +36102,7 @@
         <v>45744.34409722222</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>44909.51041666666</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>45664</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45244</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>44928</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>44841</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>44544.63826388889</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45775.61712962963</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>44803</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>44693.40193287037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>44959.60054398148</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>45448.40923611111</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>44739</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>44746.52041666667</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36905,7 +36905,7 @@
         <v>45758.47427083334</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45750.40331018518</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>44692</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45254.55388888889</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45561</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>45561</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>45330</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>44917.52387731482</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45408.42273148148</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45831.28561342593</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45831</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>44497</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>44992.53199074074</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>44974.39552083334</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45577.88273148148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45379</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45366.36186342593</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45189</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45098</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38018,7 +38018,7 @@
         <v>44335</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>45832</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>45873.50734953704</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>45217.49613425926</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45833.62319444444</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>44917</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38370,7 +38370,7 @@
         <v>44368</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>45834.48055555556</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>44873.78972222222</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45834.42243055555</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>45730.29663194445</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>44959</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45834.48547453704</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>45273.43420138889</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>44819</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>45301.31474537037</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45301.32008101852</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45763.38137731481</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>45833.63016203704</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45763</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>45327.3969212963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>45834.49290509259</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>45834.42037037037</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45145</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>45744.35152777778</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>45145.57739583333</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>45653</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45092.3869675926</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>44275.89116898148</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>44593</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45346.58555555555</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45628</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45728.57760416667</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45873</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>45616.70280092592</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45278</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45880.32877314815</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45090.53722222222</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>45610.49638888889</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>44756</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>45091.44966435185</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>45880.33408564814</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45837.43159722222</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45837.45643518519</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45335</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>45728.71802083333</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45222.46246527778</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>44973.87971064815</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45385</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>45882.68247685185</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>44621</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45881.43982638889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>44936.7375925926</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>45882.68072916667</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>44910</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45636.68237268519</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45484.50075231482</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>44865.32546296297</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45772.56983796296</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45840.36429398148</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>44973.28375</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>44985.4822337963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45883.58712962963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45883.60289351852</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45572.55528935185</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>45840.8866087963</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45372.34578703704</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45037</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>44939.46715277778</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45463</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45223</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>45230.60807870371</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45367.31642361111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42281,7 +42281,7 @@
         <v>45534.65803240741</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>45841.34291666667</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>45394.66318287037</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45090.50210648148</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45342.93295138889</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>44867.83100694444</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>44970.82792824074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45400.70824074074</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>44966.65418981481</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>44966.65623842592</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>45842.47361111111</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45552.43833333333</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45702.6415625</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44382</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45191.43909722222</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>44909</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>44973.8353125</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>44364</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43379,7 +43379,7 @@
         <v>45596.73567129629</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43436,7 +43436,7 @@
         <v>45764</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45764</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45095</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45737.66273148148</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>44243</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45695.44407407408</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45733.27633101852</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>44713.63434027778</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>44904</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45174.32129629629</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45415.32408564815</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45071</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44120,7 +44120,7 @@
         <v>45335</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45586</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45439.56545138889</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>44992.52833333334</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45740.58935185185</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>44825.37355324074</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45070</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45367.29472222222</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>44462</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>44463.49251157408</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45411.56006944444</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>44579.36934027778</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44809,7 +44809,7 @@
         <v>44713.6349537037</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
         <v>45121.62556712963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44923,7 +44923,7 @@
         <v>45121</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44980,7 +44980,7 @@
         <v>44928.58678240741</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>44594.37378472222</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>44933.42714120371</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>44977</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>44977.54047453704</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>44746.56648148148</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45322,7 +45322,7 @@
         <v>45762.3843287037</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45384,7 +45384,7 @@
         <v>44881.47697916667</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45441,7 +45441,7 @@
         <v>45188</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>44798.56335648148</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>45307</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45628</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45669,7 +45669,7 @@
         <v>45244</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>45359.64494212963</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>45089</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>45629.52961805555</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>44931.48902777778</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>45072</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46021,7 +46021,7 @@
         <v>44231.57006944445</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>45371.47248842593</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45106.66513888889</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>45561</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>45561</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>44914.47359953704</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>44083</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>44497.23909722222</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>44949.39141203704</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>45512.32738425926</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>45260</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>45057</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>45057</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>45188.35988425926</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>44909.49190972222</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>44798</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46943,7 +46943,7 @@
         <v>44819</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>45385.47306712963</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47057,7 +47057,7 @@
         <v>45056.72038194445</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47114,7 +47114,7 @@
         <v>45022.47684027778</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>45606.57791666667</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>45710.35591435185</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47285,7 +47285,7 @@
         <v>45681</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47347,7 +47347,7 @@
         <v>45075</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>45603</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47461,7 +47461,7 @@
         <v>44351.66695601852</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47518,7 +47518,7 @@
         <v>45253</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
         <v>44900.47381944444</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45754.4484375</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>45210.43765046296</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>45213.83515046296</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>45475.70619212963</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>44904</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47922,7 +47922,7 @@
         <v>44999.51451388889</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47979,7 +47979,7 @@
         <v>44984</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48036,7 +48036,7 @@
         <v>45082.42459490741</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>45177</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>44909.51342592593</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>44298.33628472222</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>45758.44347222222</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48326,7 +48326,7 @@
         <v>45091.44643518519</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45648</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48440,7 +48440,7 @@
         <v>45705.37840277778</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48497,7 +48497,7 @@
         <v>44333.63303240741</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>44494.38530092593</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48611,7 +48611,7 @@
         <v>44463.49472222223</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48668,7 +48668,7 @@
         <v>44340.37858796296</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>45392.59135416667</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48782,7 +48782,7 @@
         <v>45063.42767361111</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48839,7 +48839,7 @@
         <v>44798</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>45069.67789351852</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48953,7 +48953,7 @@
         <v>44853.58972222222</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49010,7 +49010,7 @@
         <v>45470.66217592593</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>45021</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>45079</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49181,7 +49181,7 @@
         <v>45727.55368055555</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49238,7 +49238,7 @@
         <v>45111</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49295,7 +49295,7 @@
         <v>45706.59305555555</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>45119.35530092593</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49409,7 +49409,7 @@
         <v>45668.48770833333</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49466,7 +49466,7 @@
         <v>45668.49403935186</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>44075</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49580,7 +49580,7 @@
         <v>45484.50256944444</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49637,7 +49637,7 @@
         <v>45409.28716435185</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>45694.35719907407</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49751,7 +49751,7 @@
         <v>44308</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>44713.63319444445</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44302.60905092592</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>44908</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>44974.3628125</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>45079.49798611111</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45208</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>45078</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>45525.33855324074</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>45022</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50321,7 +50321,7 @@
         <v>45590.48756944444</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>45653.66523148148</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45154.46340277778</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50497,7 +50497,7 @@
         <v>44390.44760416666</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>45175.80216435185</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45111.3095949074</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>44973.68408564815</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50730,7 +50730,7 @@
         <v>44390</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50787,7 +50787,7 @@
         <v>45078</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45231</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50901,7 +50901,7 @@
         <v>45488.44295138889</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>45050</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>45401.70074074074</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51072,7 +51072,7 @@
         <v>45149.52997685185</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>45075</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51186,7 +51186,7 @@
         <v>45679</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>44369</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>44951.40828703704</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>44880.27605324074</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>45758.65511574074</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>44386.57552083334</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51528,7 +51528,7 @@
         <v>45737.66959490741</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51585,7 +51585,7 @@
         <v>45687.58510416667</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51642,7 +51642,7 @@
         <v>45606.57449074074</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51699,7 +51699,7 @@
         <v>44818</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51756,7 +51756,7 @@
         <v>45369.55871527778</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>45762.406875</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>45762.41121527777</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>44945.47278935185</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51994,7 +51994,7 @@
         <v>44494.39315972223</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>44586.39371527778</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52108,7 +52108,7 @@
         <v>45093.41260416667</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52165,7 +52165,7 @@
         <v>45775.59509259259</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>45728.71716435185</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52279,7 +52279,7 @@
         <v>45733.60050925926</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52336,7 +52336,7 @@
         <v>45761.60565972222</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>45517.5049074074</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52450,7 +52450,7 @@
         <v>44991.4569212963</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52507,7 +52507,7 @@
         <v>45162</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52564,7 +52564,7 @@
         <v>45554</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52626,7 +52626,7 @@
         <v>44865</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52683,7 +52683,7 @@
         <v>44909.50149305556</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52740,7 +52740,7 @@
         <v>44816</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52797,7 +52797,7 @@
         <v>45762.40821759259</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52859,7 +52859,7 @@
         <v>45085.55108796297</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52916,7 +52916,7 @@
         <v>45308.45605324074</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>45649.57708333333</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45649.58368055556</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         <v>45649.63318287037</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53144,7 +53144,7 @@
         <v>45240.48289351852</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>44785.36618055555</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53258,7 +53258,7 @@
         <v>44881</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>44844</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53372,7 +53372,7 @@
         <v>45744.33675925926</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>45509.84324074074</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53486,7 +53486,7 @@
         <v>45189</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>45011</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53605,7 +53605,7 @@
         <v>45210</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53662,7 +53662,7 @@
         <v>45729.53114583333</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53719,7 +53719,7 @@
         <v>45110</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53781,7 +53781,7 @@
         <v>45568</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         <v>44418</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45728.58208333333</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45649.56231481482</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45649.56582175926</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>45591.31592592593</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>45635.46313657407</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>45670.48837962963</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54252,7 +54252,7 @@
         <v>45028.64141203704</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>44700.52403935185</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54366,7 +54366,7 @@
         <v>45072.49364583333</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         <v>44811.50899305556</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>45616.69401620371</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>44867</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45429.49690972222</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>44889</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45135</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>44594</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>45055.32497685185</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>45331.60153935185</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>45111.56173611111</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45762.38353009259</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55055,7 +55055,7 @@
         <v>45761.7169212963</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55117,7 +55117,7 @@
         <v>45762.37043981482</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55174,7 +55174,7 @@
         <v>45775</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55236,7 +55236,7 @@
         <v>45567</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55298,7 +55298,7 @@
         <v>45426.64987268519</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55355,7 +55355,7 @@
         <v>45022</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55412,7 +55412,7 @@
         <v>45177</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55474,7 +55474,7 @@
         <v>44778.47969907407</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55531,7 +55531,7 @@
         <v>45056</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55588,7 +55588,7 @@
         <v>45149</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45561</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45205.32967592592</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>44869.44665509259</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>45763</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>44882</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55935,7 +55935,7 @@
         <v>45721</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>44236</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56049,7 +56049,7 @@
         <v>45103.42912037037</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56106,7 +56106,7 @@
         <v>44431</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56163,7 +56163,7 @@
         <v>44431</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56220,7 +56220,7 @@
         <v>45188</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56277,7 +56277,7 @@
         <v>45757.40310185185</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56334,7 +56334,7 @@
         <v>44874.3702662037</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56391,7 +56391,7 @@
         <v>45240.54020833333</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56448,7 +56448,7 @@
         <v>45077</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56505,7 +56505,7 @@
         <v>45013.53428240741</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56562,7 +56562,7 @@
         <v>45090.57193287037</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56619,7 +56619,7 @@
         <v>44903.63063657407</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56676,7 +56676,7 @@
         <v>45279</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56733,7 +56733,7 @@
         <v>44609.62754629629</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45477.45034722222</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>44368.48951388889</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56904,7 +56904,7 @@
         <v>45407.58145833333</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56961,7 +56961,7 @@
         <v>44882</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57018,7 +57018,7 @@
         <v>45412</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>44882</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57132,7 +57132,7 @@
         <v>45210</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57189,7 +57189,7 @@
         <v>45296</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57246,7 +57246,7 @@
         <v>45754.57903935185</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57308,7 +57308,7 @@
         <v>45596.74167824074</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57365,7 +57365,7 @@
         <v>44368.47782407407</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57422,7 +57422,7 @@
         <v>45069.42486111111</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57479,7 +57479,7 @@
         <v>45163.48395833333</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57536,7 +57536,7 @@
         <v>45107</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57593,7 +57593,7 @@
         <v>45373.4965625</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57650,7 +57650,7 @@
         <v>45369.51451388889</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57707,7 +57707,7 @@
         <v>44825</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57764,7 +57764,7 @@
         <v>45342.58582175926</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57821,7 +57821,7 @@
         <v>45096</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57878,7 +57878,7 @@
         <v>45356.37466435185</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57935,7 +57935,7 @@
         <v>45103</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57992,7 +57992,7 @@
         <v>45098</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58049,7 +58049,7 @@
         <v>45166.81506944444</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58106,7 +58106,7 @@
         <v>45321.30368055555</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58163,7 +58163,7 @@
         <v>45575.40405092593</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58220,7 +58220,7 @@
         <v>44183</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58277,7 +58277,7 @@
         <v>45156.74657407407</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>45313</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58391,7 +58391,7 @@
         <v>45561</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58453,7 +58453,7 @@
         <v>45761.36119212963</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58510,7 +58510,7 @@
         <v>45756.64157407408</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58567,7 +58567,7 @@
         <v>45394.64731481481</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58629,7 +58629,7 @@
         <v>45013.59971064814</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58686,7 +58686,7 @@
         <v>45560.65891203703</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58743,7 +58743,7 @@
         <v>45653.6771875</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58800,7 +58800,7 @@
         <v>45603</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58857,7 +58857,7 @@
         <v>45446.57478009259</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58919,7 +58919,7 @@
         <v>45368.71136574074</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58976,7 +58976,7 @@
         <v>45369.51261574074</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59033,7 +59033,7 @@
         <v>45644.49726851852</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59090,7 +59090,7 @@
         <v>45096</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -567,7 +567,7 @@
         <v>44460.70982638889</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44606</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45810.50783564815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45189</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45616</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>44490</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44370</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>45352.45320601852</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>44867</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>45888.34414351852</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>45888.42650462963</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45735.34555555556</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44347</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>44145</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44266</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45093.3646875</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>45093.3703587963</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45695.93653935185</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>45358.44835648148</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45447</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>45428.42564814815</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45652.74018518518</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45222</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45730.63277777778</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>44785.43395833333</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45832</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44937</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45174.32886574074</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>45853</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>44120</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>45075</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>44175</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>44375</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44602</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>45042</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>45695.93015046296</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>45103</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45596.52869212963</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45594</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>45307</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>45110</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44504.50979166666</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44656</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>44448.31037037037</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>45541.51222222222</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45701.45335648148</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>45721.65631944445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44909</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>44966.64579861111</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45449.38423611111</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>45621.63548611111</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44648</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44917</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>44917</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45621.64417824074</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>45615.62699074074</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>44365</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45215</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>45096</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45850.60619212963</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>45316</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>45863.39380787037</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>44980</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>45581.56951388889</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>45621.64115740741</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>45604.50471064815</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>44120</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45840.8834375</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>45873</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45846.4975</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45891.63179398148</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>45754.48619212963</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44073</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44074</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44347</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44261</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44130</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44378</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44110.43048611111</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44073.7496875</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44179</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44120</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44183</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44224</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44230</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>44272</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44300.3625</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>44385.40346064815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44123</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44208</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>44491</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>44363.76037037037</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44407.34103009259</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>44120</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>44278</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>44201</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>44462</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44267.32773148148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44407.35815972222</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>44630</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>44089</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>44320</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>44418.56681712963</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44236</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>44379</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44225</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44297</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44342.65030092592</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>44194</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>44365</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>44071</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>44363.75403935185</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>44889.52459490741</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>44302</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>44474</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44138</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>44137.79510416667</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>44412</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>44859</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>44102</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44164</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>44861</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>44475</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44246</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44245</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44365</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44473.51576388889</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>44362</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>44581</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44587</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>44449.57666666667</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>44656</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>44844</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>44816</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>44571.48392361111</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44612</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44152</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>44645.61962962963</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>44187</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>44088</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>44201</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44130</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44565</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44256</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>44365</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>44312.52064814815</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>44691</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>44088</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>44593.58975694444</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>44131</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>44831.51668981482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44840</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44179</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44365</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44375.42613425926</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44369</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44566</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44328</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44684</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44347</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44365</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44306</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44315.67481481482</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44806.30436342592</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44364.69368055555</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44493.7688425926</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44488.93328703703</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44362</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44217.63880787037</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>44833.85800925926</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>44083</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>44078</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>44386.50282407407</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44468.38931712963</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44587</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>44624.4716087963</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>44593</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>44294.69576388889</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44449.61309027778</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>44449</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44169</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>44172</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>44419</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44321.32876157408</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44295.56511574074</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44340.37452546296</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>44851</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>44284</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>44363.75775462963</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>44136</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44259</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>44073</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>44776.4441087963</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>44378.27100694444</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44870.4825462963</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>44650</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44384</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>44211</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44137</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44223</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44839.34592592593</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>44351</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>44748.39954861111</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44771.403125</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44449.61662037037</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44594.37494212963</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44629</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44494</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44365</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44593</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44183</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>44378.26744212963</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>44881.46946759259</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>44634</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>44634</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>44218</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>44418</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>44727</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>44796</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>44075</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>44370.25283564815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>44657</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>44551.60501157407</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>44805.72581018518</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44243.24046296296</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>44104.58186342593</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>44112</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>44250</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44375</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>44161</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>44299.65049768519</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>44183</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>44300.5134375</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>44270.62047453703</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>44593</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>44092</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>44160</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>44593</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>44612.64552083334</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>44813.46402777778</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>44407.33940972222</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>44169</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>44207.56376157407</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44225</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>44363.75042824074</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>44526.31395833333</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>44449</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>44089</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>44617.57709490741</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>44376</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>44551</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>44376.47229166667</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>44375.39068287037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>44870.4822337963</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>44785.35797453704</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44587</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44578.49199074074</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44445</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44407.35585648148</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44407.35945601852</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>44209</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44222</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>45474.54547453704</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45273.43420138889</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45649.57708333333</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45649.58368055556</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45649.63318287037</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45341</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44551</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>44508</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>44246</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45687.58510416667</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>45762.406875</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45022</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>44785.36618055555</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>45113</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>44917</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>44938.4812962963</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45775.61712962963</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45560.66090277778</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>44880.27605324074</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>44488</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>45177</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>45649.55618055556</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>45649.59947916667</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>44867</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44853</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>44224</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45089.45716435185</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45208</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>45280.75414351852</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45758.47427083334</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45517.5049074074</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>44580.39465277778</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45727.54988425926</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45488.44295138889</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45534.65803240741</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45702.63752314815</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45342.58545138889</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45082.42459490741</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45591.31592592593</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45043</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45616.69777777778</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45484.50256944444</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45426.64987268519</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>44489</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45050</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45330</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45706.59305555555</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45103.4828125</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45107</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45123.42461805556</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44974.3628125</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>45162</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>44936.7375925926</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45392.56559027778</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45572.49996527778</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45756.46728009259</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>44700.52403935185</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45230.60807870371</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45092.3945949074</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>44819</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>44693.40193287037</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44739</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44622</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45240.54020833333</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44419</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44083</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>45054</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>45664.88829861111</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>44494.39315972223</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45091.44966435185</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45603</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45606.57449074074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45296</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45278</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>44865</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45744.35152777778</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45412</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>45187.45348379629</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44586.39371527778</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44984</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>45075</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45761.7169212963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45762.37043981482</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>44657</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44904</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45181</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44973.87971064815</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44348</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>44544.63826388889</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>44295</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>44933.42714120371</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45775.59509259259</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>44985.4822337963</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>44798.56335648148</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>45733.60050925926</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>44266.66663194444</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>45415.32408564815</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>44977</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>44977.54047453704</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45721</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45035</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>44909</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45090.53722222222</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>44621</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>44579.36934027778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>45392.59135416667</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44749</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>45372.34578703704</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44818</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44973.8353125</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44803</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45175</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>45762.40821759259</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45308.45605324074</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>44692</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>45577.88273148148</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>44904</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>44904</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45758.65511574074</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>45560.65891203703</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45079.49798611111</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45149.52997685185</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45763</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>45561</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45197</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45469.49331018519</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>45307</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45394.66318287037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45210</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>44881</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>45175</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>44369</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45028.64141203704</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44418</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>45175.80216435185</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45728.71802083333</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45478.55826388889</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45371.47248842593</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45727</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>44743</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45763</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>44594</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>44939.46715277778</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>45320.32636574074</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45762.38605324074</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>45111.3095949074</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>44966.65418981481</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>44966.65623842592</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45021</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45741.39699074074</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>44298.33628472222</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45681</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26736,7 +26736,7 @@
         <v>45668.49403935186</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>44882</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45702.6415625</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45313</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45079</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45733.27633101852</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45376.57670138889</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45379</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>45037</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45090.50210648148</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>45679</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45327.3969212963</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>45756.4618287037</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>45342.58582175926</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>44908</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>45561</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>45177</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>45327</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>45090.57193287037</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45110</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>45720.48189814815</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>45078</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45013.53428240741</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>45586</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45754.58804398148</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45737.66959490741</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>45653</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>44505</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>44900.47381944444</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45072</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45253</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>44465.45304398148</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>44606.73197916667</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45713</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45545.46103009259</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>45449.73532407408</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>44223</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28875,7 +28875,7 @@
         <v>44223</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>44973.51290509259</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>45407.58145833333</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45070</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>45177</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45601.6175</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45728.58208333333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>44277</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45476.37739583333</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>45489.67844907408</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>44243</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29512,7 +29512,7 @@
         <v>44909.50149305556</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>44909.51041666666</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>45587.39587962963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>44494.38530092593</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45448.40923611111</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>45118</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>44970.82792824074</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45750.40939814815</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>44594</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45763</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>45477.45034722222</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>45551.45708333333</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45224.64084490741</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>44868.38045138889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45729.53497685185</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45785.57039351852</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45785.33315972222</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>45785.5658912037</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>45596.74167824074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>45728.57760416667</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>44866.6291550926</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45107.72561342592</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>45022.47684027778</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45077</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30890,7 +30890,7 @@
         <v>45196.41028935185</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>45230.60619212963</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>44867.83456018518</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>45149</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>45189</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>45489</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>45190</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>45786.3628125</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>45408.42273148148</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>45615</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>45754.5805787037</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>45786.36038194445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>45625</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>45706.64979166666</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44368.48412037037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>45069.67789351852</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>44302.60905092592</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>45786.35825231481</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45547.5259375</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45785.85196759259</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>45785.87679398148</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>45673.35722222222</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>45572.50128472222</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>45665.30042824074</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45369.55871527778</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>44315.61856481482</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45534.67787037037</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45727.55368055555</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>44957</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>44957.56633101852</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32610,7 +32610,7 @@
         <v>44982.82561342593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45189</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45698.47010416666</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>45357.56929398148</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>45301</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>44833.86636574074</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>44300.37375</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>45695.44407407408</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44120</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>45401.55627314815</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>44333.63303240741</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>45075</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45773</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>45013.59971064814</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45628</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>45367.30908564815</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>45253</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>45552.43833333333</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>45260</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>45246.69150462963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45370</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>44609.62754629629</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45149.53783564815</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>45791.46207175926</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>45440</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>45082</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>44973</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>45092.3869675926</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>45761.36119212963</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45106.66513888889</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45111</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>45547.44084490741</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>45791.45240740741</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>45790.8237962963</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44999</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44596.39430555556</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45792.4578587963</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>45792.46865740741</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>44882</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>44841</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>45121</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>45792.46319444444</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>45049</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>45222.46246527778</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45575.40405092593</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>45792.46534722222</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35267,7 +35267,7 @@
         <v>45701.1425</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45761.54658564815</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35381,7 +35381,7 @@
         <v>45121</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>45072.49364583333</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44364</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>45470.66217592593</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45796.54754629629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44959</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>45366.36186342593</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44839</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45260</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>45369.51451388889</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>45093.41260416667</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44351</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45463</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>45093</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45121.62556712963</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45561</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>45561</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>45166.81506944444</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>44697</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>45754.57903935185</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>44746.52041666667</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45346.58555555555</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36707,7 +36707,7 @@
         <v>44992.53199074074</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>45439.56545138889</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45534.39119212963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>45409.28716435185</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>44882</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36992,7 +36992,7 @@
         <v>45561</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45561</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45075</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>44928.58678240741</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>44690.55664351852</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37277,7 +37277,7 @@
         <v>45572.55528935185</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>45070</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>45188</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44778.47969907407</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45244</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>44881.47697916667</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>45478.47974537037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>45740.58935185185</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>44869.44665509259</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>45154.46340277778</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>45664</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>44873.78972222222</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45798.38493055556</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>44867.83100694444</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45338.3546412037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>45484.50075231482</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>44908</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>45155</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45407.33482638889</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38370,7 +38370,7 @@
         <v>45084.52010416667</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>45798.87049768519</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>44973.68172453704</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>44959</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>45442.44923611111</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>45336</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45525.37091435185</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>44844</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>45079.47167824074</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45315</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45341.43773148148</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45805</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>45446.57478009259</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45509.84324074074</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45510.39084490741</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>44713.63434027778</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44949.39141203704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45367.29472222222</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45635.46313657407</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>45063</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>45254.55388888889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>45475.72082175926</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>45475.76681712963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>44959.60054398148</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>44825.37355324074</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>45188</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>44308</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45852.64087962963</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45666.41087962963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45810.50623842593</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>45702.52855324074</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>45169.63607638889</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>44497</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45554</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>44915.64974537037</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45744.34409722222</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45602</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>45763.38137731481</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45394.64731481481</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45363.79693287037</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>44075</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45525.33855324074</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>44721</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45071</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>44903.63063657407</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>44453</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45368.71136574074</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45369.51261574074</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>45772.56983796296</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44390</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>44368.47782407407</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>45117.52946759259</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>45356.37466435185</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>44853.58972222222</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45175.79483796296</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>44890.45898148148</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45078</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>44953</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45335</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45335</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>44951.40828703704</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45218.41752314815</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45429.32715277778</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>45331.60153935185</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45561.61627314815</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45093</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>45078</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45832</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42281,7 +42281,7 @@
         <v>44816</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>45852.67128472222</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>45670.48837962963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45812.31928240741</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45223</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45813.61375</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>44928</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45414.88950231481</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44307.41146990741</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45812.58846064815</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45812.59289351852</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45210.43765046296</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45813.61592592593</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45813.61734953704</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>45653.66523148148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>45561.42905092592</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>44713.6349537037</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>44497.23909722222</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>45545</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45734.48820601852</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45385</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45757.42518518519</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>45091.44643518519</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45856.43209490741</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>45668.61670138889</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45856.42729166667</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43793,7 +43793,7 @@
         <v>44889</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>45754.58637731482</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45111.56173611111</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43969,7 +43969,7 @@
         <v>45131</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44026,7 +44026,7 @@
         <v>45856.4249537037</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45859.46207175926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>44756</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45063.42767361111</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45240.48289351852</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44321,7 +44321,7 @@
         <v>44874.3702662037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>44914.47359953704</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>44914.5846875</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>45818</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>44931.48902777778</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>44183</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>45818.33222222222</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>45096</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>45119.35530092593</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45359.64494212963</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>45818</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44953,7 +44953,7 @@
         <v>45819</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>45863.79833333333</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45067,7 +45067,7 @@
         <v>45862.62265046296</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45124,7 +45124,7 @@
         <v>45863.78525462963</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>45863.79356481481</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45238,7 +45238,7 @@
         <v>45820.40359953704</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45279</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>45104.47891203704</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>45820</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>45820.4099537037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>44368</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>45821.48188657407</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>44677</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45862.61716435185</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>45198.49947916667</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45579</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45880,7 +45880,7 @@
         <v>45820.40600694445</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45820.43005787037</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45478</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45825.38628472222</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>45301.31474537037</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46170,7 +46170,7 @@
         <v>45301.32008101852</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45824.57248842593</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45596.73567129629</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45728.71716435185</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>45517.57674768518</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>45824.63803240741</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>45649.56231481482</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46574,7 +46574,7 @@
         <v>45649.56582175926</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>45775</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45824.47503472222</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45512.32738425926</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>44742</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45824.56317129629</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46926,7 +46926,7 @@
         <v>44832.45126157408</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>44340.37858796296</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45359.64686342593</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>44713.63319444445</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47216,7 +47216,7 @@
         <v>44382</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>44917.52387731482</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>45103</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>45096</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>45694.35719907407</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47506,7 +47506,7 @@
         <v>45590.48756944444</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47563,7 +47563,7 @@
         <v>44390.44760416666</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45754.4484375</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>44270</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>44798</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>44593</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45873.50734953704</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>45648</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47977,7 +47977,7 @@
         <v>45098</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48034,7 +48034,7 @@
         <v>45831.28561342593</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48091,7 +48091,7 @@
         <v>45392.56177083333</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48148,7 +48148,7 @@
         <v>44746.56648148148</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>45603</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>45191.43909722222</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>45833.63016203704</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45056</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>44865.32546296297</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48495,7 +48495,7 @@
         <v>44839</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>45217.64325231482</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>45832</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48666,7 +48666,7 @@
         <v>45118</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48723,7 +48723,7 @@
         <v>45145</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>45145.57739583333</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>45118.44516203704</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48894,7 +48894,7 @@
         <v>45579</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>45434.42591435185</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49008,7 +49008,7 @@
         <v>45833.62319444444</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45163.48395833333</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45834.48547453704</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45834.48055555556</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45182</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45056.72038194445</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49350,7 +49350,7 @@
         <v>45544.7580787037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>44827</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>44819</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>44973.28375</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>44407.33692129629</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49640,7 +49640,7 @@
         <v>45016.44748842593</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>45834.42243055555</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>44867</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         <v>44528.68445601852</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>45744.58425925926</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49925,7 +49925,7 @@
         <v>44825</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49982,7 +49982,7 @@
         <v>45091.44322916667</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>45169.62481481482</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50096,7 +50096,7 @@
         <v>45754.57761574074</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50158,7 +50158,7 @@
         <v>45233</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>45103.42912037037</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50277,7 +50277,7 @@
         <v>45103.4578125</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>45653.6771875</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50391,7 +50391,7 @@
         <v>45095</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50448,7 +50448,7 @@
         <v>45834.42037037037</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         <v>45834.49290509259</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>45098</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50619,7 +50619,7 @@
         <v>45244</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>45744.33675925926</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50733,7 +50733,7 @@
         <v>45342.93295138889</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>45881.43982638889</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>45321.30368055555</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>45649.63702546297</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50966,7 +50966,7 @@
         <v>45880.32877314815</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>45211</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51080,7 +51080,7 @@
         <v>45213.83515046296</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>44868</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51194,7 +51194,7 @@
         <v>45762.6184375</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>45629.52961805555</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51308,7 +51308,7 @@
         <v>45367.31642361111</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45880.33408564814</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>45135</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>44945.47278935185</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>44333.68109953704</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51593,7 +51593,7 @@
         <v>44275.89116898148</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45773</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         <v>45685.44299768518</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51764,7 +51764,7 @@
         <v>45873</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>45837.43159722222</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51878,7 +51878,7 @@
         <v>45837.45643518519</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45072.49809027778</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45244</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52049,7 +52049,7 @@
         <v>45841.34291666667</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52106,7 +52106,7 @@
         <v>45840.8866087963</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>45882.68247685185</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52220,7 +52220,7 @@
         <v>45211.43076388889</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52277,7 +52277,7 @@
         <v>44999.51451388889</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52334,7 +52334,7 @@
         <v>45567</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52396,7 +52396,7 @@
         <v>45188.35988425926</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52453,7 +52453,7 @@
         <v>45644.49726851852</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52510,7 +52510,7 @@
         <v>45762.47326388889</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>45840.36429398148</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
         <v>45883.58712962963</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52686,7 +52686,7 @@
         <v>45883.60289351852</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52743,7 +52743,7 @@
         <v>45882.68072916667</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52800,7 +52800,7 @@
         <v>45637.55811342593</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52857,7 +52857,7 @@
         <v>44431</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52914,7 +52914,7 @@
         <v>44811.50899305556</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>45616.69401620371</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53028,7 +53028,7 @@
         <v>45887.44094907407</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53085,7 +53085,7 @@
         <v>45713.67922453704</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53147,7 +53147,7 @@
         <v>45616.66118055556</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53204,7 +53204,7 @@
         <v>45616.68453703704</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53261,7 +53261,7 @@
         <v>45714.24815972222</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53318,7 +53318,7 @@
         <v>45842.47361111111</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>45096</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>45342.93903935186</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53489,7 +53489,7 @@
         <v>44368.48951388889</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>45225</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>45817.4940625</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>45216</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>44909.49190972222</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>44991.4569212963</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53831,7 +53831,7 @@
         <v>44910</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53888,7 +53888,7 @@
         <v>45603</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53945,7 +53945,7 @@
         <v>45156.75122685185</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54002,7 +54002,7 @@
         <v>45069.42486111111</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>44236</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>45679</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>44973.68408564815</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>44566</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>45373.4965625</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>45770.36494212963</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>44684.43402777778</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54458,7 +54458,7 @@
         <v>45764</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54515,7 +54515,7 @@
         <v>45764</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>45846.46805555555</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>44974.39552083334</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45057</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45057</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54800,7 +54800,7 @@
         <v>45210</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54857,7 +54857,7 @@
         <v>45888.41995370371</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54914,7 +54914,7 @@
         <v>44909</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54971,7 +54971,7 @@
         <v>44909.51342592593</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55028,7 +55028,7 @@
         <v>44431</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55085,7 +55085,7 @@
         <v>45846.47327546297</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55142,7 +55142,7 @@
         <v>45622.7463425926</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55199,7 +55199,7 @@
         <v>45668.48770833333</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55256,7 +55256,7 @@
         <v>45702.63559027778</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>44351.66695601852</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55375,7 +55375,7 @@
         <v>45888.65425925926</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>44972</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55489,7 +55489,7 @@
         <v>45156.74657407407</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>44231.57006944445</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55608,7 +55608,7 @@
         <v>45606.57791666667</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55665,7 +55665,7 @@
         <v>45849.46460648148</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55722,7 +55722,7 @@
         <v>44866.62503472222</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>44755</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55836,7 +55836,7 @@
         <v>44594.37378472222</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55893,7 +55893,7 @@
         <v>44992.52833333334</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>44335</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45849.47482638889</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56064,7 +56064,7 @@
         <v>45373.43667824074</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45085.55108796297</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56178,7 +56178,7 @@
         <v>45705.37840277778</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56235,7 +56235,7 @@
         <v>45891.37724537037</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56292,7 +56292,7 @@
         <v>45551.45940972222</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56349,7 +56349,7 @@
         <v>45628</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>45177</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56468,7 +56468,7 @@
         <v>45475.70619212963</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56525,7 +56525,7 @@
         <v>44386.57552083334</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56582,7 +56582,7 @@
         <v>44910</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56639,7 +56639,7 @@
         <v>45205.32967592592</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>45217.49613425926</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>44463.49472222223</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>45761.60565972222</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56867,7 +56867,7 @@
         <v>45174.32129629629</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45385.47306712963</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56981,7 +56981,7 @@
         <v>44376</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57038,7 +57038,7 @@
         <v>45011</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>44645.61398148148</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57152,7 +57152,7 @@
         <v>45401.70074074074</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57209,7 +57209,7 @@
         <v>45400.70824074074</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57266,7 +57266,7 @@
         <v>45239</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57323,7 +57323,7 @@
         <v>45089</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57385,7 +57385,7 @@
         <v>45737.66273148148</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57442,7 +57442,7 @@
         <v>44462</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57499,7 +57499,7 @@
         <v>44463.49251157408</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>45079</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57613,7 +57613,7 @@
         <v>45429.49690972222</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57670,7 +57670,7 @@
         <v>44798</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57727,7 +57727,7 @@
         <v>45231</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57784,7 +57784,7 @@
         <v>45610.49638888889</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57841,7 +57841,7 @@
         <v>45055.32497685185</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57898,7 +57898,7 @@
         <v>45730.29663194445</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>45744.56760416667</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58012,7 +58012,7 @@
         <v>45713</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58069,7 +58069,7 @@
         <v>45714.28113425926</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58126,7 +58126,7 @@
         <v>45762.62880787037</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58183,7 +58183,7 @@
         <v>45664.89855324074</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>45616.70280092592</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>45253</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58354,7 +58354,7 @@
         <v>45411.56006944444</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>45191.39680555555</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58473,7 +58473,7 @@
         <v>45710.35591435185</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -567,7 +567,7 @@
         <v>44460.70982638889</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44606</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45810.50783564815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45189</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45616</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>44490</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44370</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>45352.45320601852</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>44112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>44867</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>45888.34414351852</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>45888.42650462963</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45735.34555555556</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44347</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>44145</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>44266</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45093.3646875</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>45093.3703587963</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45695.93653935185</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>45358.44835648148</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45447</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>45428.42564814815</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45652.74018518518</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45222</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45730.63277777778</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>44785.43395833333</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45832</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>44937</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45174.32886574074</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>45853</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>44120</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>45075</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>44175</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>44375</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44602</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>45042</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>45695.93015046296</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>45103</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45596.52869212963</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45594</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>45307</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>45110</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44504.50979166666</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44656</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>44448.31037037037</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>45541.51222222222</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45701.45335648148</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>45721.65631944445</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44909</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>44966.64579861111</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45449.38423611111</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>45621.63548611111</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44648</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44917</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>44917</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45621.64417824074</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>45615.62699074074</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>44365</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45215</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>45096</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45850.60619212963</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>45316</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>45863.39380787037</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>44980</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>45581.56951388889</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>45621.64115740741</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>45604.50471064815</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>44120</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45840.8834375</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>45873</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45846.4975</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45891.63179398148</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>45754.48619212963</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44073</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44074</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44347</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44261</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44130</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44378</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44110.43048611111</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44073.7496875</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44179</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44120</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44183</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44224</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44230</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>44272</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44300.3625</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>44385.40346064815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44123</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44208</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>44491</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>44363.76037037037</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44407.34103009259</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>44120</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>44278</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>44201</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>44462</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44267.32773148148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44407.35815972222</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>44630</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>44089</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>44320</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>44418.56681712963</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44236</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>44379</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44225</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44297</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44342.65030092592</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>44194</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>44365</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>44071</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>44363.75403935185</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>44889.52459490741</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>44302</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>44474</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44138</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>44137.79510416667</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>44412</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>44859</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>44102</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44164</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>44861</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>44475</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44246</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44245</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44365</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44473.51576388889</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>44362</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>44581</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44587</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>44449.57666666667</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>44656</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>44844</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>44816</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>44571.48392361111</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44612</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44152</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>44645.61962962963</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>44187</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>44088</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>44201</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44130</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44565</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44256</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>44365</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>44312.52064814815</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>44691</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>44088</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>44593.58975694444</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>44131</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>44831.51668981482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44840</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44179</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44365</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44375.42613425926</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44369</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44566</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44328</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44684</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44347</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44365</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44306</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44315.67481481482</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44806.30436342592</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44364.69368055555</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44493.7688425926</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44488.93328703703</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44362</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44217.63880787037</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>44833.85800925926</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>44083</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>44078</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>44386.50282407407</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44468.38931712963</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44587</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>44624.4716087963</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>44593</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>44294.69576388889</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44449.61309027778</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>44449</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44169</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>44172</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>44419</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44321.32876157408</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44295.56511574074</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44340.37452546296</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>44851</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>44284</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>44363.75775462963</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>44136</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44259</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>44073</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>44776.4441087963</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>44378.27100694444</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44870.4825462963</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>44650</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44384</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>44211</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44137</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44223</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>44839.34592592593</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>44351</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>44748.39954861111</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44771.403125</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44449.61662037037</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44594.37494212963</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44629</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44494</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44365</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44593</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44183</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>44378.26744212963</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>44881.46946759259</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>44634</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>44634</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>44218</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>44418</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>44727</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>44796</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>44075</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>44370.25283564815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>44657</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>44551.60501157407</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>44805.72581018518</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44243.24046296296</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>44104.58186342593</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>44112</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>44250</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44375</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>44161</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>44299.65049768519</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>44183</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>44300.5134375</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>44270.62047453703</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>44593</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>44092</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>44160</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>44593</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>44612.64552083334</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>44813.46402777778</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>44407.33940972222</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>44169</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>44207.56376157407</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44225</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>44363.75042824074</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>44526.31395833333</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>44449</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>44089</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>44617.57709490741</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>44376</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>44551</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>44376.47229166667</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>44375.39068287037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>44870.4822337963</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>44785.35797453704</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44587</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44578.49199074074</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44445</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44407.35585648148</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44407.35945601852</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>44209</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44222</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>45474.54547453704</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45273.43420138889</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45649.57708333333</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45649.58368055556</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45649.63318287037</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45341</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44551</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>44508</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>44246</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45687.58510416667</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>45762.406875</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45022</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>44785.36618055555</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>45113</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>44917</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>44938.4812962963</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45775.61712962963</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45560.66090277778</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>44880.27605324074</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>44488</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>45177</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>45649.55618055556</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>45649.59947916667</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>44867</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44853</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>44224</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45089.45716435185</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45208</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>45280.75414351852</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45758.47427083334</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45517.5049074074</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>44580.39465277778</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45727.54988425926</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45488.44295138889</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45534.65803240741</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45702.63752314815</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45342.58545138889</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45082.42459490741</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45591.31592592593</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45043</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45616.69777777778</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45484.50256944444</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45426.64987268519</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>44489</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45050</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45330</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45706.59305555555</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45103.4828125</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45107</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45123.42461805556</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44974.3628125</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>45162</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>44936.7375925926</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45392.56559027778</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45572.49996527778</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45756.46728009259</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>44700.52403935185</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45230.60807870371</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45092.3945949074</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>44819</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>44693.40193287037</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44739</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44622</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45240.54020833333</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44419</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44083</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>45054</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>45664.88829861111</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>44494.39315972223</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45091.44966435185</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45603</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45606.57449074074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45296</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45278</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>44865</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45744.35152777778</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45412</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>45187.45348379629</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44586.39371527778</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44984</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>45075</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45761.7169212963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45762.37043981482</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>44657</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44904</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45181</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44973.87971064815</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44348</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>44544.63826388889</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>44295</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>44933.42714120371</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45775.59509259259</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>44985.4822337963</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>44798.56335648148</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>45733.60050925926</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>44266.66663194444</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>45415.32408564815</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>44977</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>44977.54047453704</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45721</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45035</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>44909</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45090.53722222222</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>44621</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>44579.36934027778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>45392.59135416667</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44749</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>45372.34578703704</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44818</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44973.8353125</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44803</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45175</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>45762.40821759259</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45308.45605324074</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>44692</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>45577.88273148148</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>44904</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>44904</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45758.65511574074</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>45560.65891203703</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45079.49798611111</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45149.52997685185</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45763</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>45561</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45197</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45469.49331018519</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>45307</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45394.66318287037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45210</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>44881</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>45175</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>44369</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45028.64141203704</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44418</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>45175.80216435185</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45728.71802083333</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45478.55826388889</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45371.47248842593</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45727</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>44743</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45763</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>44594</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>44939.46715277778</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>45320.32636574074</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45762.38605324074</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>45111.3095949074</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>44966.65418981481</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>44966.65623842592</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45021</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45741.39699074074</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>44298.33628472222</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45681</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26736,7 +26736,7 @@
         <v>45668.49403935186</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>44882</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45702.6415625</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45313</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45079</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45733.27633101852</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45376.57670138889</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45379</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>45037</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45090.50210648148</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>45679</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45327.3969212963</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>45756.4618287037</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>45342.58582175926</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>44908</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>45561</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>45177</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>45327</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>45090.57193287037</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45110</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>45720.48189814815</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>45078</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45013.53428240741</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>45586</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45754.58804398148</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45737.66959490741</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>45653</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>44505</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>44900.47381944444</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45072</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45253</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>44465.45304398148</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>44606.73197916667</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45713</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45545.46103009259</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>45449.73532407408</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>44223</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28875,7 +28875,7 @@
         <v>44223</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>44973.51290509259</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>45407.58145833333</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45070</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>45177</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45601.6175</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45728.58208333333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>44277</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45476.37739583333</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>45489.67844907408</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>44243</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29512,7 +29512,7 @@
         <v>44909.50149305556</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>44909.51041666666</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>45587.39587962963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>44494.38530092593</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45448.40923611111</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>45118</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>44970.82792824074</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45750.40939814815</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>44594</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45763</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>45477.45034722222</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>45551.45708333333</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45224.64084490741</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>44868.38045138889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45729.53497685185</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45785.57039351852</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45785.33315972222</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>45785.5658912037</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>45596.74167824074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>45728.57760416667</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>44866.6291550926</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45107.72561342592</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>45022.47684027778</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45077</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30890,7 +30890,7 @@
         <v>45196.41028935185</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>45230.60619212963</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>44867.83456018518</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>45149</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>45189</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>45489</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>45190</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>45786.3628125</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>45408.42273148148</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>45615</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>45754.5805787037</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>45786.36038194445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>45625</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>45706.64979166666</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44368.48412037037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>45069.67789351852</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>44302.60905092592</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>45786.35825231481</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45547.5259375</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45785.85196759259</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>45785.87679398148</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>45673.35722222222</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>45572.50128472222</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>45665.30042824074</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45369.55871527778</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>44315.61856481482</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45534.67787037037</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45727.55368055555</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>44957</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>44957.56633101852</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32610,7 +32610,7 @@
         <v>44982.82561342593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45189</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45698.47010416666</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>45357.56929398148</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>45301</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>44833.86636574074</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>44300.37375</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>45695.44407407408</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44120</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>45401.55627314815</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>44333.63303240741</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>45075</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45773</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>45013.59971064814</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45628</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>45367.30908564815</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>45253</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>45552.43833333333</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>45260</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>45246.69150462963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45370</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>44609.62754629629</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45149.53783564815</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>45791.46207175926</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>45440</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>45082</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>44973</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>45092.3869675926</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>45761.36119212963</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45106.66513888889</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45111</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>45547.44084490741</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>45791.45240740741</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>45790.8237962963</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44999</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44596.39430555556</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45792.4578587963</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>45792.46865740741</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>44882</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>44841</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>45121</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>45792.46319444444</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>45049</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>45222.46246527778</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45575.40405092593</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>45792.46534722222</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35267,7 +35267,7 @@
         <v>45701.1425</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45761.54658564815</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35381,7 +35381,7 @@
         <v>45121</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>45072.49364583333</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>44364</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>45470.66217592593</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45796.54754629629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44959</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>45366.36186342593</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44839</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45260</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>45369.51451388889</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>45093.41260416667</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44351</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45463</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>45093</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45121.62556712963</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45561</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>45561</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>45166.81506944444</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>44697</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>45754.57903935185</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>44746.52041666667</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45346.58555555555</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36707,7 +36707,7 @@
         <v>44992.53199074074</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>45439.56545138889</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45534.39119212963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>45409.28716435185</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>44882</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36992,7 +36992,7 @@
         <v>45561</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45561</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45075</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>44928.58678240741</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>44690.55664351852</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37277,7 +37277,7 @@
         <v>45572.55528935185</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>45070</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>45188</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44778.47969907407</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45244</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>44881.47697916667</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>45478.47974537037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>45740.58935185185</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>44869.44665509259</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>45154.46340277778</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>45664</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>44873.78972222222</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45798.38493055556</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>44867.83100694444</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45338.3546412037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>45484.50075231482</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>44908</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>45155</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45407.33482638889</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38370,7 +38370,7 @@
         <v>45084.52010416667</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>45798.87049768519</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>44973.68172453704</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>44959</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>45442.44923611111</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>45336</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45525.37091435185</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>44844</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>45079.47167824074</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45315</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45341.43773148148</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45805</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>45446.57478009259</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45509.84324074074</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45510.39084490741</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>44713.63434027778</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44949.39141203704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45367.29472222222</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45635.46313657407</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>45063</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>45254.55388888889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>45475.72082175926</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>45475.76681712963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>44959.60054398148</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>44825.37355324074</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>45188</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>44308</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45852.64087962963</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45666.41087962963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45810.50623842593</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>45702.52855324074</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>45169.63607638889</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>44497</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45554</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>44915.64974537037</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45744.34409722222</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45602</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>45763.38137731481</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45394.64731481481</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45363.79693287037</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>44075</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45525.33855324074</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>44721</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45071</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>44903.63063657407</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>44453</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45368.71136574074</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45369.51261574074</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>45772.56983796296</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44390</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>44368.47782407407</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>45117.52946759259</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>45356.37466435185</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>44853.58972222222</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45175.79483796296</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>44890.45898148148</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45078</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>44953</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45335</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45335</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>44951.40828703704</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45218.41752314815</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45429.32715277778</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>45331.60153935185</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45561.61627314815</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45093</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>45078</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45832</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42281,7 +42281,7 @@
         <v>44816</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>45852.67128472222</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>45670.48837962963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45812.31928240741</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45223</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45813.61375</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>44928</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45414.88950231481</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44307.41146990741</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45812.58846064815</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45812.59289351852</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45210.43765046296</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45813.61592592593</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45813.61734953704</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>45653.66523148148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>45561.42905092592</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>44713.6349537037</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>44497.23909722222</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>45545</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45734.48820601852</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45385</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45757.42518518519</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>45091.44643518519</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45856.43209490741</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>45668.61670138889</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45856.42729166667</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43793,7 +43793,7 @@
         <v>44889</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>45754.58637731482</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45111.56173611111</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43969,7 +43969,7 @@
         <v>45131</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44026,7 +44026,7 @@
         <v>45856.4249537037</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45859.46207175926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>44756</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45063.42767361111</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>45240.48289351852</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44321,7 +44321,7 @@
         <v>44874.3702662037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>44914.47359953704</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>44914.5846875</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>45818</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>44931.48902777778</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>44183</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>45818.33222222222</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>45096</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>45119.35530092593</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45359.64494212963</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>45818</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44953,7 +44953,7 @@
         <v>45819</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>45863.79833333333</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45067,7 +45067,7 @@
         <v>45862.62265046296</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45124,7 +45124,7 @@
         <v>45863.78525462963</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>45863.79356481481</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45238,7 +45238,7 @@
         <v>45820.40359953704</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45279</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>45104.47891203704</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>45820</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>45820.4099537037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>44368</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>45821.48188657407</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>44677</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45862.61716435185</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>45198.49947916667</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45579</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45880,7 +45880,7 @@
         <v>45820.40600694445</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45820.43005787037</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45478</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45825.38628472222</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>45301.31474537037</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46170,7 +46170,7 @@
         <v>45301.32008101852</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45824.57248842593</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45596.73567129629</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45728.71716435185</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>45517.57674768518</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>45824.63803240741</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>45649.56231481482</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46574,7 +46574,7 @@
         <v>45649.56582175926</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>45775</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45824.47503472222</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45512.32738425926</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>44742</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45824.56317129629</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46926,7 +46926,7 @@
         <v>44832.45126157408</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>44340.37858796296</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45359.64686342593</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>44713.63319444445</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47216,7 +47216,7 @@
         <v>44382</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>44917.52387731482</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>45103</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>45096</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>45694.35719907407</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47506,7 +47506,7 @@
         <v>45590.48756944444</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47563,7 +47563,7 @@
         <v>44390.44760416666</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45754.4484375</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>44270</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>44798</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>44593</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45873.50734953704</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>45648</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47977,7 +47977,7 @@
         <v>45098</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48034,7 +48034,7 @@
         <v>45831.28561342593</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48091,7 +48091,7 @@
         <v>45392.56177083333</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48148,7 +48148,7 @@
         <v>44746.56648148148</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>45603</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>45191.43909722222</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>45833.63016203704</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45056</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>44865.32546296297</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48495,7 +48495,7 @@
         <v>44839</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>45217.64325231482</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>45832</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48666,7 +48666,7 @@
         <v>45118</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48723,7 +48723,7 @@
         <v>45145</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>45145.57739583333</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>45118.44516203704</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48894,7 +48894,7 @@
         <v>45579</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>45434.42591435185</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49008,7 +49008,7 @@
         <v>45833.62319444444</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45163.48395833333</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45834.48547453704</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45834.48055555556</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45182</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45056.72038194445</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49350,7 +49350,7 @@
         <v>45544.7580787037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>44827</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>44819</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>44973.28375</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>44407.33692129629</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49640,7 +49640,7 @@
         <v>45016.44748842593</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>45834.42243055555</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>44867</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         <v>44528.68445601852</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>45744.58425925926</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49925,7 +49925,7 @@
         <v>44825</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49982,7 +49982,7 @@
         <v>45091.44322916667</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>45169.62481481482</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50096,7 +50096,7 @@
         <v>45754.57761574074</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50158,7 +50158,7 @@
         <v>45233</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>45103.42912037037</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50277,7 +50277,7 @@
         <v>45103.4578125</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>45653.6771875</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50391,7 +50391,7 @@
         <v>45095</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50448,7 +50448,7 @@
         <v>45834.42037037037</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         <v>45834.49290509259</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>45098</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50619,7 +50619,7 @@
         <v>45244</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>45744.33675925926</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50733,7 +50733,7 @@
         <v>45342.93295138889</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>45881.43982638889</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>45321.30368055555</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>45649.63702546297</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50966,7 +50966,7 @@
         <v>45880.32877314815</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>45211</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51080,7 +51080,7 @@
         <v>45213.83515046296</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>44868</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51194,7 +51194,7 @@
         <v>45762.6184375</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>45629.52961805555</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51308,7 +51308,7 @@
         <v>45367.31642361111</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45880.33408564814</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>45135</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>44945.47278935185</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>44333.68109953704</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51593,7 +51593,7 @@
         <v>44275.89116898148</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45773</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         <v>45685.44299768518</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51764,7 +51764,7 @@
         <v>45873</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>45837.43159722222</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51878,7 +51878,7 @@
         <v>45837.45643518519</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45072.49809027778</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45244</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52049,7 +52049,7 @@
         <v>45841.34291666667</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52106,7 +52106,7 @@
         <v>45840.8866087963</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>45882.68247685185</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52220,7 +52220,7 @@
         <v>45211.43076388889</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52277,7 +52277,7 @@
         <v>44999.51451388889</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52334,7 +52334,7 @@
         <v>45567</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52396,7 +52396,7 @@
         <v>45188.35988425926</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52453,7 +52453,7 @@
         <v>45644.49726851852</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52510,7 +52510,7 @@
         <v>45762.47326388889</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>45840.36429398148</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
         <v>45883.58712962963</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52686,7 +52686,7 @@
         <v>45883.60289351852</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52743,7 +52743,7 @@
         <v>45882.68072916667</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52800,7 +52800,7 @@
         <v>45637.55811342593</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52857,7 +52857,7 @@
         <v>44431</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52914,7 +52914,7 @@
         <v>44811.50899305556</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>45616.69401620371</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53028,7 +53028,7 @@
         <v>45887.44094907407</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53085,7 +53085,7 @@
         <v>45713.67922453704</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53147,7 +53147,7 @@
         <v>45616.66118055556</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53204,7 +53204,7 @@
         <v>45616.68453703704</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53261,7 +53261,7 @@
         <v>45714.24815972222</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53318,7 +53318,7 @@
         <v>45842.47361111111</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>45096</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>45342.93903935186</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53489,7 +53489,7 @@
         <v>44368.48951388889</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>45225</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>45817.4940625</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>45216</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>44909.49190972222</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>44991.4569212963</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53831,7 +53831,7 @@
         <v>44910</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53888,7 +53888,7 @@
         <v>45603</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53945,7 +53945,7 @@
         <v>45156.75122685185</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54002,7 +54002,7 @@
         <v>45069.42486111111</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>44236</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>45679</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>44973.68408564815</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>44566</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>45373.4965625</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>45770.36494212963</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>44684.43402777778</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54458,7 +54458,7 @@
         <v>45764</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54515,7 +54515,7 @@
         <v>45764</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>45846.46805555555</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>44974.39552083334</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45057</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45057</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54800,7 +54800,7 @@
         <v>45210</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54857,7 +54857,7 @@
         <v>45888.41995370371</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54914,7 +54914,7 @@
         <v>44909</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54971,7 +54971,7 @@
         <v>44909.51342592593</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55028,7 +55028,7 @@
         <v>44431</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55085,7 +55085,7 @@
         <v>45846.47327546297</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55142,7 +55142,7 @@
         <v>45622.7463425926</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55199,7 +55199,7 @@
         <v>45668.48770833333</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55256,7 +55256,7 @@
         <v>45702.63559027778</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>44351.66695601852</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55375,7 +55375,7 @@
         <v>45888.65425925926</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>44972</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55489,7 +55489,7 @@
         <v>45156.74657407407</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>44231.57006944445</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55608,7 +55608,7 @@
         <v>45606.57791666667</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55665,7 +55665,7 @@
         <v>45849.46460648148</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55722,7 +55722,7 @@
         <v>44866.62503472222</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>44755</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55836,7 +55836,7 @@
         <v>44594.37378472222</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55893,7 +55893,7 @@
         <v>44992.52833333334</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>44335</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45849.47482638889</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56064,7 +56064,7 @@
         <v>45373.43667824074</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45085.55108796297</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56178,7 +56178,7 @@
         <v>45705.37840277778</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56235,7 +56235,7 @@
         <v>45891.37724537037</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56292,7 +56292,7 @@
         <v>45551.45940972222</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56349,7 +56349,7 @@
         <v>45628</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>45177</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56468,7 +56468,7 @@
         <v>45475.70619212963</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56525,7 +56525,7 @@
         <v>44386.57552083334</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56582,7 +56582,7 @@
         <v>44910</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56639,7 +56639,7 @@
         <v>45205.32967592592</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>45217.49613425926</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>44463.49472222223</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>45761.60565972222</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56867,7 +56867,7 @@
         <v>45174.32129629629</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45385.47306712963</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56981,7 +56981,7 @@
         <v>44376</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57038,7 +57038,7 @@
         <v>45011</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>44645.61398148148</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57152,7 +57152,7 @@
         <v>45401.70074074074</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57209,7 +57209,7 @@
         <v>45400.70824074074</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57266,7 +57266,7 @@
         <v>45239</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57323,7 +57323,7 @@
         <v>45089</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57385,7 +57385,7 @@
         <v>45737.66273148148</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57442,7 +57442,7 @@
         <v>44462</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57499,7 +57499,7 @@
         <v>44463.49251157408</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>45079</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57613,7 +57613,7 @@
         <v>45429.49690972222</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57670,7 +57670,7 @@
         <v>44798</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57727,7 +57727,7 @@
         <v>45231</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57784,7 +57784,7 @@
         <v>45610.49638888889</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57841,7 +57841,7 @@
         <v>45055.32497685185</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57898,7 +57898,7 @@
         <v>45730.29663194445</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>45744.56760416667</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58012,7 +58012,7 @@
         <v>45713</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58069,7 +58069,7 @@
         <v>45714.28113425926</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58126,7 +58126,7 @@
         <v>45762.62880787037</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58183,7 +58183,7 @@
         <v>45664.89855324074</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>45616.70280092592</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>45253</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58354,7 +58354,7 @@
         <v>45411.56006944444</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>45191.39680555555</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58473,7 +58473,7 @@
         <v>45710.35591435185</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -567,7 +567,7 @@
         <v>44460.70982638889</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44606</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45810.50783564815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45616</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45189</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>45898.5890625</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>44490</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>44370</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45735.34555555556</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>44112</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>45352.45320601852</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>45888.34414351852</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>45888.42650462963</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44867</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44347</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>44145</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>44266</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45174.32886574074</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45652.74018518518</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>45447</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45428.42564814815</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>45730.63277777778</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>45695.93653935185</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45075</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>44120</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45358.44835648148</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>44785.43395833333</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45093.3646875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>45093.3703587963</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>45832</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>45853</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44937</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45222</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>44175</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44375</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>44602</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>45721.65631944445</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45215</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>45541.51222222222</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45096</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44909</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>45701.45335648148</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>45316</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44504.50979166666</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>45594</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45042</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>44648</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44120</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>45621.64417824074</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>45103</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>45863.39380787037</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45449.38423611111</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>45110</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>45621.64115740741</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44448.31037037037</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>45581.56951388889</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44656</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>45621.63548611111</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45754.48619212963</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>45873</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>45840.8834375</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>45846.4975</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45307</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>45850.60619212963</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>45894.56163194445</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45891.63179398148</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>45894.64087962963</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44917</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>44365</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>45604.50471064815</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>44966.64579861111</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44917</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>45695.93015046296</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45615.62699074074</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>44980</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>44073</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44074</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44261</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>44347</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>44179</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>44378</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>44073.7496875</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44130</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>44110.43048611111</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>44120</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>44183</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>44224</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>44230</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>44300.3625</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44385.40346064815</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>44123</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>44208</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>44491</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>44120</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>44278</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44407.34103009259</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>44363.76037037037</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>44267.32773148148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>44201</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>44462</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44407.35815972222</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44379</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>44089</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>44418.56681712963</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>44320</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>44236</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>44225</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>44342.65030092592</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>44297</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>44194</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44365</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44363.75403935185</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44889.52459490741</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>44302</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>44691</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>44138</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>44474</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>44137.79510416667</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>44412</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>44859</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>44102</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44164</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44861</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>44475</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>44246</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44245</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>44365</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>44473.51576388889</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44362</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44587</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44581</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44449.57666666667</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44656</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>44844</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>44816</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>44571.48392361111</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>44612</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>44152</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>44645.61962962963</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>44187</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44201</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44088</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>44088</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>44565</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>44256</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>44130</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44312.52064814815</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>44365</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>44593.58975694444</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>44131</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>44831.51668981482</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>44840</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>44783</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>44179</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>44365</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>44375.42613425926</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>44369</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>44566</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>44328</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>44684</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>44347</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>44365</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>44306</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>44315.67481481482</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>44806.30436342592</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>44364.69368055555</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44493.7688425926</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>44488.93328703703</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44362</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44833.85800925926</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44217.63880787037</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>44083</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>44078</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>44386.50282407407</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>44468.38931712963</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44587</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44624.4716087963</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>44593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44294.69576388889</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>44449.61309027778</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44449</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44169</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44172</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44419</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>44321.32876157408</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>44295.56511574074</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44340.37452546296</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>44363.75775462963</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>44284</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>44259</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>44776.4441087963</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44870.4825462963</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44073</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>44384</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>44378.27100694444</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>44650</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>44449.61662037037</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>44351</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44594.37494212963</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>44629</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>44494</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>44211</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>44137</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>44748.39954861111</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44771.403125</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>44593</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>44223</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>44839.34592592593</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>44378.26744212963</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>44881.46946759259</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>44365</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44418</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>44183</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44796</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>44075</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>44370.25283564815</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>44634</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>44634</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>44218</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44657</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>44727</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>44551.60501157407</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>44104.58186342593</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>44112</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>44375</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>44805.72581018518</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>44161</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>44243.24046296296</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>44250</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>44270.62047453703</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>44612.64552083334</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>44299.65049768519</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>44407.33940972222</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>44183</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>44593</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44300.5134375</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>44449</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>44813.46402777778</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>44092</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44617.57709490741</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>44160</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>44169</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44207.56376157407</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>44593</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>44363.75042824074</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>44526.31395833333</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>44225</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>44089</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>44376.47229166667</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>44551</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>44508</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>44246</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>44375.39068287037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>44785.35797453704</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>44578.49199074074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>44376</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>44551</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>44445</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>44407.35585648148</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>44407.35945601852</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>44870.4822337963</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>44136</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>44587</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>44853</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>45572.49996527778</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44419</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>45510.39084490741</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>44851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>44222</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>45713</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45702.52855324074</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>45091.44322916667</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>45190</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>45579</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>44839</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44866.62503472222</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>44866.6291550926</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>44755</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         <v>44867</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>44505</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>45216</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>45341.43773148148</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45118.44516203704</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>44266.66663194444</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45773</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45121</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45280.75414351852</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45075</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45253</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45123.42461805556</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>45762.6184375</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>44270</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45342.93903935186</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>44827</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>44376</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>44348</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45679</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45043</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45054</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>45363.79693287037</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>44295</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45117.52946759259</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45336</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>45434.42591435185</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>45713</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>45714.28113425926</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45649.55618055556</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>45649.59947916667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20700,7 +20700,7 @@
         <v>45649.63702546297</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>45217.64325231482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45762.62880787037</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45622.7463425926</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>44999</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>45078</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45666.41087962963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45702.63752314815</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45084.52010416667</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45181</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>44307.41146990741</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45093</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45070</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>44277</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>44606.73197916667</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45551.45940972222</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45561.42905092592</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>44489</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45601.6175</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>45449.73532407408</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45545.46103009259</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45476.37739583333</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45079.47167824074</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>44890.45898148148</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45489.67844907408</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>45103.4578125</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45103.4828125</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44453</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45107.72561342592</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>44465.45304398148</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>45376.57670138889</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>44953</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45440</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>44868.38045138889</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45156.75122685185</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45149.53783564815</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45754.58804398148</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>44407.33692129629</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>45104.47891203704</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>45469.49331018519</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45587.39587962963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45478.55826388889</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45786.36038194445</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45665.30042824074</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45392.56559027778</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45785.85196759259</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45706.64979166666</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>45698.47010416666</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45547.5259375</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45572.50128472222</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>44867.83456018518</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>44300.37375</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44315.61856481482</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45230.60619212963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45359.64686342593</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45370</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>45246.69150462963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45253</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45357.56929398148</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45155</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>45429.32715277778</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>44839</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44910</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>45367.30908564815</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45785.57039351852</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>45673.35722222222</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45785.5658912037</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44938.4812962963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45301</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>45625</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>45489</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>44973.51290509259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>44973</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45770.36494212963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45785.33315972222</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>44973.68172453704</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>45786.35825231481</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45744.56760416667</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45260</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>45401.55627314815</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45785.87679398148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>45786.3628125</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>45534.67787037037</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>44982.82561342593</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45233</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>44957</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>44957.56633101852</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45616.69777777778</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45096</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>45791.46207175926</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45579</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45474.54547453704</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45790.8237962963</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>45169.62481481482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>44580.39465277778</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44333.68109953704</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45792.46319444444</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>45792.46534722222</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>45079</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>45791.45240740741</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>45792.4578587963</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>45792.46865740741</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>45320.32636574074</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45113</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>45796.54754629629</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>45701.1425</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45342.58545138889</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>44528.68445601852</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>45118</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45131</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>45763</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45534.39119212963</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>45773</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>45315</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>45761.54658564815</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>45016.44748842593</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>45561.61627314815</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>44566</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>44596.39430555556</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45092.3945949074</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>45798.38493055556</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45668.61670138889</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>45341</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45197</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>45475.72082175926</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45475.76681712963</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>45603</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>45729.53497685185</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>44915.64974537037</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>45035</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>45798.87049768519</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>44697</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45545</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44972</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44832.45126157408</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
         <v>44908</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>45218.41752314815</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45169.63607638889</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>45089.45716435185</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45551.45708333333</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>44488</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>45338.3546412037</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>45525.37091435185</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>45560.66090277778</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>44914.5846875</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45547.44084490741</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>45805</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>44645.61398148148</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45544.7580787037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45478.47974537037</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>44904</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45727.54988425926</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>45727</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>45713.67922453704</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45714.24815972222</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>45442.44923611111</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>45602</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>45664.89855324074</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>44677</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29828,7 +29828,7 @@
         <v>45373.43667824074</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45327</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45063</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>45082</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45810.50623842593</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>45191.39680555555</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>44959</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45517.57674768518</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45744.58425925926</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45812.58846064815</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>45812.59289351852</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>44351</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>44657</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45664</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>44928</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45812.31928240741</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>44594</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>45049</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44120</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>44622</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>45813.61592592593</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45813.61734953704</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>44544.63826388889</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>44959.60054398148</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45813.61375</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>45224.64084490741</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45177</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45758.47427083334</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31469,7 +31469,7 @@
         <v>45637.55811342593</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>44692</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>45818.33222222222</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>45561</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45561</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45859.46207175926</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>44917.52387731482</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45408.42273148148</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45072.49809027778</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44992.53199074074</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>45577.88273148148</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45098</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>45664.88829861111</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45820.4099537037</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>44873.78972222222</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45762.47326388889</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>45820.40359953704</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45819</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45754.57761574074</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45118</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>45818</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>45818</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>44209</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45820.40600694445</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>45820.43005787037</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>45392.56177083333</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>45862.62265046296</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>45145</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>45862.61716435185</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>45145.57739583333</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45653</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>45820</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>44593</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45863.79833333333</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45824.57248842593</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>45196.41028935185</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>45821.48188657407</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>45824.47503472222</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45335</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>45863.78525462963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>45863.79356481481</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>45222.46246527778</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45824.63803240741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45478</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44973.87971064815</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>45385</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45824.56317129629</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>44833.86636574074</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44910</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>45825.38628472222</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>44973.28375</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>44690.55664351852</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>45754.58637731482</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>45762.38605324074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45572.55528935185</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45372.34578703704</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45037</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>45685.44299768518</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>44684.43402777778</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45615</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>44939.46715277778</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45223</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>45230.60807870371</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>45367.31642361111</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45182</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45720.48189814815</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>45175</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>45093</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>44867.83100694444</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>44970.82792824074</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>44966.65418981481</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>44966.65623842592</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>45702.6415625</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45191.43909722222</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>45831.28561342593</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>45244</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>45741.39699074074</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45832</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>45873.50734953704</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>45596.73567129629</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45756.4618287037</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>45764</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45764</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>45833.62319444444</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>45095</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>45737.66273148148</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>45834.48055555556</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45695.44407407408</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>45733.27633101852</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>45834.42243055555</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>45211</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>44223</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>44223</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>44713.63434027778</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>45834.48547453704</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45187.45348379629</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>45702.63559027778</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>45415.32408564815</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>45071</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>44368.48412037037</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45586</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45439.56545138889</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45407.33482638889</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45239</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>44742</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45740.58935185185</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45177</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>44909</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37777,7 +37777,7 @@
         <v>45833.63016203704</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45175</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44825.37355324074</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45070</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>45367.29472222222</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>45198.49947916667</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>45411.56006944444</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>45211.43076388889</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>45757.42518518519</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>45225</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44224</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>45834.49290509259</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44749</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>45834.42037037037</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44713.6349537037</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45121.62556712963</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45121</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>44746.56648148148</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>44721</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44275.89116898148</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45873</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45880.32877314815</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44798.56335648148</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44743</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45307</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45628</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>45359.64494212963</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45880.33408564814</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45837.43159722222</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45837.45643518519</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>45750.40939814815</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>45089</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>45175.79483796296</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45629.52961805555</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>44931.48902777778</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44231.57006944445</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39849,7 +39849,7 @@
         <v>45882.68247685185</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>45106.66513888889</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>45561</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40020,7 +40020,7 @@
         <v>45561</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45881.43982638889</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45734.48820601852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45882.68072916667</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45414.88950231481</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45754.5805787037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45756.46728009259</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45744.34409722222</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>44909.51041666666</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45840.36429398148</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45883.58712962963</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45883.60289351852</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45840.8866087963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>45244</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>44841</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>45775.61712962963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>44803</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         <v>44693.40193287037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>45448.40923611111</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41118,7 +41118,7 @@
         <v>44739</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>44746.52041666667</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45254.55388888889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         <v>45841.34291666667</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>45330</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>45057</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45057</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41517,7 +41517,7 @@
         <v>44497</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>45842.47361111111</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>44819</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>44974.39552083334</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>45887.44094907407</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>45616.69401620371</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>45888.65425925926</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>45379</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45366.36186342593</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45189</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>45022.47684027778</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>44335</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>45681</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>45846.47327546297</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45817.4940625</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>45846.46805555555</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42439,7 +42439,7 @@
         <v>45217.49613425926</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>44917</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>44368</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>44351.66695601852</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42672,7 +42672,7 @@
         <v>45616.66118055556</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>45616.68453703704</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45730.29663194445</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>45253</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>45888.41995370371</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>45754.4484375</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>44959</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45210.43765046296</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45475.70619212963</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45273.43420138889</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>44819</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>45301.31474537037</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45301.32008101852</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43423,7 +43423,7 @@
         <v>45763.38137731481</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45763</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>45327.3969212963</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>44999.51451388889</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45177</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>44298.33628472222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>45888</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45705.37840277778</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>44333.63303240741</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>45744.35152777778</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>45891.37724537037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>44340.37858796296</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45092.3869675926</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45849.47482638889</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>45346.58555555555</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44293,7 +44293,7 @@
         <v>45628</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
         <v>45728.57760416667</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>45894.57494212963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44474,7 +44474,7 @@
         <v>45894.63583333333</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45894.63924768518</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44598,7 +44598,7 @@
         <v>45894.64207175926</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45849.46460648148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45894.45178240741</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45616.70280092592</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45852.67128472222</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>45278</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45090.53722222222</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>45894.63353009259</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>45894.63461805556</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45126,7 +45126,7 @@
         <v>45610.49638888889</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>45852.64087962963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45240,7 +45240,7 @@
         <v>45894.45385416667</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>44756</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45359,7 +45359,7 @@
         <v>45091.44966435185</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>45894.55900462963</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>45894.57186342592</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>44868</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45597,7 +45597,7 @@
         <v>45727.55368055555</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>45706.59305555555</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>45728.71802083333</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>45119.35530092593</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>44075</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45882,7 +45882,7 @@
         <v>44621</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45939,7 +45939,7 @@
         <v>44936.7375925926</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>45832</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46053,7 +46053,7 @@
         <v>45484.50075231482</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46110,7 +46110,7 @@
         <v>45484.50256944444</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46167,7 +46167,7 @@
         <v>44865.32546296297</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>45409.28716435185</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45772.56983796296</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>45694.35719907407</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>44308</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45856.42729166667</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46514,7 +46514,7 @@
         <v>45856.43209490741</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>44302.60905092592</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         <v>44985.4822337963</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46690,7 +46690,7 @@
         <v>45898.59107638889</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46752,7 +46752,7 @@
         <v>45894</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46809,7 +46809,7 @@
         <v>45856.4249537037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45463</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>45534.65803240741</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>45022</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>45394.66318287037</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45653.66523148148</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>45154.46340277778</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47223,7 +47223,7 @@
         <v>45090.50210648148</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         <v>45342.93295138889</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>44390.44760416666</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47399,7 +47399,7 @@
         <v>45400.70824074074</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47456,7 +47456,7 @@
         <v>45111.3095949074</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47513,7 +47513,7 @@
         <v>44390</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45552.43833333333</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47627,7 +47627,7 @@
         <v>44382</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47684,7 +47684,7 @@
         <v>45231</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47741,7 +47741,7 @@
         <v>44369</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47798,7 +47798,7 @@
         <v>44909</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47855,7 +47855,7 @@
         <v>44973.8353125</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>44386.57552083334</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47969,7 +47969,7 @@
         <v>44364</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>45687.58510416667</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44818</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48140,7 +48140,7 @@
         <v>45369.55871527778</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48197,7 +48197,7 @@
         <v>45762.406875</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48259,7 +48259,7 @@
         <v>44243</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>44945.47278935185</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>44494.39315972223</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>45775.59509259259</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48487,7 +48487,7 @@
         <v>45728.71716435185</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48544,7 +48544,7 @@
         <v>45733.60050925926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48601,7 +48601,7 @@
         <v>44991.4569212963</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48658,7 +48658,7 @@
         <v>44904</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>45554</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         <v>45174.32129629629</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48834,7 +48834,7 @@
         <v>45335</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>44816</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48953,7 +48953,7 @@
         <v>45762.40821759259</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>44992.52833333334</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>44881</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>44844</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49186,7 +49186,7 @@
         <v>45744.33675925926</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>44462</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49300,7 +49300,7 @@
         <v>44463.49251157408</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>45509.84324074074</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49414,7 +49414,7 @@
         <v>45189</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49476,7 +49476,7 @@
         <v>44579.36934027778</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>44418</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>44928.58678240741</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         <v>44594.37378472222</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>44933.42714120371</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49761,7 +49761,7 @@
         <v>44977</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>44977.54047453704</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49875,7 +49875,7 @@
         <v>45728.58208333333</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49937,7 +49937,7 @@
         <v>44881.47697916667</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49994,7 +49994,7 @@
         <v>44700.52403935185</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>45072.49364583333</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50108,7 +50108,7 @@
         <v>45188</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45244</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>45072</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45371.47248842593</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>44914.47359953704</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>44889</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45135</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45055.32497685185</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>44083</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>44497.23909722222</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>44949.39141203704</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45111.56173611111</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         <v>45761.7169212963</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>45762.37043981482</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50916,7 +50916,7 @@
         <v>45775</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45512.32738425926</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>45567</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45426.64987268519</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45260</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45188.35988425926</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>44869.44665509259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>45763</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>44909.49190972222</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>44798</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>45385.47306712963</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>45056.72038194445</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>44236</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>44431</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>44431</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45606.57791666667</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45710.35591435185</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45075</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>45188</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45603</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>44874.3702662037</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>45077</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>45013.53428240741</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52237,7 +52237,7 @@
         <v>45090.57193287037</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52294,7 +52294,7 @@
         <v>44609.62754629629</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>44900.47381944444</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45213.83515046296</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>44882</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>44904</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45210</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45296</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52693,7 +52693,7 @@
         <v>45754.57903935185</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45596.74167824074</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>44984</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>45082.42459490741</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52926,7 +52926,7 @@
         <v>45107</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52983,7 +52983,7 @@
         <v>44909.51342592593</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53040,7 +53040,7 @@
         <v>44825</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53097,7 +53097,7 @@
         <v>45342.58582175926</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53154,7 +53154,7 @@
         <v>45091.44643518519</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53211,7 +53211,7 @@
         <v>45648</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53268,7 +53268,7 @@
         <v>45096</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53325,7 +53325,7 @@
         <v>45103</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53382,7 +53382,7 @@
         <v>44494.38530092593</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53439,7 +53439,7 @@
         <v>45098</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53496,7 +53496,7 @@
         <v>44463.49472222223</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53553,7 +53553,7 @@
         <v>45575.40405092593</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53610,7 +53610,7 @@
         <v>44183</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53667,7 +53667,7 @@
         <v>45392.59135416667</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>45063.42767361111</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53781,7 +53781,7 @@
         <v>44798</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>45156.74657407407</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53895,7 +53895,7 @@
         <v>45313</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>45561</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>45069.67789351852</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>45761.36119212963</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>44853.58972222222</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>45470.66217592593</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45021</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45079</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45394.64731481481</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45446.57478009259</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>45368.71136574074</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>45369.51261574074</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45111</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45668.48770833333</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45668.49403935186</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>44713.63319444445</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>44908</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>44974.3628125</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>45079.49798611111</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45208</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         <v>45078</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45525.33855324074</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45590.48756944444</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>45175.80216435185</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>44973.68408564815</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45078</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         <v>45488.44295138889</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         <v>45050</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>45401.70074074074</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55563,7 +55563,7 @@
         <v>45149.52997685185</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>45075</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55677,7 +55677,7 @@
         <v>45679</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         <v>44951.40828703704</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55791,7 +55791,7 @@
         <v>44880.27605324074</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>45758.65511574074</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>45737.66959490741</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         <v>45606.57449074074</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56019,7 +56019,7 @@
         <v>44586.39371527778</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56076,7 +56076,7 @@
         <v>45093.41260416667</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>45761.60565972222</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56190,7 +56190,7 @@
         <v>45517.5049074074</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45162</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>44865</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>44909.50149305556</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56418,7 +56418,7 @@
         <v>45085.55108796297</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56475,7 +56475,7 @@
         <v>45308.45605324074</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         <v>45649.57708333333</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56589,7 +56589,7 @@
         <v>45649.58368055556</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         <v>45649.63318287037</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>45240.48289351852</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56760,7 +56760,7 @@
         <v>44785.36618055555</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56817,7 +56817,7 @@
         <v>45011</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
         <v>45210</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56931,7 +56931,7 @@
         <v>45110</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56993,7 +56993,7 @@
         <v>45649.56231481482</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57050,7 +57050,7 @@
         <v>45649.56582175926</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57107,7 +57107,7 @@
         <v>45591.31592592593</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57164,7 +57164,7 @@
         <v>45635.46313657407</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57221,7 +57221,7 @@
         <v>45670.48837962963</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>45028.64141203704</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57340,7 +57340,7 @@
         <v>44811.50899305556</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57397,7 +57397,7 @@
         <v>44867</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57454,7 +57454,7 @@
         <v>45429.49690972222</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57511,7 +57511,7 @@
         <v>44594</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57568,7 +57568,7 @@
         <v>45331.60153935185</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57625,7 +57625,7 @@
         <v>45022</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57682,7 +57682,7 @@
         <v>45177</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57744,7 +57744,7 @@
         <v>44778.47969907407</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57801,7 +57801,7 @@
         <v>45056</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57858,7 +57858,7 @@
         <v>45149</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57915,7 +57915,7 @@
         <v>45561</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57977,7 +57977,7 @@
         <v>45205.32967592592</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>44882</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>45721</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58148,7 +58148,7 @@
         <v>45103.42912037037</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58205,7 +58205,7 @@
         <v>45240.54020833333</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58262,7 +58262,7 @@
         <v>44903.63063657407</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58319,7 +58319,7 @@
         <v>45279</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58376,7 +58376,7 @@
         <v>45477.45034722222</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58433,7 +58433,7 @@
         <v>44368.48951388889</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58490,7 +58490,7 @@
         <v>45407.58145833333</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58547,7 +58547,7 @@
         <v>45412</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58604,7 +58604,7 @@
         <v>44882</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>44368.47782407407</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58718,7 +58718,7 @@
         <v>45069.42486111111</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>45163.48395833333</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>45373.4965625</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58889,7 +58889,7 @@
         <v>45369.51451388889</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         <v>45356.37466435185</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         <v>45166.81506944444</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>45321.30368055555</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>45013.59971064814</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59174,7 +59174,7 @@
         <v>45560.65891203703</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         <v>45653.6771875</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45603</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         <v>45644.49726851852</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         <v>45096</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -567,7 +567,7 @@
         <v>44460.70982638889</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44606</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45810.50783564815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45616</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>45189</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>45898.5890625</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>44490</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>44370</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45735.34555555556</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>44112</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>45352.45320601852</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>45888.34414351852</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>45888.42650462963</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44867</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44347</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>44145</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>44266</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45174.32886574074</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45652.74018518518</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>45447</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45428.42564814815</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>45730.63277777778</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>45695.93653935185</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45075</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>44120</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45358.44835648148</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>44785.43395833333</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45093.3646875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>45093.3703587963</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>45832</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>45853</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44937</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45222</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>44175</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44375</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>44602</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>45721.65631944445</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45215</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>45541.51222222222</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45096</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44909</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>45701.45335648148</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>45316</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44504.50979166666</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>45594</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45042</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>44648</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44120</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>45621.64417824074</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>45103</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>45863.39380787037</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45449.38423611111</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>45110</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>45621.64115740741</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44448.31037037037</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>45581.56951388889</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44656</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>45621.63548611111</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45754.48619212963</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>45873</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>45840.8834375</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>45846.4975</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45307</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>45850.60619212963</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>45894.56163194445</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45891.63179398148</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>45894.64087962963</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44917</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>44365</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>45604.50471064815</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>44966.64579861111</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44917</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>45695.93015046296</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45615.62699074074</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>44980</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>44073</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44074</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44261</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>44347</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>44179</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>44378</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>44073.7496875</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44130</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>44110.43048611111</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>44120</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>44183</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>44224</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>44230</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>44300.3625</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44385.40346064815</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>44123</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>44208</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>44491</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>44120</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>44278</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44407.34103009259</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>44363.76037037037</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>44267.32773148148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>44201</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>44462</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44407.35815972222</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44379</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>44089</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>44418.56681712963</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>44320</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>44236</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>44225</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>44342.65030092592</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>44297</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>44194</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44365</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44363.75403935185</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44889.52459490741</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>44302</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>44691</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>44138</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>44474</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>44137.79510416667</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>44412</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>44859</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>44102</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44164</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44861</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>44475</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>44246</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44245</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>44365</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>44473.51576388889</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44362</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44587</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44581</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44449.57666666667</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44656</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>44844</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>44816</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>44571.48392361111</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>44612</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>44152</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>44645.61962962963</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>44187</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44201</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44088</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>44088</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>44565</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>44256</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>44130</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44312.52064814815</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>44365</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>44593.58975694444</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>44131</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>44831.51668981482</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>44840</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>44783</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>44179</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>44365</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>44375.42613425926</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>44369</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>44566</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>44328</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>44684</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>44347</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>44365</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>44306</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>44315.67481481482</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>44806.30436342592</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>44364.69368055555</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44493.7688425926</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>44488.93328703703</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44362</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44833.85800925926</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44217.63880787037</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>44083</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>44078</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>44386.50282407407</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>44468.38931712963</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44587</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44624.4716087963</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>44593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44294.69576388889</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>44449.61309027778</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44449</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44169</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44172</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44419</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>44321.32876157408</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>44295.56511574074</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44340.37452546296</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>44363.75775462963</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>44284</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>44259</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>44776.4441087963</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44870.4825462963</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44073</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>44384</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>44378.27100694444</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>44650</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>44449.61662037037</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>44351</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44594.37494212963</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>44629</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>44494</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>44211</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>44137</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>44748.39954861111</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44771.403125</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>44593</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>44223</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>44839.34592592593</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>44378.26744212963</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>44881.46946759259</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>44365</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44418</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>44183</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44796</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>44075</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>44370.25283564815</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>44634</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>44634</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>44218</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44657</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>44727</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>44551.60501157407</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>44104.58186342593</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>44112</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>44375</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>44805.72581018518</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>44161</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>44243.24046296296</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>44250</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>44270.62047453703</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>44612.64552083334</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>44299.65049768519</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>44407.33940972222</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>44183</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>44593</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44300.5134375</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>44449</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>44813.46402777778</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>44092</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44617.57709490741</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>44160</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>44169</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44207.56376157407</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>44593</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>44363.75042824074</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>44526.31395833333</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>44225</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>44089</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>44376.47229166667</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>44551</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>44508</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>44246</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>44375.39068287037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>44785.35797453704</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>44578.49199074074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>44376</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>44551</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>44445</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>44407.35585648148</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>44407.35945601852</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>44870.4822337963</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>44136</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>44587</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>44853</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>45572.49996527778</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44419</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>45510.39084490741</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>44851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>44222</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>45713</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45702.52855324074</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>45091.44322916667</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>45190</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>45579</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>44839</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44866.62503472222</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>44866.6291550926</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>44755</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         <v>44867</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>44505</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>45216</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>45341.43773148148</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45118.44516203704</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>44266.66663194444</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45773</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45121</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45280.75414351852</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45075</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45253</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45123.42461805556</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>45762.6184375</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>44270</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45342.93903935186</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>44827</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>44376</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>44348</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45679</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45043</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45054</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>45363.79693287037</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>44295</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45117.52946759259</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45336</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>45434.42591435185</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>45713</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>45714.28113425926</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45649.55618055556</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>45649.59947916667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20700,7 +20700,7 @@
         <v>45649.63702546297</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>45217.64325231482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45762.62880787037</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45622.7463425926</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>44999</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>45078</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45666.41087962963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45702.63752314815</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45084.52010416667</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45181</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>44307.41146990741</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45093</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45070</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>44277</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>44606.73197916667</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45551.45940972222</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45561.42905092592</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>44489</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45601.6175</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>45449.73532407408</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45545.46103009259</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45476.37739583333</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45079.47167824074</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>44890.45898148148</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45489.67844907408</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>45103.4578125</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45103.4828125</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44453</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45107.72561342592</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>44465.45304398148</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>45376.57670138889</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>44953</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45440</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>44868.38045138889</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45156.75122685185</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45149.53783564815</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45754.58804398148</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>44407.33692129629</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>45104.47891203704</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>45469.49331018519</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45587.39587962963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45478.55826388889</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45786.36038194445</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45665.30042824074</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45392.56559027778</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45785.85196759259</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45706.64979166666</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>45698.47010416666</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45547.5259375</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45572.50128472222</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>44867.83456018518</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>44300.37375</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44315.61856481482</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45230.60619212963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45359.64686342593</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45370</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>45246.69150462963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45253</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45357.56929398148</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45155</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>45429.32715277778</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>44839</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44910</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>45367.30908564815</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45785.57039351852</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>45673.35722222222</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45785.5658912037</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44938.4812962963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45301</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>45625</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>45489</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>44973.51290509259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>44973</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45770.36494212963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45785.33315972222</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>44973.68172453704</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>45786.35825231481</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45744.56760416667</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45260</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>45401.55627314815</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45785.87679398148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>45786.3628125</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>45534.67787037037</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>44982.82561342593</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45233</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>44957</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>44957.56633101852</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45616.69777777778</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45096</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>45791.46207175926</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45579</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45474.54547453704</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45790.8237962963</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>45169.62481481482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>44580.39465277778</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44333.68109953704</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45792.46319444444</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>45792.46534722222</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>45079</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>45791.45240740741</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>45792.4578587963</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>45792.46865740741</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>45320.32636574074</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45113</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>45796.54754629629</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>45701.1425</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45342.58545138889</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>44528.68445601852</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>45118</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45131</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>45763</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45534.39119212963</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>45773</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>45315</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>45761.54658564815</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>45016.44748842593</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>45561.61627314815</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>44566</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>44596.39430555556</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45092.3945949074</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>45798.38493055556</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45668.61670138889</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>45341</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45197</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>45475.72082175926</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45475.76681712963</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>45603</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>45729.53497685185</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>44915.64974537037</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>45035</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>45798.87049768519</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>44697</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45545</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44972</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44832.45126157408</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
         <v>44908</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>45218.41752314815</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45169.63607638889</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>45089.45716435185</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45551.45708333333</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>44488</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>45338.3546412037</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>45525.37091435185</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>45560.66090277778</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>44914.5846875</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45547.44084490741</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>45805</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>44645.61398148148</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45544.7580787037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45478.47974537037</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>44904</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45727.54988425926</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>45727</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>45713.67922453704</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45714.24815972222</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>45442.44923611111</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>45602</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>45664.89855324074</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>44677</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29828,7 +29828,7 @@
         <v>45373.43667824074</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45327</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45063</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>45082</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45810.50623842593</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>45191.39680555555</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>44959</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45517.57674768518</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45744.58425925926</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45812.58846064815</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>45812.59289351852</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>44351</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>44657</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45664</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>44928</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45812.31928240741</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>44594</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>45049</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44120</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>44622</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>45813.61592592593</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45813.61734953704</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>44544.63826388889</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>44959.60054398148</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45813.61375</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>45224.64084490741</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45177</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45758.47427083334</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31469,7 +31469,7 @@
         <v>45637.55811342593</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>44692</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>45818.33222222222</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>45561</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45561</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45859.46207175926</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>44917.52387731482</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45408.42273148148</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45072.49809027778</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44992.53199074074</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>45577.88273148148</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45098</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>45664.88829861111</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45820.4099537037</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>44873.78972222222</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45762.47326388889</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>45820.40359953704</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45819</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45754.57761574074</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45118</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>45818</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>45818</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>44209</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45820.40600694445</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>45820.43005787037</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>45392.56177083333</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>45862.62265046296</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>45145</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>45862.61716435185</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>45145.57739583333</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45653</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>45820</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>44593</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45863.79833333333</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45824.57248842593</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>45196.41028935185</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>45821.48188657407</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>45824.47503472222</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45335</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>45863.78525462963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>45863.79356481481</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>45222.46246527778</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45824.63803240741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45478</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44973.87971064815</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>45385</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45824.56317129629</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>44833.86636574074</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44910</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>45825.38628472222</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>44973.28375</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>44690.55664351852</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>45754.58637731482</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>45762.38605324074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45572.55528935185</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45372.34578703704</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45037</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>45685.44299768518</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>44684.43402777778</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45615</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>44939.46715277778</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45223</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>45230.60807870371</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>45367.31642361111</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45182</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45720.48189814815</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>45175</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>45093</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>44867.83100694444</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>44970.82792824074</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>44966.65418981481</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>44966.65623842592</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>45702.6415625</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45191.43909722222</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>45831.28561342593</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>45244</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>45741.39699074074</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45832</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>45873.50734953704</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>45596.73567129629</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45756.4618287037</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>45764</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45764</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>45833.62319444444</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>45095</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36456,7 +36456,7 @@
         <v>45737.66273148148</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>45834.48055555556</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45695.44407407408</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>45733.27633101852</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>45834.42243055555</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>45211</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>44223</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>44223</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>44713.63434027778</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>45834.48547453704</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45187.45348379629</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>45702.63559027778</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>45415.32408564815</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>45071</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>44368.48412037037</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45586</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45439.56545138889</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45407.33482638889</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45239</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>44742</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45740.58935185185</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45177</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>44909</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37777,7 +37777,7 @@
         <v>45833.63016203704</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45175</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44825.37355324074</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45070</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>45367.29472222222</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>45198.49947916667</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>45411.56006944444</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>45211.43076388889</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>45757.42518518519</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>45225</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44224</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>45834.49290509259</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44749</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>45834.42037037037</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44713.6349537037</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45121.62556712963</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45121</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>44746.56648148148</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>44721</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44275.89116898148</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45873</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45880.32877314815</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44798.56335648148</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44743</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45307</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45628</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>45359.64494212963</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45880.33408564814</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45837.43159722222</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45837.45643518519</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>45750.40939814815</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>45089</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>45175.79483796296</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45629.52961805555</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>44931.48902777778</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44231.57006944445</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39849,7 +39849,7 @@
         <v>45882.68247685185</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>45106.66513888889</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>45561</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40020,7 +40020,7 @@
         <v>45561</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45881.43982638889</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45734.48820601852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45882.68072916667</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45414.88950231481</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45754.5805787037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45756.46728009259</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45744.34409722222</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>44909.51041666666</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45840.36429398148</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45883.58712962963</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45883.60289351852</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45840.8866087963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>45244</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>44841</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>45775.61712962963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>44803</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         <v>44693.40193287037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>45448.40923611111</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41118,7 +41118,7 @@
         <v>44739</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>44746.52041666667</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45254.55388888889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         <v>45841.34291666667</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>45330</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>45057</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45057</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41517,7 +41517,7 @@
         <v>44497</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>45842.47361111111</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>44819</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>44974.39552083334</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>45887.44094907407</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>45616.69401620371</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>45888.65425925926</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>45379</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45366.36186342593</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45189</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>45022.47684027778</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>44335</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>45681</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>45846.47327546297</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45817.4940625</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>45846.46805555555</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42439,7 +42439,7 @@
         <v>45217.49613425926</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>44917</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>44368</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>44351.66695601852</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42672,7 +42672,7 @@
         <v>45616.66118055556</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>45616.68453703704</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45730.29663194445</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>45253</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>45888.41995370371</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>45754.4484375</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>44959</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45210.43765046296</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45475.70619212963</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45273.43420138889</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>44819</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>45301.31474537037</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45301.32008101852</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43423,7 +43423,7 @@
         <v>45763.38137731481</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45763</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>45327.3969212963</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>44999.51451388889</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45177</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>44298.33628472222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>45888</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45705.37840277778</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>44333.63303240741</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>45744.35152777778</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>45891.37724537037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>44340.37858796296</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45092.3869675926</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45849.47482638889</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>45346.58555555555</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44293,7 +44293,7 @@
         <v>45628</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
         <v>45728.57760416667</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>45894.57494212963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44474,7 +44474,7 @@
         <v>45894.63583333333</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45894.63924768518</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44598,7 +44598,7 @@
         <v>45894.64207175926</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45849.46460648148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45894.45178240741</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45616.70280092592</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45852.67128472222</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>45278</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45090.53722222222</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>45894.63353009259</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>45894.63461805556</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45126,7 +45126,7 @@
         <v>45610.49638888889</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>45852.64087962963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45240,7 +45240,7 @@
         <v>45894.45385416667</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>44756</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45359,7 +45359,7 @@
         <v>45091.44966435185</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>45894.55900462963</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>45894.57186342592</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>44868</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45597,7 +45597,7 @@
         <v>45727.55368055555</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>45706.59305555555</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>45728.71802083333</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>45119.35530092593</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>44075</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45882,7 +45882,7 @@
         <v>44621</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45939,7 +45939,7 @@
         <v>44936.7375925926</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>45832</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46053,7 +46053,7 @@
         <v>45484.50075231482</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46110,7 +46110,7 @@
         <v>45484.50256944444</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46167,7 +46167,7 @@
         <v>44865.32546296297</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>45409.28716435185</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45772.56983796296</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>45694.35719907407</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>44308</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45856.42729166667</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46514,7 +46514,7 @@
         <v>45856.43209490741</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>44302.60905092592</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         <v>44985.4822337963</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46690,7 +46690,7 @@
         <v>45898.59107638889</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46752,7 +46752,7 @@
         <v>45894</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46809,7 +46809,7 @@
         <v>45856.4249537037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45463</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>45534.65803240741</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>45022</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>45394.66318287037</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45653.66523148148</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>45154.46340277778</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47223,7 +47223,7 @@
         <v>45090.50210648148</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         <v>45342.93295138889</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>44390.44760416666</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47399,7 +47399,7 @@
         <v>45400.70824074074</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47456,7 +47456,7 @@
         <v>45111.3095949074</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47513,7 +47513,7 @@
         <v>44390</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45552.43833333333</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47627,7 +47627,7 @@
         <v>44382</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47684,7 +47684,7 @@
         <v>45231</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47741,7 +47741,7 @@
         <v>44369</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47798,7 +47798,7 @@
         <v>44909</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47855,7 +47855,7 @@
         <v>44973.8353125</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>44386.57552083334</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47969,7 +47969,7 @@
         <v>44364</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>45687.58510416667</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44818</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48140,7 +48140,7 @@
         <v>45369.55871527778</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48197,7 +48197,7 @@
         <v>45762.406875</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48259,7 +48259,7 @@
         <v>44243</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>44945.47278935185</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>44494.39315972223</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>45775.59509259259</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48487,7 +48487,7 @@
         <v>45728.71716435185</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48544,7 +48544,7 @@
         <v>45733.60050925926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48601,7 +48601,7 @@
         <v>44991.4569212963</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48658,7 +48658,7 @@
         <v>44904</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>45554</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         <v>45174.32129629629</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48834,7 +48834,7 @@
         <v>45335</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>44816</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48953,7 +48953,7 @@
         <v>45762.40821759259</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>44992.52833333334</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>44881</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>44844</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49186,7 +49186,7 @@
         <v>45744.33675925926</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>44462</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49300,7 +49300,7 @@
         <v>44463.49251157408</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>45509.84324074074</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49414,7 +49414,7 @@
         <v>45189</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49476,7 +49476,7 @@
         <v>44579.36934027778</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>44418</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>44928.58678240741</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         <v>44594.37378472222</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>44933.42714120371</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49761,7 +49761,7 @@
         <v>44977</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>44977.54047453704</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49875,7 +49875,7 @@
         <v>45728.58208333333</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49937,7 +49937,7 @@
         <v>44881.47697916667</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49994,7 +49994,7 @@
         <v>44700.52403935185</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>45072.49364583333</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50108,7 +50108,7 @@
         <v>45188</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45244</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>45072</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45371.47248842593</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>44914.47359953704</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>44889</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45135</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45055.32497685185</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>44083</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>44497.23909722222</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>44949.39141203704</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45111.56173611111</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         <v>45761.7169212963</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>45762.37043981482</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50916,7 +50916,7 @@
         <v>45775</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45512.32738425926</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>45567</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45426.64987268519</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45260</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45188.35988425926</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>44869.44665509259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>45763</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>44909.49190972222</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>44798</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>45385.47306712963</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>45056.72038194445</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>44236</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>44431</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>44431</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45606.57791666667</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45710.35591435185</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45075</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>45188</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45603</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>44874.3702662037</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>45077</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>45013.53428240741</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52237,7 +52237,7 @@
         <v>45090.57193287037</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52294,7 +52294,7 @@
         <v>44609.62754629629</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>44900.47381944444</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45213.83515046296</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>44882</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>44904</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45210</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45296</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52693,7 +52693,7 @@
         <v>45754.57903935185</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45596.74167824074</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>44984</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>45082.42459490741</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52926,7 +52926,7 @@
         <v>45107</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52983,7 +52983,7 @@
         <v>44909.51342592593</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53040,7 +53040,7 @@
         <v>44825</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53097,7 +53097,7 @@
         <v>45342.58582175926</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53154,7 +53154,7 @@
         <v>45091.44643518519</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53211,7 +53211,7 @@
         <v>45648</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53268,7 +53268,7 @@
         <v>45096</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53325,7 +53325,7 @@
         <v>45103</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53382,7 +53382,7 @@
         <v>44494.38530092593</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53439,7 +53439,7 @@
         <v>45098</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53496,7 +53496,7 @@
         <v>44463.49472222223</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53553,7 +53553,7 @@
         <v>45575.40405092593</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53610,7 +53610,7 @@
         <v>44183</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53667,7 +53667,7 @@
         <v>45392.59135416667</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>45063.42767361111</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53781,7 +53781,7 @@
         <v>44798</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>45156.74657407407</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53895,7 +53895,7 @@
         <v>45313</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>45561</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54014,7 +54014,7 @@
         <v>45069.67789351852</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>45761.36119212963</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>44853.58972222222</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>45470.66217592593</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45021</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45079</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45394.64731481481</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45446.57478009259</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>45368.71136574074</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>45369.51261574074</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45111</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45668.48770833333</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45668.49403935186</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>44713.63319444445</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>44908</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>44974.3628125</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>45079.49798611111</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45208</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         <v>45078</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45525.33855324074</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45590.48756944444</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>45175.80216435185</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>44973.68408564815</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45078</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         <v>45488.44295138889</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         <v>45050</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>45401.70074074074</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55563,7 +55563,7 @@
         <v>45149.52997685185</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55620,7 +55620,7 @@
         <v>45075</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55677,7 +55677,7 @@
         <v>45679</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         <v>44951.40828703704</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55791,7 +55791,7 @@
         <v>44880.27605324074</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>45758.65511574074</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>45737.66959490741</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         <v>45606.57449074074</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56019,7 +56019,7 @@
         <v>44586.39371527778</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56076,7 +56076,7 @@
         <v>45093.41260416667</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>45761.60565972222</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56190,7 +56190,7 @@
         <v>45517.5049074074</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45162</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>44865</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>44909.50149305556</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56418,7 +56418,7 @@
         <v>45085.55108796297</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56475,7 +56475,7 @@
         <v>45308.45605324074</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         <v>45649.57708333333</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56589,7 +56589,7 @@
         <v>45649.58368055556</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         <v>45649.63318287037</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>45240.48289351852</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56760,7 +56760,7 @@
         <v>44785.36618055555</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56817,7 +56817,7 @@
         <v>45011</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
         <v>45210</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56931,7 +56931,7 @@
         <v>45110</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56993,7 +56993,7 @@
         <v>45649.56231481482</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57050,7 +57050,7 @@
         <v>45649.56582175926</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57107,7 +57107,7 @@
         <v>45591.31592592593</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57164,7 +57164,7 @@
         <v>45635.46313657407</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57221,7 +57221,7 @@
         <v>45670.48837962963</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>45028.64141203704</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57340,7 +57340,7 @@
         <v>44811.50899305556</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57397,7 +57397,7 @@
         <v>44867</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57454,7 +57454,7 @@
         <v>45429.49690972222</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57511,7 +57511,7 @@
         <v>44594</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57568,7 +57568,7 @@
         <v>45331.60153935185</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57625,7 +57625,7 @@
         <v>45022</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57682,7 +57682,7 @@
         <v>45177</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57744,7 +57744,7 @@
         <v>44778.47969907407</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57801,7 +57801,7 @@
         <v>45056</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57858,7 +57858,7 @@
         <v>45149</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57915,7 +57915,7 @@
         <v>45561</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57977,7 +57977,7 @@
         <v>45205.32967592592</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>44882</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>45721</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58148,7 +58148,7 @@
         <v>45103.42912037037</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58205,7 +58205,7 @@
         <v>45240.54020833333</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58262,7 +58262,7 @@
         <v>44903.63063657407</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58319,7 +58319,7 @@
         <v>45279</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58376,7 +58376,7 @@
         <v>45477.45034722222</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58433,7 +58433,7 @@
         <v>44368.48951388889</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58490,7 +58490,7 @@
         <v>45407.58145833333</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58547,7 +58547,7 @@
         <v>45412</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58604,7 +58604,7 @@
         <v>44882</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>44368.47782407407</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58718,7 +58718,7 @@
         <v>45069.42486111111</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>45163.48395833333</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>45373.4965625</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58889,7 +58889,7 @@
         <v>45369.51451388889</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         <v>45356.37466435185</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         <v>45166.81506944444</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>45321.30368055555</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>45013.59971064814</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59174,7 +59174,7 @@
         <v>45560.65891203703</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         <v>45653.6771875</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45603</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         <v>45644.49726851852</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         <v>45096</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -567,7 +567,7 @@
         <v>44460.70982638889</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>44606</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45810.50783564815</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>45898.5890625</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>45616</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45189</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44490</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>44370</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>45352.45320601852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>44112</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>44867</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45888.34414351852</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45888.42650462963</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45735.34555555556</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44347</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44145</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>44266</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45358.44835648148</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>45730.63277777778</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>45652.74018518518</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>45222</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>45621.63548611111</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44937</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45174.32886574074</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>44785.43395833333</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45853</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>45832</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>45894.64087962963</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>44120</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>45075</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>45093.3646875</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45093.3703587963</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>45447</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45695.93653935185</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>45428.42564814815</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>44175</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44375</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>44602</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>45594</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45541.51222222222</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45701.45335648148</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>45110</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>45103</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>44909</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44448.31037037037</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45721.65631944445</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45449.38423611111</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44966.64579861111</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44648</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44917</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>44917</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45615.62699074074</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>45215</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45621.64417824074</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>44365</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>45840.8834375</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45873</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>45316</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>45616.66118055556</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>45846.4975</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>45891.63179398148</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45894.56163194445</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>45894.64207175926</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>45850.60619212963</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45096</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44980</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>45581.56951388889</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45863.39380787037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45621.64115740741</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>45604.50471064815</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>44120</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45754.48619212963</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45042</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>45695.93015046296</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>45307</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>44504.50979166666</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>44656</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>44347</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44261</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44378</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>44120</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44179</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44183</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44130</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44110.43048611111</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>44224</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>44230</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>44272</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44300.3625</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>44385.40346064815</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44123</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>44208</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>44491</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44407.34103009259</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>44363.76037037037</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44267.32773148148</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44201</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44120</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44278</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44462</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44407.35815972222</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>44379</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44630</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44089</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>44418.56681712963</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>44320</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>44236</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>44225</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>44342.65030092592</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>44297</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>44194</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>44365</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44363.75403935185</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>44889.52459490741</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>44302</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44691</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>44138</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44474</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>44137.79510416667</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>44412</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>44859</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44102</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44164</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>44861</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44475</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>44246</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44245</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44365</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>44473.51576388889</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>44362</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>44581</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>44656</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44587</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44844</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44449.57666666667</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44816</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>44571.48392361111</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>44612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>44152</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44645.61962962963</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>44187</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44088</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44088</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>44201</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44565</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>44130</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>44256</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>44365</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>44312.52064814815</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>44593.58975694444</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>44131</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>44831.51668981482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>44840</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>44783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>44179</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>44365</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>44375.42613425926</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>44369</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>44566</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44684</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>44328</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>44347</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>44365</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>44306</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>44315.67481481482</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44806.30436342592</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>44364.69368055555</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>44493.7688425926</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>44488.93328703703</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>44362</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>44217.63880787037</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44833.85800925926</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44083</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>44386.50282407407</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>44468.38931712963</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>44587</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>44624.4716087963</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44593</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>44294.69576388889</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>44449.61309027778</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>44449</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>44169</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>44172</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>44419</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>44321.32876157408</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>44295.56511574074</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>44340.37452546296</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44284</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>44259</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>44776.4441087963</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>44363.75775462963</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44870.4825462963</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>44594.37494212963</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>44629</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>44494</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>44351</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>44211</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>44137</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>44748.39954861111</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44771.403125</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>44223</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>44839.34592592593</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>44365</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44593</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44378.26744212963</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>44881.46946759259</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>44218</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>44418</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>44183</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44657</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44796</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>44370.25283564815</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>44634</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>44634</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>44551.60501157407</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44727</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44104.58186342593</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>44112</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44375</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44161</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>44270.62047453703</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>44612.64552083334</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>44805.72581018518</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>44243.24046296296</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>44407.33940972222</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>44449</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>44250</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>44593</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>44183</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>44617.57709490741</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>44299.65049768519</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>44813.46402777778</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>44160</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>44300.5134375</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>44169</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>44207.56376157407</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>44092</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>44225</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>44593</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>44363.75042824074</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>44526.31395833333</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>44089</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>44785.35797453704</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>44376.47229166667</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17004,7 +17004,7 @@
         <v>44375.39068287037</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>44376</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>44551</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44136</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44870.4822337963</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44578.49199074074</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>44551</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>44508</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>44246</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>44445</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>44407.35585648148</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>44407.35945601852</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>44587</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44378.27100694444</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44650</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45230.60807870371</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>45092.3945949074</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>44819</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>44222</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>44853</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44851</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45054</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>45273.43420138889</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>45341</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>45091.44966435185</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>44384</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45606.57449074074</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>45278</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>44984</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45075</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>45687.58510416667</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>45022</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>44657</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45181</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>45762.38605324074</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>44973.87971064815</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>44966.65418981481</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>44966.65623842592</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44544.63826388889</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44295</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44449.61662037037</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44933.42714120371</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>45775.59509259259</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>45679</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44985.4822337963</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>45313</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>45586</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>45775.61712962963</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45737.66959490741</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>45079</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45253</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45733.27633101852</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44606.73197916667</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45545.46103009259</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45449.73532407408</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>45070</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>45601.6175</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>44277</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>45476.37739583333</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>45489.67844907408</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45090.50210648148</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45587.39587962963</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>44818</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45756.4618287037</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45342.58582175926</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>44692</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45577.88273148148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>44908</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45561</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45561</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>45177</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>45327</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45785.57039351852</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45307</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45785.33315972222</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45394.66318287037</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45785.5658912037</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45090.57193287037</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45110</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>45175</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45720.48189814815</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45028.64141203704</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45649.55618055556</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>45649.59947916667</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45078</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45013.53428240741</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>44224</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45763</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>45517.5049074074</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45727.54988425926</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45230.60619212963</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>44867.83456018518</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45754.58804398148</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>45111.3095949074</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45488.44295138889</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45021</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45082.42459490741</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45653</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>44505</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>44900.47381944444</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>45072</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44465.45304398148</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45668.49403935186</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>45713</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>45489</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>45786.3628125</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>44223</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>44223</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>45407.58145833333</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>45177</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45786.36038194445</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45625</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45706.64979166666</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>45786.35825231481</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45547.5259375</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>45785.85196759259</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>45785.87679398148</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>45673.35722222222</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>45572.50128472222</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>45665.30042824074</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>44315.61856481482</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>45534.67787037037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>44970.82792824074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45702.6415625</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45750.40939814815</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>45698.47010416666</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45357.56929398148</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>45301</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>44300.37375</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>45401.55627314815</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45763</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45367.30908564815</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>45253</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45376.57670138889</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45477.45034722222</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45551.45708333333</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>45224.64084490741</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>44489</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>44868.38045138889</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>45037</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45246.69150462963</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>45370</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45791.46207175926</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>45107</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45123.42461805556</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>45327.3969212963</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>45162</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45392.56559027778</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>45596.74167824074</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>45728.57760416667</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>44866.6291550926</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>45022.47684027778</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45077</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45196.41028935185</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>45791.45240740741</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>45790.8237962963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>45190</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>45408.42273148148</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45615</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45792.4578587963</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45792.46865740741</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44368.48412037037</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45069.67789351852</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>44973.51290509259</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45728.58208333333</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>45369.55871527778</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45727.55368055555</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>44957</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>44957.56633101852</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>45792.46319444444</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>45695.44407407408</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44333.63303240741</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>45013.59971064814</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45628</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45552.43833333333</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>44243</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>44909.50149305556</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>44909.51041666666</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45792.46534722222</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27307,7 +27307,7 @@
         <v>45701.1425</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45761.54658564815</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>45149.53783564815</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>44494.38530092593</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>45796.54754629629</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45440</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>45448.40923611111</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45082</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>44973</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45092.3869675926</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>45118</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44594</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>45729.53497685185</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>45107.72561342592</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44999</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44596.39430555556</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44697</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>44841</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>45149</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>45189</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>45121</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>45575.40405092593</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45754.5805787037</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44302.60905092592</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45072.49364583333</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>45022</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>45470.66217592593</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>44959</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>44982.82561342593</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45798.38493055556</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>45189</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>44833.86636574074</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>44120</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>45075</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>45798.87049768519</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>45773</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>45260</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44839</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44609.62754629629</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45369.51451388889</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>45093.41260416667</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>45463</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>45093</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>45121.62556712963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>45525.37091435185</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>45561</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>45561</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>45761.36119212963</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>45166.81506944444</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44746.52041666667</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45106.66513888889</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45111</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>45547.44084490741</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>45439.56545138889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>45534.39119212963</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44882</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44882</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45805</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>45075</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>45049</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>45222.46246527778</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>45070</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>45244</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44881.47697916667</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45121</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45478.47974537037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45740.58935185185</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44364</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>44869.44665509259</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>45154.46340277778</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>44873.78972222222</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45366.36186342593</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>44908</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>45155</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>45084.52010416667</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>44973.68172453704</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31679,7 +31679,7 @@
         <v>45442.44923611111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>45260</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>45336</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44351</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44844</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>45810.50623842593</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>45754.57903935185</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>45079.47167824074</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>45315</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>45341.43773148148</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45346.58555555555</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>44992.53199074074</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>45509.84324074074</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>45409.28716435185</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32487,7 +32487,7 @@
         <v>45510.39084490741</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32544,7 +32544,7 @@
         <v>44713.63434027778</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45367.29472222222</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>45635.46313657407</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>45561</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45561</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45475.72082175926</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45475.76681712963</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>44825.37355324074</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>44928.58678240741</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45666.41087962963</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>45812.31928240741</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45813.61375</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44497</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>45554</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33352,7 +33352,7 @@
         <v>44690.55664351852</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33409,7 +33409,7 @@
         <v>45812.58846064815</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>45812.59289351852</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>45572.55528935185</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>45763.38137731481</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45813.61592592593</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33709,7 +33709,7 @@
         <v>45813.61734953704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>45363.79693287037</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45071</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>45188</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>44778.47969907407</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45117.52946759259</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34056,7 +34056,7 @@
         <v>45356.37466435185</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>45175.79483796296</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34170,7 +34170,7 @@
         <v>44953</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45335</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>45335</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>45664</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>45218.41752314815</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45818</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>44867.83100694444</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>45338.3546412037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45818.33222222222</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>45484.50075231482</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>45818</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34802,7 +34802,7 @@
         <v>45093</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34859,7 +34859,7 @@
         <v>45078</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34916,7 +34916,7 @@
         <v>45407.33482638889</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34973,7 +34973,7 @@
         <v>44816</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>45819</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45670.48837962963</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>45863.79833333333</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>44959</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45863.78525462963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>45863.79356481481</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45820.40359953704</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44928</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>45820</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45820.4099537037</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45821.48188657407</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45414.88950231481</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44307.41146990741</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>45820.40600694445</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45820.43005787037</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45478</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45825.38628472222</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45653.66523148148</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45824.57248842593</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>44713.6349537037</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45824.63803240741</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45824.47503472222</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45824.56317129629</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45446.57478009259</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45873.50734953704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45831.28561342593</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45545</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45833.63016203704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>44949.39141203704</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>45734.48820601852</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>45063</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>45254.55388888889</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>45832</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>45385</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37008,7 +37008,7 @@
         <v>45833.62319444444</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>45834.48547453704</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>45834.48055555556</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>44959.60054398148</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45834.42243055555</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>45188</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>44308</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45834.42037037037</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45702.52855324074</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45834.49290509259</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45881.43982638889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>45668.61670138889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45880.32877314815</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45880.33408564814</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>44889</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>44275.89116898148</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45873</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45837.43159722222</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45837.45643518519</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>45169.63607638889</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>45841.34291666667</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>45840.8866087963</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>45882.68247685185</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45840.36429398148</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>45883.58712962963</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>45883.60289351852</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45882.68072916667</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>44915.64974537037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>45744.34409722222</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45616.69401620371</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>45887.44094907407</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>45754.58637731482</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45616.68453703704</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45842.47361111111</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45111.56173611111</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45602</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45131</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45394.64731481481</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45817.4940625</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>44756</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39308,7 +39308,7 @@
         <v>45063.42767361111</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39365,7 +39365,7 @@
         <v>44874.3702662037</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45846.46805555555</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45888.41995370371</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>45525.33855324074</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>44721</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39650,7 +39650,7 @@
         <v>45846.47327546297</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39707,7 +39707,7 @@
         <v>45888.65425925926</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>45119.35530092593</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45849.46460648148</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>44903.63063657407</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39935,7 +39935,7 @@
         <v>44453</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>45368.71136574074</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40049,7 +40049,7 @@
         <v>45369.51261574074</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>45772.56983796296</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>45849.47482638889</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>45104.47891203704</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40282,7 +40282,7 @@
         <v>45891.37724537037</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40339,7 +40339,7 @@
         <v>44390</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>45894.57494212963</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45894.63583333333</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>45894.63924768518</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>45894.55900462963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45894.57186342592</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>44368.47782407407</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>45852.64087962963</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>45852.67128472222</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45894.45385416667</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45888</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>45894.63353009259</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>45832</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>45894.45178240741</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41167,7 +41167,7 @@
         <v>44368</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>45894.63461805556</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45894</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>44677</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>44853.58972222222</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>45901.85667824074</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45856.43209490741</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>45198.49947916667</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41633,7 +41633,7 @@
         <v>45856.42729166667</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>44890.45898148148</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>45078</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41809,7 +41809,7 @@
         <v>45901.8715625</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>45856.4249537037</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45859.46207175926</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45898.59107638889</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>45894</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45579</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>45301.31474537037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>45301.32008101852</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>44951.40828703704</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45429.32715277778</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45331.60153935185</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45649.56231481482</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>45649.56582175926</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45561.61627314815</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45862.61716435185</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45775</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45223</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45512.32738425926</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>44742</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45905.61746527778</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>44340.37858796296</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45210.43765046296</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45862.62265046296</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45561.42905092592</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45359.64686342593</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>44497.23909722222</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>44713.63319444445</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>44917.52387731482</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45096</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45590.48756944444</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45757.42518518519</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45091.44643518519</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>44798</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43715,7 +43715,7 @@
         <v>44593</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45648</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
         <v>45098</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43886,7 +43886,7 @@
         <v>45392.56177083333</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>44746.56648148148</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>45240.48289351852</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44057,7 +44057,7 @@
         <v>45056</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>44914.47359953704</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>44914.5846875</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>44931.48902777778</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>44183</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45096</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45359.64494212963</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45118</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45118.44516203704</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45579</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>45279</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>45056.72038194445</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45544.7580787037</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>44827</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>44973.28375</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>44407.33692129629</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44974,7 +44974,7 @@
         <v>45016.44748842593</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45031,7 +45031,7 @@
         <v>45596.73567129629</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45728.71716435185</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45145,7 +45145,7 @@
         <v>45517.57674768518</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>44825</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>45754.57761574074</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45653.6771875</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>44832.45126157408</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45095</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>44382</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45103</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45694.35719907407</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>44390.44760416666</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45754.4484375</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>44270</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45603</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45191.43909722222</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45098</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>44865.32546296297</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>44839</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45244</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>45744.33675925926</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45217.64325231482</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>45145</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45145.57739583333</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46481,7 +46481,7 @@
         <v>45434.42591435185</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>45163.48395833333</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>45182</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>44819</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46714,7 +46714,7 @@
         <v>44867</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46771,7 +46771,7 @@
         <v>45211</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46828,7 +46828,7 @@
         <v>44528.68445601852</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46885,7 +46885,7 @@
         <v>45762.6184375</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46942,7 +46942,7 @@
         <v>45744.58425925926</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46999,7 +46999,7 @@
         <v>45367.31642361111</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45091.44322916667</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>45773</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>45169.62481481482</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45233</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47289,7 +47289,7 @@
         <v>45072.49809027778</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45244</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47403,7 +47403,7 @@
         <v>45103.42912037037</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>45103.4578125</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47517,7 +47517,7 @@
         <v>44999.51451388889</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47574,7 +47574,7 @@
         <v>45188.35988425926</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>45644.49726851852</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>45342.93295138889</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47745,7 +47745,7 @@
         <v>45321.30368055555</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47802,7 +47802,7 @@
         <v>45649.63702546297</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         <v>44431</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>45213.83515046296</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>44868</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>45629.52961805555</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>45342.93903935186</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45135</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>45225</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>44945.47278935185</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48315,7 +48315,7 @@
         <v>44333.68109953704</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48372,7 +48372,7 @@
         <v>44910</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45603</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45685.44299768518</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45156.75122685185</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>44566</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45373.4965625</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45770.36494212963</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45211.43076388889</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45210</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45567</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45762.47326388889</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>44909</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>44909.51342592593</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45622.7463425926</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45668.48770833333</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45702.63559027778</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49299,7 +49299,7 @@
         <v>44351.66695601852</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>45156.74657407407</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>44231.57006944445</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45637.55811342593</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
         <v>44811.50899305556</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49589,7 +49589,7 @@
         <v>45713.67922453704</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49651,7 +49651,7 @@
         <v>45714.24815972222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49708,7 +49708,7 @@
         <v>44866.62503472222</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>44755</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>44594.37378472222</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49879,7 +49879,7 @@
         <v>44992.52833333334</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45096</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49993,7 +49993,7 @@
         <v>44335</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50050,7 +50050,7 @@
         <v>44368.48951388889</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>45373.43667824074</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>45085.55108796297</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45705.37840277778</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>45216</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>44909.49190972222</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50392,7 +50392,7 @@
         <v>44991.4569212963</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>45069.42486111111</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>44236</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50563,7 +50563,7 @@
         <v>45679</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50620,7 +50620,7 @@
         <v>44973.68408564815</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         <v>45551.45940972222</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50734,7 +50734,7 @@
         <v>44684.43402777778</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>45628</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50848,7 +50848,7 @@
         <v>45764</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50905,7 +50905,7 @@
         <v>45764</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50962,7 +50962,7 @@
         <v>44974.39552083334</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45057</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45057</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45177</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51195,7 +51195,7 @@
         <v>45475.70619212963</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51252,7 +51252,7 @@
         <v>44431</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>44386.57552083334</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51366,7 +51366,7 @@
         <v>44910</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51423,7 +51423,7 @@
         <v>45205.32967592592</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51480,7 +51480,7 @@
         <v>44972</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51537,7 +51537,7 @@
         <v>44463.49472222223</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51594,7 +51594,7 @@
         <v>45606.57791666667</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51651,7 +51651,7 @@
         <v>45401.70074074074</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51708,7 +51708,7 @@
         <v>45239</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51765,7 +51765,7 @@
         <v>45089</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45079</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51884,7 +51884,7 @@
         <v>45429.49690972222</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>44798</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45730.29663194445</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45762.62880787037</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>44785.36618055555</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45113</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45217.49613425926</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45761.60565972222</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>44880.27605324074</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45174.32129629629</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45385.47306712963</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>44376</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>44488</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45177</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45011</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45089.45716435185</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>44645.61398148148</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45208</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45400.70824074074</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45737.66273148148</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>44462</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>44463.49251157408</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45231</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45610.49638888889</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45055.32497685185</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45534.65803240741</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45702.63752314815</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45744.56760416667</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45713</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45714.28113425926</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45342.58545138889</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45664.89855324074</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45616.70280092592</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45484.50256944444</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45253</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>45411.56006944444</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45191.39680555555</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45710.35591435185</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45706.59305555555</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>44209</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>44936.7375925926</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45572.49996527778</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45474.54547453704</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54350,7 +54350,7 @@
         <v>45756.46728009259</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
         <v>45649.57708333333</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54464,7 +54464,7 @@
         <v>45649.58368055556</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54521,7 +54521,7 @@
         <v>45649.63318287037</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54578,7 +54578,7 @@
         <v>44700.52403935185</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54635,7 +54635,7 @@
         <v>45762.406875</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54697,7 +54697,7 @@
         <v>44917</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>44938.4812962963</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>44622</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54873,7 +54873,7 @@
         <v>45240.54020833333</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>44419</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54987,7 +54987,7 @@
         <v>44083</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>45560.66090277778</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>44865</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55163,7 +55163,7 @@
         <v>44867</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55220,7 +55220,7 @@
         <v>45744.35152777778</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55277,7 +55277,7 @@
         <v>45280.75414351852</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55334,7 +55334,7 @@
         <v>45758.47427083334</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>44580.39465277778</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45761.7169212963</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55515,7 +55515,7 @@
         <v>45762.37043981482</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55572,7 +55572,7 @@
         <v>44749</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55629,7 +55629,7 @@
         <v>45591.31592592593</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55686,7 +55686,7 @@
         <v>44973.8353125</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55743,7 +55743,7 @@
         <v>45043</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55800,7 +55800,7 @@
         <v>45616.69777777778</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55857,7 +55857,7 @@
         <v>45175</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>45308.45605324074</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55971,7 +55971,7 @@
         <v>45426.64987268519</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>45050</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56085,7 +56085,7 @@
         <v>45330</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56142,7 +56142,7 @@
         <v>45103.4828125</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56199,7 +56199,7 @@
         <v>45758.65511574074</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56256,7 +56256,7 @@
         <v>44974.3628125</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56313,7 +56313,7 @@
         <v>45149.52997685185</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56370,7 +56370,7 @@
         <v>44693.40193287037</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56432,7 +56432,7 @@
         <v>44739</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>45210</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>44881</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>44369</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>45664.88829861111</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>44494.39315972223</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>45603</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45296</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45175.80216435185</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>45728.71802083333</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>45412</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45371.47248842593</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>45187.45348379629</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>44586.39371527778</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>44743</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57287,7 +57287,7 @@
         <v>44594</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45320.32636574074</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>44904</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>44348</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57520,7 +57520,7 @@
         <v>45741.39699074074</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57577,7 +57577,7 @@
         <v>44298.33628472222</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57634,7 +57634,7 @@
         <v>45681</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57696,7 +57696,7 @@
         <v>44798.56335648148</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57753,7 +57753,7 @@
         <v>44882</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57810,7 +57810,7 @@
         <v>45733.60050925926</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>44266.66663194444</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57924,7 +57924,7 @@
         <v>45415.32408564815</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57981,7 +57981,7 @@
         <v>45379</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58038,7 +58038,7 @@
         <v>44977</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58095,7 +58095,7 @@
         <v>44977.54047453704</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58152,7 +58152,7 @@
         <v>45721</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58209,7 +58209,7 @@
         <v>45035</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58266,7 +58266,7 @@
         <v>44909</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58323,7 +58323,7 @@
         <v>45090.53722222222</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58380,7 +58380,7 @@
         <v>44621</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>44579.36934027778</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>45392.59135416667</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>45372.34578703704</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58608,7 +58608,7 @@
         <v>44803</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58665,7 +58665,7 @@
         <v>44904</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58722,7 +58722,7 @@
         <v>44904</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58779,7 +58779,7 @@
         <v>45560.65891203703</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>45079.49798611111</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>45763</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58950,7 +58950,7 @@
         <v>45197</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59007,7 +59007,7 @@
         <v>45469.49331018519</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59064,7 +59064,7 @@
         <v>44418</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>45478.55826388889</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>45727</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59240,7 +59240,7 @@
         <v>44939.46715277778</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -567,7 +567,7 @@
         <v>45898.5890625</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>44460.70982638889</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44606</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45810.50783564815</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45616</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45189</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>44490</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44112</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>45735.34555555556</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44370</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>45352.45320601852</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44867</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45888.34414351852</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45888.42650462963</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44347</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44145</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45174.32886574074</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>45652.74018518518</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>45428.42564814815</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45447</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>45730.63277777778</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45695.93653935185</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>44266</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>45075</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>44120</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>45358.44835648148</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>45621.63548611111</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>44785.43395833333</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45093.3646875</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45093.3703587963</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44937</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>45894.56163194445</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>45894.64087962963</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45832</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>45853</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45222</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>44175</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44602</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44375</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>45215</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45721.65631944445</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>45541.51222222222</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45096</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>44909</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>44504.50979166666</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>45594</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>45701.45335648148</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>45316</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>44648</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45042</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45621.64417824074</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44120</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>45103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>45621.64115740741</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45449.38423611111</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>45110</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45754.48619212963</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>44448.31037037037</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45581.56951388889</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44656</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45307</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>45873</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45840.8834375</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>44365</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>44917</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>45846.4975</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>45616.66118055556</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>45850.60619212963</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>45894.57494212963</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>45894.64207175926</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>45891.63179398148</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45894.55900462963</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45894.57186342592</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45604.50471064815</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45863.39380787037</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>44966.64579861111</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>44917</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>45695.93015046296</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>45615.62699074074</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>44980</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44347</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44179</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>44261</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44378</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>44120</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44183</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44130</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>44110.43048611111</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44224</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>44385.40346064815</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>44230</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>44272</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>44300.3625</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>44123</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>44208</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44120</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44278</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44407.34103009259</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44363.76037037037</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44267.32773148148</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44462</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44201</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44407.35815972222</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44379</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44630</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>44418.56681712963</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>44089</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>44320</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44236</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>44225</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44342.65030092592</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>44297</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>44365</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>44194</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>44363.75403935185</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44889.52459490741</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>44302</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>44691</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>44138</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>44137.79510416667</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44474</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44412</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>44859</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44102</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44164</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>44245</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44365</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>44473.51576388889</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>44861</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44475</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44246</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44362</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44581</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>44587</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44449.57666666667</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44844</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>44656</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>44612</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44816</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44571.48392361111</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>44152</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>44645.61962962963</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44187</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>44088</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>44088</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>44130</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44201</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>44565</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>44256</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>44312.52064814815</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>44593.58975694444</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>44131</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>44831.51668981482</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>44840</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44365</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>44783</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>44179</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>44365</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>44375.42613425926</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>44369</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>44566</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>44684</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44328</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>44365</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>44306</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>44347</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>44315.67481481482</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>44806.30436342592</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44364.69368055555</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44493.7688425926</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>44488.93328703703</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>44362</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44217.63880787037</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>44833.85800925926</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44386.50282407407</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>44468.38931712963</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>44587</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>44624.4716087963</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>44593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>44294.69576388889</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>44449.61309027778</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>44449</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>44169</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>44172</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44321.32876157408</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>44419</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>44295.56511574074</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>44340.37452546296</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>44363.75775462963</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>44284</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>44259</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>44776.4441087963</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>44384</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44870.4825462963</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>44449.61662037037</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>44594.37494212963</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>44629</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44494</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44351</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44593</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44378.26744212963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44748.39954861111</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>44771.403125</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>44881.46946759259</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>44183</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>44378.27100694444</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>44418</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44650</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>44365</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>44634</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>44634</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>44796</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44370.25283564815</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44727</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44657</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44551.60501157407</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44104.58186342593</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44112</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44211</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44137</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>44223</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>44839.34592592593</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44161</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>44375</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>44183</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>44218</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>44270.62047453703</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>44612.64552083334</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>44160</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44407.33940972222</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>44593</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>44449</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>44813.46402777778</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44225</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>44169</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>44089</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>44207.56376157407</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44617.57709490741</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44805.72581018518</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44243.24046296296</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>44376</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>44551</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>44870.4822337963</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>44785.35797453704</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>44551</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>44508</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>44246</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>44587</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>44250</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>44136</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>44376</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>44348</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>45043</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>45054</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>44222</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45572.49996527778</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>44419</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>45510.39084490741</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>45702.52855324074</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>45091.44322916667</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45713</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44853</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45190</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>44839</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>44851</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>44866.62503472222</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>44866.6291550926</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>44755</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>44867</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>44299.65049768519</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45075</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>45253</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>44270</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>45342.93903935186</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>44827</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>45363.79693287037</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>44295</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45216</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>45341.43773148148</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45336</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45773</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45434.42591435185</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45078</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45702.63752314815</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>45579</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>44505</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>44300.5134375</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         <v>44307.41146990741</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45762.6184375</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>45118.44516203704</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>44266.66663194444</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45093</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>45121</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45280.75414351852</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45679</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45123.42461805556</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45117.52946759259</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45713</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45714.28113425926</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>45649.55618055556</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>45649.59947916667</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45649.63702546297</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45217.64325231482</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45762.62880787037</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>44890.45898148148</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>44092</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45622.7463425926</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>44999</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>45084.52010416667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>45666.41087962963</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>45103.4578125</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>45103.4828125</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45181</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45376.57670138889</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45440</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>45551.45940972222</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>45070</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>45561.42905092592</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44489</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>44868.38045138889</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>44277</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>44606.73197916667</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>45601.6175</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45449.73532407408</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>45545.46103009259</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>45079.47167824074</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45476.37739583333</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>45149.53783564815</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>44453</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>45107.72561342592</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>44465.45304398148</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>45754.58804398148</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>45489.67844907408</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>44407.33692129629</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>44953</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45469.49331018519</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>44593</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>45156.75122685185</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44363.75042824074</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44526.31395833333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45478.55826388889</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22724,7 +22724,7 @@
         <v>45104.47891203704</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45392.56559027778</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45587.39587962963</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>45359.64686342593</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>45155</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45786.36038194445</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45429.32715277778</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>45665.30042824074</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>45785.85196759259</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45706.64979166666</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>45698.47010416666</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>45547.5259375</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45572.50128472222</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44867.83456018518</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44300.37375</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>44315.61856481482</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>45230.60619212963</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>44839</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44910</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45370</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44938.4812962963</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45246.69150462963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>45253</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45357.56929398148</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>44973.68172453704</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45367.30908564815</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45785.57039351852</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>45673.35722222222</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>45785.5658912037</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>45301</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>44973.51290509259</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24496,7 +24496,7 @@
         <v>44973</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45625</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>45744.56760416667</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>45260</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>45770.36494212963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45489</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45785.33315972222</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>44982.82561342593</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45616.69777777778</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45096</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45579</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45474.54547453704</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45169.62481481482</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>44580.39465277778</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>44333.68109953704</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45786.35825231481</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>45079</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44376.47229166667</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>45320.32636574074</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>44375.39068287037</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>45401.55627314815</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>45233</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>44957</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>45786.3628125</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>44957.56633101852</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>45534.67787037037</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>45791.46207175926</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>45113</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>44578.49199074074</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>45790.8237962963</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>45792.46319444444</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>44445</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>44407.35585648148</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>44407.35945601852</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>45792.46534722222</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45791.45240740741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>45792.4578587963</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45792.46865740741</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45118</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>45131</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45763</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>45534.39119212963</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>45773</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>45315</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>45016.44748842593</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27091,7 +27091,7 @@
         <v>45342.58545138889</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>45561.61627314815</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44528.68445601852</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44566</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45796.54754629629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>45701.1425</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45092.3945949074</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>45668.61670138889</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45197</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45761.54658564815</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>44596.39430555556</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27728,7 +27728,7 @@
         <v>45603</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>45035</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45341</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>45798.38493055556</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>44832.45126157408</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>45475.72082175926</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>45475.76681712963</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45218.41752314815</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>45169.63607638889</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>45338.3546412037</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45560.66090277778</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>44645.61398148148</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28417,7 +28417,7 @@
         <v>45729.53497685185</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45478.47974537037</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>44915.64974537037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45727.54988425926</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>45727</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>45545</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45713.67922453704</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45714.24815972222</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45602</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>45798.87049768519</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>44697</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44972</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45664.89855324074</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>44908</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>44677</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45373.43667824074</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45327</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>45063</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>45089.45716435185</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>45551.45708333333</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>45525.37091435185</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44488</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>45082</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45191.39680555555</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>45805</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>44351</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44657</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>44914.5846875</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45547.44084490741</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45544.7580787037</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>44594</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45049</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>44120</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>44622</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45224.64084490741</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45177</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45637.55811342593</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44904</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>45072.49809027778</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>45442.44923611111</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>44959</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45517.57674768518</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>45744.58425925926</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45664.88829861111</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>45664</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>45762.47326388889</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>45754.57761574074</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>45118</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44209</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44928</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>45392.56177083333</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>45810.50623842593</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31426,7 +31426,7 @@
         <v>45196.41028935185</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>44544.63826388889</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>45812.59289351852</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>44959.60054398148</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>45758.47427083334</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>44833.86636574074</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44692</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>45812.31928240741</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>45561</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>45561</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>44917.52387731482</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>45813.61592592593</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>45813.61734953704</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44690.55664351852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>45408.42273148148</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>45754.58637731482</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>45685.44299768518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>45813.61375</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44684.43402777778</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>45615</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>44992.53199074074</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>45577.88273148148</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>45818.33222222222</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>45098</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32834,7 +32834,7 @@
         <v>45182</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32891,7 +32891,7 @@
         <v>45720.48189814815</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>45175</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45093</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>44873.78972222222</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>45820.4099537037</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>45145</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>45145.57739583333</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>45653</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>45820.40359953704</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45819</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>44593</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45244</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45741.39699074074</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45818</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45820.40600694445</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45820.43005787037</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>45756.4618287037</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33880,7 +33880,7 @@
         <v>45335</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45820</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45222.46246527778</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>45211</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>44223</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34165,7 +34165,7 @@
         <v>44223</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34222,7 +34222,7 @@
         <v>44973.87971064815</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>45187.45348379629</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34336,7 +34336,7 @@
         <v>45702.63559027778</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>45824.57248842593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45385</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>45821.48188657407</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>45824.47503472222</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>44368.48412037037</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>45824.63803240741</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>45478</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34802,7 +34802,7 @@
         <v>45407.33482638889</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34859,7 +34859,7 @@
         <v>45824.56317129629</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>45239</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44910</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>44742</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>45177</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>44909</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>45825.38628472222</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>45175</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45198.49947916667</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44973.28375</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45211.43076388889</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>45572.55528935185</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45372.34578703704</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45037</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45757.42518518519</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>45225</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>44224</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>44749</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>44939.46715277778</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>45223</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>45230.60807870371</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45367.31642361111</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44721</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>44743</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>44733.39600694444</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44867.83100694444</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45831.28561342593</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45175.79483796296</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>44970.82792824074</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>44966.65418981481</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>44966.65623842592</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45734.48820601852</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45702.6415625</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45191.43909722222</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>45414.88950231481</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>45754.5805787037</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45832</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45873.50734953704</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>45756.46728009259</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37117,7 +37117,7 @@
         <v>45744.34409722222</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>44909.51041666666</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45833.62319444444</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45834.48055555556</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>45244</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>45834.42243055555</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>45834.48547453704</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>44841</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37573,7 +37573,7 @@
         <v>45833.63016203704</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45775.61712962963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>44803</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>44693.40193287037</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45834.49290509259</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45596.73567129629</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45448.40923611111</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45834.42037037037</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45764</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45764</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>44739</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>44746.52041666667</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45095</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45737.66273148148</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45695.44407407408</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45733.27633101852</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>44713.63434027778</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45415.32408564815</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45071</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45586</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45439.56545138889</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45740.58935185185</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>44825.37355324074</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>45070</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45367.29472222222</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45411.56006944444</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>45254.55388888889</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>44713.6349537037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>45121.62556712963</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>45121</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>44275.89116898148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>44746.56648148148</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45330</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45873</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>45880.32877314815</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>44497</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>44974.39552083334</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>45880.33408564814</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>44798.56335648148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>45307</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>45628</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45359.64494212963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39972,7 +39972,7 @@
         <v>45837.43159722222</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>45837.45643518519</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
         <v>45089</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>45629.52961805555</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>44931.48902777778</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>44231.57006944445</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>45106.66513888889</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>45561</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>45561</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>45366.36186342593</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>45189</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>44335</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>45057</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>45057</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40790,7 +40790,7 @@
         <v>45217.49613425926</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40847,7 +40847,7 @@
         <v>44917</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>44368</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>45730.29663194445</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>44959</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>45273.43420138889</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>44819</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45301.31474537037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45301.32008101852</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41313,7 +41313,7 @@
         <v>44819</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>45763.38137731481</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>45882.68247685185</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>45763</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41546,7 +41546,7 @@
         <v>45881.43982638889</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41608,7 +41608,7 @@
         <v>45327.3969212963</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41665,7 +41665,7 @@
         <v>45022.47684027778</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>45681</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>45882.68072916667</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>44351.66695601852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>45253</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>45754.4484375</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>45210.43765046296</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>45475.70619212963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>44999.51451388889</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45177</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>44298.33628472222</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>45705.37840277778</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>44333.63303240741</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>44340.37858796296</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>45744.35152777778</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>45092.3869675926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>45346.58555555555</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>45628</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42711,7 +42711,7 @@
         <v>45728.57760416667</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45727.55368055555</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45706.59305555555</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45119.35530092593</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42944,7 +42944,7 @@
         <v>45278</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>45840.36429398148</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43058,7 +43058,7 @@
         <v>45090.53722222222</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
         <v>45610.49638888889</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43172,7 +43172,7 @@
         <v>45883.58712962963</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>45883.60289351852</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>44756</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>45484.50256944444</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>45091.44966435185</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>45409.28716435185</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>45840.8866087963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43576,7 +43576,7 @@
         <v>45694.35719907407</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>44308</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43690,7 +43690,7 @@
         <v>44302.60905092592</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43747,7 +43747,7 @@
         <v>44868</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45728.71802083333</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45022</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45841.34291666667</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>44621</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45653.66523148148</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45154.46340277778</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>44390.44760416666</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44213,7 +44213,7 @@
         <v>45111.3095949074</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>44936.7375925926</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44327,7 +44327,7 @@
         <v>44390</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>45231</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>45484.50075231482</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44498,7 +44498,7 @@
         <v>44865.32546296297</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>44369</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>44386.57552083334</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45687.58510416667</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>44818</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>45772.56983796296</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>45369.55871527778</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>45762.406875</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>44945.47278935185</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>44494.39315972223</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45775.59509259259</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>45728.71716435185</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>45733.60050925926</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>44991.4569212963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45554</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>44816</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>44881</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>44844</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45744.33675925926</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45509.84324074074</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>44985.4822337963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45189</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>44418</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>45728.58208333333</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>44700.52403935185</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45943,7 +45943,7 @@
         <v>45072.49364583333</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46000,7 +46000,7 @@
         <v>44889</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>45135</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45463</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>45534.65803240741</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45055.32497685185</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>45111.56173611111</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>45761.7169212963</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46404,7 +46404,7 @@
         <v>45762.37043981482</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46461,7 +46461,7 @@
         <v>45775</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         <v>45426.64987268519</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45842.47361111111</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>44869.44665509259</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45763</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45394.66318287037</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>45090.50210648148</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>44236</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45342.93295138889</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>44431</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>44431</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>45887.44094907407</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45616.69401620371</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>45888.65425925926</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>45188</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47326,7 +47326,7 @@
         <v>45400.70824074074</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47383,7 +47383,7 @@
         <v>44874.3702662037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47440,7 +47440,7 @@
         <v>45077</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47497,7 +47497,7 @@
         <v>45013.53428240741</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>45090.57193287037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>44609.62754629629</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45552.43833333333</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45846.47327546297</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>44382</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>44882</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>44909</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>44973.8353125</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45210</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45296</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48124,7 +48124,7 @@
         <v>45754.57903935185</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48186,7 +48186,7 @@
         <v>45817.4940625</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>45846.46805555555</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45107</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>44825</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48414,7 +48414,7 @@
         <v>45342.58582175926</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48471,7 +48471,7 @@
         <v>45616.68453703704</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45096</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45888.41995370371</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45098</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>44364</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45575.40405092593</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>44183</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>44243</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45156.74657407407</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45313</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45561</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49160,7 +49160,7 @@
         <v>45761.36119212963</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49217,7 +49217,7 @@
         <v>44904</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49274,7 +49274,7 @@
         <v>45174.32129629629</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49331,7 +49331,7 @@
         <v>45335</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49393,7 +49393,7 @@
         <v>45394.64731481481</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>45888</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49512,7 +49512,7 @@
         <v>45446.57478009259</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45368.71136574074</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45369.51261574074</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>44992.52833333334</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45891.37724537037</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45849.47482638889</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>44462</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>44463.49251157408</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45894.63583333333</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45894.63924768518</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>44579.36934027778</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45849.46460648148</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>44928.58678240741</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45894.45178240741</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>44594.37378472222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>44933.42714120371</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>44977</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>44977.54047453704</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45852.67128472222</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45894.63353009259</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45894.63461805556</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50734,7 +50734,7 @@
         <v>45852.64087962963</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>45894.45385416667</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50848,7 +50848,7 @@
         <v>44881.47697916667</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50905,7 +50905,7 @@
         <v>45188</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50962,7 +50962,7 @@
         <v>45244</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45072</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45832</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45371.47248842593</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>44914.47359953704</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45856.42729166667</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45856.43209490741</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45898.59107638889</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>44497.23909722222</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>44949.39141203704</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45512.32738425926</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45260</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51661,7 +51661,7 @@
         <v>45894</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51718,7 +51718,7 @@
         <v>45188.35988425926</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>45856.4249537037</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>44909.49190972222</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>44798</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51951,7 +51951,7 @@
         <v>45385.47306712963</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>45056.72038194445</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52065,7 +52065,7 @@
         <v>45859.46207175926</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52122,7 +52122,7 @@
         <v>45901.8715625</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52179,7 +52179,7 @@
         <v>45606.57791666667</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>45710.35591435185</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52293,7 +52293,7 @@
         <v>45075</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52350,7 +52350,7 @@
         <v>45894</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52407,7 +52407,7 @@
         <v>45901.85667824074</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         <v>45603</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52521,7 +52521,7 @@
         <v>44900.47381944444</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>45213.83515046296</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52635,7 +52635,7 @@
         <v>45862.61716435185</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52692,7 +52692,7 @@
         <v>45862.62265046296</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>44904</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>44984</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>45082.42459490741</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52920,7 +52920,7 @@
         <v>44909.51342592593</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52977,7 +52977,7 @@
         <v>45863.79833333333</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         <v>45567</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>45091.44643518519</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53153,7 +53153,7 @@
         <v>45648</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45908.56230324074</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53267,7 +53267,7 @@
         <v>45908.49853009259</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53324,7 +53324,7 @@
         <v>44494.38530092593</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53381,7 +53381,7 @@
         <v>44463.49472222223</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53438,7 +53438,7 @@
         <v>45818</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>45863.79356481481</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>45616.70280092592</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45905.61746527778</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45392.59135416667</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45063.42767361111</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>44798</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45863.78525462963</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45069.67789351852</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>44853.58972222222</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45470.66217592593</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45021</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45079</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45111</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45668.48770833333</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45668.49403935186</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54350,7 +54350,7 @@
         <v>45910.73662037037</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
         <v>45912.49222222222</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54464,7 +54464,7 @@
         <v>45912.47719907408</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54521,7 +54521,7 @@
         <v>45911.42645833334</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54578,7 +54578,7 @@
         <v>44713.63319444445</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54635,7 +54635,7 @@
         <v>45911.40376157407</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54692,7 +54692,7 @@
         <v>44908</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54749,7 +54749,7 @@
         <v>44974.3628125</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54806,7 +54806,7 @@
         <v>45079.49798611111</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>45208</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>45909</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54977,7 +54977,7 @@
         <v>45078</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>45525.33855324074</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55091,7 +55091,7 @@
         <v>45590.48756944444</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55148,7 +55148,7 @@
         <v>45175.80216435185</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55205,7 +55205,7 @@
         <v>44973.68408564815</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55262,7 +55262,7 @@
         <v>45078</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55319,7 +55319,7 @@
         <v>45488.44295138889</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55376,7 +55376,7 @@
         <v>45050</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55433,7 +55433,7 @@
         <v>45401.70074074074</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55490,7 +55490,7 @@
         <v>45149.52997685185</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         <v>45075</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55604,7 +55604,7 @@
         <v>45679</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         <v>44951.40828703704</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55718,7 +55718,7 @@
         <v>44880.27605324074</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>45758.65511574074</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55832,7 +55832,7 @@
         <v>45737.66959490741</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55889,7 +55889,7 @@
         <v>45606.57449074074</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55946,7 +55946,7 @@
         <v>44586.39371527778</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56003,7 +56003,7 @@
         <v>45093.41260416667</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>45517.5049074074</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>45162</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>44865</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         <v>44909.50149305556</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         <v>45085.55108796297</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>45308.45605324074</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>45649.57708333333</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>45649.58368055556</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>45649.63318287037</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45240.48289351852</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>44785.36618055555</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56687,7 +56687,7 @@
         <v>45011</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45210</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45110</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>45649.56231481482</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45649.56582175926</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56977,7 +56977,7 @@
         <v>45591.31592592593</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57034,7 +57034,7 @@
         <v>45635.46313657407</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57091,7 +57091,7 @@
         <v>45670.48837962963</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57153,7 +57153,7 @@
         <v>45028.64141203704</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         <v>44811.50899305556</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57267,7 +57267,7 @@
         <v>44867</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57324,7 +57324,7 @@
         <v>45429.49690972222</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57381,7 +57381,7 @@
         <v>44594</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         <v>45331.60153935185</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57495,7 +57495,7 @@
         <v>45022</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         <v>45177</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57614,7 +57614,7 @@
         <v>44778.47969907407</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57671,7 +57671,7 @@
         <v>45056</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>45149</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57785,7 +57785,7 @@
         <v>45561</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45205.32967592592</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>44882</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45721</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45103.42912037037</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45240.54020833333</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>44903.63063657407</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45279</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45477.45034722222</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>44368.48951388889</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45407.58145833333</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         <v>44882</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>44368.47782407407</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45069.42486111111</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45163.48395833333</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45373.4965625</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45369.51451388889</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>45356.37466435185</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>45166.81506944444</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58873,7 +58873,7 @@
         <v>45321.30368055555</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58930,7 +58930,7 @@
         <v>45013.59971064814</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45560.65891203703</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59044,7 +59044,7 @@
         <v>45653.6771875</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59101,7 +59101,7 @@
         <v>45603</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59158,7 +59158,7 @@
         <v>45644.49726851852</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59215,7 +59215,7 @@
         <v>45096</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -567,7 +567,7 @@
         <v>45898.5890625</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>44460.70982638889</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44606</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45810.50783564815</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45616</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>45189</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>44490</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>44112</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>45735.34555555556</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>44370</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>45352.45320601852</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44867</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>45888.34414351852</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45888.42650462963</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44347</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44145</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45174.32886574074</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>45652.74018518518</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>45428.42564814815</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45447</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>45730.63277777778</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>45695.93653935185</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>44266</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>45075</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>44120</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>45358.44835648148</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>45621.63548611111</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>44785.43395833333</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45093.3646875</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45093.3703587963</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44937</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>45894.56163194445</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>45894.64087962963</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45832</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>45853</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45222</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>44175</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44602</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44375</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>45215</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45721.65631944445</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>45541.51222222222</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45096</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>44909</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>44504.50979166666</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>45594</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>45701.45335648148</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>45316</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>44648</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45042</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45621.64417824074</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44120</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>45103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>45621.64115740741</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45449.38423611111</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>45110</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45754.48619212963</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>44448.31037037037</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45581.56951388889</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44656</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45307</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>45873</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45840.8834375</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>44365</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>44917</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>45846.4975</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>45616.66118055556</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>45850.60619212963</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>45894.57494212963</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>45894.64207175926</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>45891.63179398148</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45894.55900462963</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45894.57186342592</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45604.50471064815</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45863.39380787037</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>44966.64579861111</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>44917</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>45695.93015046296</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>45615.62699074074</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>44980</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44347</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44179</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>44261</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44378</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>44120</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44183</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44130</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>44110.43048611111</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44224</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>44385.40346064815</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>44230</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>44272</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>44300.3625</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>44123</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>44208</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44120</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44278</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44407.34103009259</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44363.76037037037</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44267.32773148148</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44462</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44201</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44407.35815972222</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44379</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44630</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>44418.56681712963</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>44089</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>44320</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44236</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>44225</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44342.65030092592</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>44297</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>44365</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>44194</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>44363.75403935185</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44889.52459490741</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>44302</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>44691</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>44138</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>44137.79510416667</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44474</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44412</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>44859</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44102</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44164</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>44245</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44365</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>44473.51576388889</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>44861</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44475</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44246</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44362</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44581</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>44587</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44449.57666666667</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44844</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>44656</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>44612</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44816</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44571.48392361111</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>44152</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>44645.61962962963</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44187</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>44088</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>44088</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>44130</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44201</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>44565</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>44256</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>44312.52064814815</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>44593.58975694444</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>44131</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>44831.51668981482</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>44840</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44365</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>44783</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>44179</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>44365</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>44375.42613425926</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>44369</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>44566</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>44684</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44328</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>44365</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>44306</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>44347</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>44315.67481481482</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>44806.30436342592</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44364.69368055555</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44493.7688425926</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>44488.93328703703</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>44362</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44217.63880787037</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>44833.85800925926</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44386.50282407407</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>44468.38931712963</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>44587</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>44624.4716087963</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>44593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>44294.69576388889</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>44449.61309027778</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>44449</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>44169</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>44172</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44321.32876157408</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>44419</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>44295.56511574074</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>44340.37452546296</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>44363.75775462963</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>44284</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>44259</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>44776.4441087963</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>44384</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44870.4825462963</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>44449.61662037037</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>44594.37494212963</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>44629</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44494</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44351</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44593</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44378.26744212963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44748.39954861111</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>44771.403125</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>44881.46946759259</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>44183</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>44378.27100694444</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>44418</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44650</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>44365</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>44634</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>44634</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <